--- a/tablitsa.xlsx
+++ b/tablitsa.xlsx
@@ -18,11 +18,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={003400C8-000C-4901-AD9F-0059003B004C}</author>
-    <author>tc={000E00F7-0050-424A-AA86-00CF008B00D2}</author>
+    <author>tc={00E700B8-0084-45E6-9A91-00A000CD00FA}</author>
+    <author>tc={00CF0080-00CC-480A-BACB-009500460033}</author>
   </authors>
   <commentList>
-    <comment ref="R2" authorId="0" xr:uid="{003400C8-000C-4901-AD9F-0059003B004C}">
+    <comment ref="R2" authorId="0" xr:uid="{00E700B8-0084-45E6-9A91-00A000CD00FA}">
       <text>
         <r>
           <rPr>
@@ -43,7 +43,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T2" authorId="1" xr:uid="{000E00F7-0050-424A-AA86-00CF008B00D2}">
+    <comment ref="T2" authorId="1" xr:uid="{00CF0080-00CC-480A-BACB-009500460033}">
       <text>
         <r>
           <rPr>
@@ -2271,7 +2271,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Автор" id="{E392FECC-2F65-6D15-B283-1C8885577552}"/>
+  <person displayName="Автор" id="{B551CB52-1C51-A024-EE68-1ABF630277D0}"/>
 </personList>
 </file>
 
@@ -2769,11 +2769,11 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="R2" personId="{E392FECC-2F65-6D15-B283-1C8885577552}" id="{003400C8-000C-4901-AD9F-0059003B004C}" done="0">
+  <threadedComment ref="R2" personId="{B551CB52-1C51-A024-EE68-1ABF630277D0}" id="{00E700B8-0084-45E6-9A91-00A000CD00FA}" done="0">
     <text xml:space="preserve">Цена всех юнитов в игре уменьшена на 20%
 </text>
   </threadedComment>
-  <threadedComment ref="T2" personId="{E392FECC-2F65-6D15-B283-1C8885577552}" id="{000E00F7-0050-424A-AA86-00CF008B00D2}" done="0">
+  <threadedComment ref="T2" personId="{B551CB52-1C51-A024-EE68-1ABF630277D0}" id="{00CF0080-00CC-480A-BACB-009500460033}" done="0">
     <text xml:space="preserve">Уровень в игре влияет на приоритет получения баффов и дебаффов на урон
 </text>
   </threadedComment>
@@ -2830,7 +2830,7 @@
       <c r="U1" s="13"/>
       <c r="V1" s="6"/>
     </row>
-    <row r="2" ht="16.5">
+    <row r="2" ht="15.75">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" s="35">
         <v>1</v>
@@ -3050,44 +3050,44 @@
       </c>
       <c r="F6" s="26">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="35">
         <v>350</v>
       </c>
       <c r="H6" s="35">
         <f t="shared" si="1"/>
-        <v>29.4495099158381</v>
+        <v>21.417825393336798</v>
       </c>
       <c r="I6" s="31">
         <f t="shared" ref="I6:I9" si="5">(500/F6)/((500/F6)-(G6/300))</f>
-        <v>1.0130001688333616</v>
+        <v>1.009421265141319</v>
       </c>
       <c r="J6" s="32"/>
       <c r="K6" s="36">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L6" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="35">
         <v>0.059999999999999998</v>
       </c>
       <c r="N6" s="35">
         <f t="shared" si="2"/>
-        <v>79.5</v>
+        <v>70</v>
       </c>
       <c r="O6" s="37">
         <f t="shared" si="3"/>
-        <v>14.43670320585786</v>
+        <v>12.7115625711956</v>
       </c>
       <c r="P6" s="26"/>
       <c r="Q6" s="36">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="R6" s="38">
         <f t="shared" si="4"/>
-        <v>45.290194662188192</v>
+        <v>45.326558248612976</v>
       </c>
       <c r="T6" s="38">
         <v>2</v>
@@ -3174,22 +3174,22 @@
         <v>1</v>
       </c>
       <c r="E8" s="26">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="F8" s="26">
         <f t="shared" si="0"/>
-        <v>14.285714285714286</v>
+        <v>14.705882352941178</v>
       </c>
       <c r="G8" s="26">
         <v>600</v>
       </c>
       <c r="H8" s="26">
         <f t="shared" si="1"/>
-        <v>76.492233547631429</v>
+        <v>78.742005122561764</v>
       </c>
       <c r="I8" s="31">
         <f t="shared" si="5"/>
-        <v>1.0606060606060606</v>
+        <v>1.0625</v>
       </c>
       <c r="J8" s="32"/>
       <c r="K8" s="33">
@@ -3211,11 +3211,11 @@
       </c>
       <c r="P8" s="26"/>
       <c r="Q8" s="33">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="R8" s="34">
         <f t="shared" si="4"/>
-        <v>90.034224741501461</v>
+        <v>80.207305981516356</v>
       </c>
       <c r="T8" s="34">
         <v>4</v>
@@ -3919,7 +3919,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="33">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C20" s="26">
         <v>1</v>
@@ -3928,16 +3928,16 @@
         <v>11</v>
       </c>
       <c r="E20" s="26">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="F20" s="26">
         <f t="shared" si="6"/>
-        <v>37.931034482758619</v>
+        <v>32.258064516129032</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="26">
         <f t="shared" si="7"/>
-        <v>203.10006838509031</v>
+        <v>172.72439833336128</v>
       </c>
       <c r="I20" s="31">
         <v>1</v>
@@ -3962,11 +3962,11 @@
       </c>
       <c r="P20" s="26"/>
       <c r="Q20" s="33">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="R20" s="34">
         <f t="shared" si="9"/>
-        <v>399.73390048577232</v>
+        <v>400.23336444438911</v>
       </c>
       <c r="T20" s="34">
         <v>7</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="J21" s="32"/>
       <c r="K21" s="36">
-        <v>1250</v>
+        <v>910</v>
       </c>
       <c r="L21" s="35">
         <v>3</v>
@@ -4015,19 +4015,19 @@
       </c>
       <c r="N21" s="35">
         <f t="shared" si="2"/>
-        <v>1475</v>
+        <v>1073.8</v>
       </c>
       <c r="O21" s="37">
         <f t="shared" si="3"/>
-        <v>267.85078275019299</v>
+        <v>194.99536984214049</v>
       </c>
       <c r="P21" s="26"/>
       <c r="Q21" s="36">
-        <v>237</v>
+        <v>310</v>
       </c>
       <c r="R21" s="38">
         <f t="shared" si="9"/>
-        <v>499.63090442918951</v>
+        <v>499.7465741027475</v>
       </c>
       <c r="T21" s="38">
         <v>8</v>
@@ -4082,7 +4082,7 @@
       <c r="T25" s="12"/>
       <c r="U25" s="45"/>
     </row>
-    <row r="26" ht="16.5">
+    <row r="26" ht="15.75">
       <c r="A26" s="14" t="s">
         <v>36</v>
       </c>
@@ -4367,22 +4367,22 @@
         <v>2</v>
       </c>
       <c r="E31" s="24">
-        <v>2.1499999999999999</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="F31" s="24">
         <f t="shared" si="6"/>
-        <v>5.8139534883720936</v>
+        <v>6.0975609756097562</v>
       </c>
       <c r="G31" s="24">
         <v>500</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="7"/>
-        <v>31.130560164733723</v>
+        <v>32.649124075208533</v>
       </c>
       <c r="I31" s="25">
         <f t="shared" si="8"/>
-        <v>1.0197628458498025</v>
+        <v>1.0207468879668051</v>
       </c>
       <c r="J31" s="32"/>
       <c r="K31" s="27">
@@ -4404,11 +4404,11 @@
       </c>
       <c r="P31" s="46"/>
       <c r="Q31" s="27">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R31" s="34">
         <f t="shared" si="9"/>
-        <v>45.481497564211224</v>
+        <v>45.132246402544155</v>
       </c>
       <c r="T31" s="34">
         <v>3</v>
@@ -4488,7 +4488,7 @@
         <v>43</v>
       </c>
       <c r="B33" s="36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="35">
         <v>1</v>
@@ -4497,22 +4497,22 @@
         <v>2</v>
       </c>
       <c r="E33" s="35">
-        <v>2.1499999999999999</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="F33" s="35">
         <f t="shared" si="6"/>
-        <v>5.3488372093023262</v>
+        <v>5.1219512195121952</v>
       </c>
       <c r="G33" s="35">
         <v>500</v>
       </c>
       <c r="H33" s="35">
         <f t="shared" si="7"/>
-        <v>28.640115351555025</v>
+        <v>27.425264223175169</v>
       </c>
       <c r="I33" s="37">
         <f t="shared" si="8"/>
-        <v>1.0181531176006315</v>
+        <v>1.0173697270471465</v>
       </c>
       <c r="J33" s="32"/>
       <c r="K33" s="36">
@@ -4534,11 +4534,11 @@
       </c>
       <c r="P33" s="46"/>
       <c r="Q33" s="36">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="R33" s="38">
         <f t="shared" si="9"/>
-        <v>79.809807922076715</v>
+        <v>72.248471948450771</v>
       </c>
       <c r="T33" s="38">
         <v>4</v>
@@ -5342,7 +5342,7 @@
       <c r="T49" s="12"/>
       <c r="U49" s="45"/>
     </row>
-    <row r="50" ht="16.5">
+    <row r="50" ht="15.75">
       <c r="A50" s="14" t="s">
         <v>56</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>97</v>
       </c>
       <c r="B102" s="33">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C102" s="26">
         <v>1</v>
@@ -7983,16 +7983,16 @@
         <v>4</v>
       </c>
       <c r="E102" s="26">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="F102" s="26">
         <f t="shared" si="18"/>
-        <v>12.427745664739884</v>
+        <v>11.016949152542372</v>
       </c>
       <c r="G102" s="26"/>
       <c r="H102" s="26">
         <f t="shared" si="19"/>
-        <v>66.543821670049297</v>
+        <v>58.989773329105581</v>
       </c>
       <c r="I102" s="31">
         <f t="shared" si="20"/>
@@ -8017,11 +8017,11 @@
       </c>
       <c r="P102" s="26"/>
       <c r="Q102" s="36">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R102" s="38">
         <f t="shared" si="23"/>
-        <v>100.23081753652626</v>
+        <v>99.787578863771273</v>
       </c>
       <c r="T102" s="38">
         <v>3</v>
@@ -9816,22 +9816,22 @@
         <v>2</v>
       </c>
       <c r="E135" s="35">
-        <v>1.5700000000000001</v>
+        <v>1.45</v>
       </c>
       <c r="F135" s="35">
         <f t="shared" si="18"/>
-        <v>5.4140127388535033</v>
+        <v>5.862068965517242</v>
       </c>
       <c r="G135" s="35">
         <v>625</v>
       </c>
       <c r="H135" s="35">
         <f t="shared" si="19"/>
-        <v>28.989094879516369</v>
+        <v>31.388192386786692</v>
       </c>
       <c r="I135" s="37">
         <f t="shared" si="20"/>
-        <v>1.0230790116752646</v>
+        <v>1.0250368188512518</v>
       </c>
       <c r="K135" s="36">
         <v>110</v>
@@ -9851,11 +9851,11 @@
         <v>19.975312611878799</v>
       </c>
       <c r="Q135" s="36">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="R135" s="38">
         <f t="shared" si="23"/>
-        <v>94.912601124643373</v>
+        <v>89.681295409804036</v>
       </c>
       <c r="T135" s="38">
         <v>2</v>
@@ -11578,7 +11578,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3250" id="{00F6008B-00A8-49B3-8FEA-009D00CF0024}">
+          <x14:cfRule type="dataBar" priority="3250" id="{00EB0026-0014-4128-A3A4-0033000B0003}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11588,7 +11588,7 @@
           <xm:sqref>N148:N152 N154:N155 N157:N167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3246" id="{00ED00B0-00BC-4A86-BAB0-004C009700F9}">
+          <x14:cfRule type="dataBar" priority="3246" id="{00A90070-0016-479C-A466-0024002100CC}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11598,7 +11598,7 @@
           <xm:sqref>F148:F152 F154:F155 F157:F167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3242" id="{00CA0023-0093-41BA-AC14-00FA0086000C}">
+          <x14:cfRule type="dataBar" priority="3242" id="{00910037-00E2-4B3C-A090-002400850031}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11608,7 +11608,7 @@
           <xm:sqref>T148:U152 T154:U155 T157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3238" id="{002500CA-003E-4701-A240-00F6004D0003}">
+          <x14:cfRule type="dataBar" priority="3238" id="{00400076-00CB-4C3C-9545-00450025008B}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11618,7 +11618,7 @@
           <xm:sqref>S148:S152 S154:S155 S157:S167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3235" id="{000900B7-00EB-430F-9A8B-005F0067000D}">
+          <x14:cfRule type="dataBar" priority="3235" id="{008B00EA-0033-4EBE-90BF-000D00AA00D6}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11628,7 +11628,7 @@
           <xm:sqref>U148:U152 U154 U157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3230" id="{00CB00F6-0093-48BF-BDC1-00E200030082}">
+          <x14:cfRule type="dataBar" priority="3230" id="{0055009A-00C8-4E24-991E-0057000E0055}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11638,7 +11638,7 @@
           <xm:sqref>T148:T152 T154 T157:T167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3229" id="{0086009D-0023-4D83-8C98-000000F00019}">
+          <x14:cfRule type="dataBar" priority="3229" id="{002C001A-0080-40A1-A671-004800BF004D}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -11650,7 +11650,7 @@
           <xm:sqref>T148:T152 T154 T157:T167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3220" id="{00DF0097-001F-44D1-A71C-005500930070}">
+          <x14:cfRule type="dataBar" priority="3220" id="{00010022-008F-472A-9004-0019005F00A5}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11660,7 +11660,7 @@
           <xm:sqref>F148:F152 F154 F157:F167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3215" id="{0064009F-0056-43E2-9593-009F00F70087}">
+          <x14:cfRule type="dataBar" priority="3215" id="{00B80083-00EA-4163-92DF-0000002F0039}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11670,7 +11670,7 @@
           <xm:sqref>F151:F152 F154 F157:F167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3214" id="{002E00E5-0063-4815-9FAA-006D0082005A}">
+          <x14:cfRule type="dataBar" priority="3214" id="{00F00073-0043-4AA2-B861-00A900DA00F9}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -11682,7 +11682,7 @@
           <xm:sqref>F151:F152 F154 F157:F167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3209" id="{0078005C-009F-4908-8371-000200E50053}">
+          <x14:cfRule type="dataBar" priority="3209" id="{00E100D0-0094-443B-AF99-007900BB0002}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11692,7 +11692,7 @@
           <xm:sqref>N151:N152 N154 N157:N167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3208" id="{005800E3-0082-4FD1-A51D-00EA00B10033}">
+          <x14:cfRule type="dataBar" priority="3208" id="{00B2001F-00E5-4C78-BE46-00C300E900F3}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -11704,7 +11704,7 @@
           <xm:sqref>N151:N152 N154 N157:N167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3205" id="{003300BF-008E-42D9-A182-00EE00830079}">
+          <x14:cfRule type="dataBar" priority="3205" id="{0002002F-002D-4C09-A7B8-00AA001F0014}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11716,17 +11716,17 @@
           <xm:sqref>U151:U152 U154 U157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3202" id="{00E20053-0032-488F-853C-004D002C0010}">
+          <x14:cfRule type="dataBar" priority="3202" id="{001E009A-0093-461C-84E8-002000D80007}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:fillColor rgb="FF638EC6"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>U154 U152 U157:U167</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3199" id="{00280097-0014-41F5-9213-00B800550017}">
+          <xm:sqref>U152 U154 U157:U167</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" priority="3199" id="{009B006B-0092-48A7-8AF7-00C20013004E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11738,7 +11738,7 @@
           <xm:sqref>U152 U154 U157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3196" id="{007D00EF-0010-4E04-BB5A-002C008200C6}">
+          <x14:cfRule type="dataBar" priority="3196" id="{002700A5-00D8-4F13-B671-00B9002E007B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11750,7 +11750,7 @@
           <xm:sqref>U152 U154 U157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3184" id="{007B00A0-0097-456B-88B6-00D800DD0093}">
+          <x14:cfRule type="dataBar" priority="3184" id="{00840003-00CE-4A7C-89A3-009F004F00F7}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11760,7 +11760,7 @@
           <xm:sqref>U151:U152 U154 U157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3181" id="{00360036-00F4-481F-A84D-00A000ED00C4}">
+          <x14:cfRule type="dataBar" priority="3181" id="{000400E1-00C8-49B6-B16B-002E002300A7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11772,7 +11772,7 @@
           <xm:sqref>U151:U152 U154 U157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3178" id="{00C90066-00EC-4403-B1C9-005500EE0049}">
+          <x14:cfRule type="dataBar" priority="3178" id="{00B0001E-00F9-4135-A22B-008E00A300DB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11784,7 +11784,7 @@
           <xm:sqref>U151:U152 U154 U157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3175" id="{003600EF-004F-43A3-9143-00600093006E}">
+          <x14:cfRule type="dataBar" priority="3175" id="{00A60062-0049-42AF-AE3E-00A400D70027}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11794,7 +11794,7 @@
           <xm:sqref>T151:T152 T154 T157:T167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3172" id="{00230013-0042-4E5F-A765-00A200C7002C}">
+          <x14:cfRule type="dataBar" priority="3172" id="{00760099-00A9-45CF-A165-00A600010099}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11806,7 +11806,7 @@
           <xm:sqref>T151:T152 T154 T157:T167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3169" id="{00F10084-00AC-40A8-A0C3-007600B4002F}">
+          <x14:cfRule type="dataBar" priority="3169" id="{006B0087-001B-478F-93FF-003900C700CC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11818,7 +11818,7 @@
           <xm:sqref>T151:T152 T154 T157:T167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3166" id="{00340067-0096-4EC6-9090-003000D9009B}">
+          <x14:cfRule type="dataBar" priority="3166" id="{003600A4-000C-400F-83AD-00EE001500BE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11830,7 +11830,7 @@
           <xm:sqref>S151:S152 S154 S157:S167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3163" id="{00420002-0096-4F16-872F-00A700C70029}">
+          <x14:cfRule type="dataBar" priority="3163" id="{002B0038-00D3-4C92-A650-0071004800E3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11842,33 +11842,21 @@
           <xm:sqref>S151:S152 S154 S157:S167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3158" id="{001700E0-00EE-42E7-B957-00DA00A5005E}">
+          <x14:cfRule type="dataBar" priority="3158" id="{0054001A-00DA-4888-97E9-004000DE00D4}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:fillColor rgb="FF638EC6"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>U150 U148 U152 U154 U157:U167</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3153" id="{009E003B-00EA-4003-AB53-0065005600A2}">
-            <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:fillColor rgb="FF638EC6"/>
-              <x14:negativeFillColor indexed="2"/>
-              <x14:axisColor indexed="64"/>
-            </x14:dataBar>
-          </x14:cfRule>
           <xm:sqref>U148 U150 U152 U154 U157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3148" id="{002B00BE-00A3-4902-B15F-003C006B00C3}">
-            <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:fillColor rgb="FFFFB628"/>
+          <x14:cfRule type="dataBar" priority="3153" id="{002D009C-005E-4C6E-8FF0-00D7005300A1}">
+            <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:fillColor rgb="FF638EC6"/>
               <x14:negativeFillColor indexed="2"/>
               <x14:axisColor indexed="64"/>
             </x14:dataBar>
@@ -11876,17 +11864,29 @@
           <xm:sqref>U148 U150 U152 U154 U157:U167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3143" id="{005900C2-00FA-46FB-AC9E-00F80065006A}">
+          <x14:cfRule type="dataBar" priority="3148" id="{007900B9-00C5-4E96-A016-0021008A0073}">
+            <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:fillColor rgb="FFFFB628"/>
+              <x14:negativeFillColor indexed="2"/>
+              <x14:axisColor indexed="64"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>U148 U150 U152 U154 U157:U167</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" priority="3143" id="{00D100CB-0043-40FD-A3CC-000B002A000E}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:fillColor rgb="FF638EC6"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>T150 T148 T152 T154 T157:T167</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3138" id="{002D009E-00F6-4A8B-830F-0016009D009F}">
+          <xm:sqref>T148 T150 T152 T154 T157:T167</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" priority="3138" id="{008700FE-008E-44E5-81CB-0074000B0021}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11898,7 +11898,7 @@
           <xm:sqref>T148 T150 T152 T154 T157:T167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3133" id="{00B100EE-00B2-4FED-B46D-00770003004D}">
+          <x14:cfRule type="dataBar" priority="3133" id="{00A6007D-0054-4333-8D2E-00B800D500E2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11910,7 +11910,7 @@
           <xm:sqref>T148 T150 T152 T154 T157:T167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3128" id="{0037004B-00F8-4ECD-98FF-003A002A001E}">
+          <x14:cfRule type="dataBar" priority="3128" id="{007200ED-00E2-4264-9179-0029009E00DE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11922,7 +11922,7 @@
           <xm:sqref>S148 S150 S152 S154 S157:S167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3123" id="{00DD00B2-0079-4F3E-B4C2-00B70043005D}">
+          <x14:cfRule type="dataBar" priority="3123" id="{005C00DA-00DD-493B-8995-001200F8000C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11934,7 +11934,7 @@
           <xm:sqref>N145:N148 N150 N152 N154 N157:N167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3118" id="{000C00CE-0002-4EBF-9AC2-006400C90016}">
+          <x14:cfRule type="dataBar" priority="3118" id="{00BF0055-0004-45DD-876F-0006004E00E8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11946,7 +11946,7 @@
           <xm:sqref>F145:F148 F150 F152 F154 F157:F163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3113" id="{001600A4-004A-4DF8-BC19-005C00450006}">
+          <x14:cfRule type="dataBar" priority="3113" id="{003F00B2-008D-4361-9F5E-000F000D00D9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11958,7 +11958,7 @@
           <xm:sqref>S145:S148 S150 S152 S154 S157:S167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3108" id="{00350078-0081-4CD7-BD64-003600DF0074}">
+          <x14:cfRule type="dataBar" priority="3108" id="{00C90001-00A0-46BD-AFBE-00B300DB002B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11970,7 +11970,7 @@
           <xm:sqref>S148 S150 S152 S154 S157:S167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3103" id="{00BF00E0-0040-49A9-9F75-008E002F00C5}">
+          <x14:cfRule type="dataBar" priority="3103" id="{00D9002F-00AC-4FF0-AA35-00D200130098}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11982,7 +11982,7 @@
           <xm:sqref>N148 N150 N152 N154 N157:N167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3098" id="{004D00D5-002F-4E47-866E-006100450009}">
+          <x14:cfRule type="dataBar" priority="3098" id="{00120097-00FC-4539-BA8F-00A7003500FB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11994,7 +11994,7 @@
           <xm:sqref>F150 F148 F152 F154 F157:F167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3079" id="{00F10083-00E5-487C-9F69-004100320075}">
+          <x14:cfRule type="dataBar" priority="3079" id="{005F00A9-00D1-4033-B67D-001E00A60009}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -12004,7 +12004,7 @@
           <xm:sqref>N148:N152 N154 N157:N167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3070" id="{00FF00D1-00AB-483A-A21E-003200B900C4}">
+          <x14:cfRule type="dataBar" priority="3070" id="{00940033-00F0-4DFC-BA99-00EE005C00AC}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -12014,7 +12014,7 @@
           <xm:sqref>S148:S152 S154 S157:S167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3006" id="{00A90043-00E3-419F-9041-0002005F00DA}">
+          <x14:cfRule type="dataBar" priority="3006" id="{00AD00CD-0096-4BB2-B107-006700060003}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12026,7 +12026,7 @@
           <xm:sqref>N157:N167 N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3002" id="{004800BD-0047-4BD3-B715-007200A40028}">
+          <x14:cfRule type="dataBar" priority="3002" id="{00790018-001C-4970-8841-0085007400CC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12038,7 +12038,7 @@
           <xm:sqref>F157:F167 F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2998" id="{00A800E7-0038-46E3-A00A-00B500FE0079}">
+          <x14:cfRule type="dataBar" priority="2998" id="{00B40055-008C-4D07-8B50-00E3003600C3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12050,7 +12050,7 @@
           <xm:sqref>S157:S167 S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2994" id="{009F002B-0015-40C4-8A38-0044001900F1}">
+          <x14:cfRule type="dataBar" priority="2994" id="{00370078-0051-4B34-A7CE-001E004400E8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12062,7 +12062,7 @@
           <xm:sqref>N157:N165 N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2990" id="{003900BC-0065-4A11-8244-0022002E0074}">
+          <x14:cfRule type="dataBar" priority="2990" id="{004100B7-00F8-4E75-9B5E-002B00DF0057}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12074,7 +12074,7 @@
           <xm:sqref>F157:F165 F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2986" id="{00EF0025-0065-4F76-B5CF-00A8002E0009}">
+          <x14:cfRule type="dataBar" priority="2986" id="{001C0055-005F-4359-A61D-0047003D006C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12086,7 +12086,7 @@
           <xm:sqref>S157:S165 S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2946" id="{000500EF-00CC-4713-86FE-00E500DB0063}">
+          <x14:cfRule type="dataBar" priority="2946" id="{00AC0051-0068-49C4-8186-001300380095}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12098,7 +12098,7 @@
           <xm:sqref>N157:N158 N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2942" id="{00BC0049-005C-4148-8750-0031003300E6}">
+          <x14:cfRule type="dataBar" priority="2942" id="{00180018-0008-49C0-8054-0090006F00AC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12110,7 +12110,7 @@
           <xm:sqref>F157:F158 F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2938" id="{00DB00D4-008C-42D1-875B-00CF006C008A}">
+          <x14:cfRule type="dataBar" priority="2938" id="{00A8009E-00D9-423C-B551-0022004300E7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12122,7 +12122,7 @@
           <xm:sqref>S157:S158 S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2666" id="{00460020-00DD-40E2-8368-00B8007D00BA}">
+          <x14:cfRule type="dataBar" priority="2666" id="{00DA008C-00DA-4E44-917C-008500E50016}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -12132,7 +12132,7 @@
           <xm:sqref>N157:N167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2597" id="{00B800D1-007C-46D2-9491-008D000500B8}">
+          <x14:cfRule type="dataBar" priority="2597" id="{00B40084-00C8-4A08-AFE9-0077009F0013}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12144,7 +12144,7 @@
           <xm:sqref>N157:N164 N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2594" id="{00E900B3-00AC-415E-A830-0062000200AF}">
+          <x14:cfRule type="dataBar" priority="2594" id="{0004000F-00AD-471D-9F54-009500140037}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12156,7 +12156,7 @@
           <xm:sqref>F157:F164 F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2591" id="{00C900C4-0059-4C0E-A4FC-008400820018}">
+          <x14:cfRule type="dataBar" priority="2591" id="{002100D5-0000-400B-9F72-0061003100F0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12168,7 +12168,7 @@
           <xm:sqref>S157:S164 S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2588" id="{001200FE-0019-495A-B018-00F9007C00D6}">
+          <x14:cfRule type="dataBar" priority="2588" id="{00470004-001E-4E34-871F-0091005A00E5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12180,7 +12180,7 @@
           <xm:sqref>N157:N163 N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2585" id="{00B600A9-00AF-4C07-9FF4-00DE008B001F}">
+          <x14:cfRule type="dataBar" priority="2585" id="{007A007A-00A3-4A43-866C-001F007B00BD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12192,7 +12192,7 @@
           <xm:sqref>F157:F163 F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2582" id="{00CF00F9-0060-41B7-A364-00AD000B00B1}">
+          <x14:cfRule type="dataBar" priority="2582" id="{00AC00D9-0081-40BC-ABF7-0071000F00B7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12204,7 +12204,7 @@
           <xm:sqref>S157:S163 S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2579" id="{00AC00BA-007D-4FD6-9A8D-00B9007D00E3}">
+          <x14:cfRule type="dataBar" priority="2579" id="{002000DF-00AE-4B3A-A79A-00D9003A00B2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12216,7 +12216,7 @@
           <xm:sqref>N157:N162 N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2576" id="{00EC0066-0063-41CD-BAA3-006500B400FA}">
+          <x14:cfRule type="dataBar" priority="2576" id="{004C0084-004E-498E-89AD-004A00700008}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12228,7 +12228,7 @@
           <xm:sqref>F157:F162 F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2573" id="{00A600AD-0086-41F4-8A0D-00DD004500EF}">
+          <x14:cfRule type="dataBar" priority="2573" id="{00FD0086-008B-4146-AFC8-001100A300C9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12240,7 +12240,7 @@
           <xm:sqref>S157:S162 S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2561" id="{009E0019-00AF-43BB-BE03-00B6005A0092}">
+          <x14:cfRule type="dataBar" priority="2561" id="{002B0003-00AB-4678-804E-00D200F7009A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12252,7 +12252,7 @@
           <xm:sqref>N154 N157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2558" id="{004900AF-004A-434F-80C2-008F00D2002C}">
+          <x14:cfRule type="dataBar" priority="2558" id="{00920040-00C7-418A-9C01-00E800DC00E5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12264,7 +12264,7 @@
           <xm:sqref>F157 F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2555" id="{006700B8-0004-4578-80C7-009D001400FE}">
+          <x14:cfRule type="dataBar" priority="2555" id="{00A10012-0052-45D8-822D-00CE008A0038}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12276,7 +12276,7 @@
           <xm:sqref>S157 S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1515" id="{00AE00E3-000A-421C-81AA-005D00950049}">
+          <x14:cfRule type="dataBar" priority="1515" id="{004A0039-0033-48AF-AB5F-00AD002400F5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12288,7 +12288,7 @@
           <xm:sqref>F4:F8 F10:F22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1512" id="{007500BE-0010-4148-A884-00F700990065}">
+          <x14:cfRule type="dataBar" priority="1512" id="{009B00CE-00A3-47B6-A08C-00A0000B002A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12300,7 +12300,7 @@
           <xm:sqref>N10:N22 N4:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1371" id="{0095007B-0027-4397-9E51-0078004D00E2}">
+          <x14:cfRule type="dataBar" priority="1371" id="{00B6009B-00FB-427E-AB71-00BB00B6007F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12312,7 +12312,7 @@
           <xm:sqref>N18 N21 N15 N12 N25:N46 N111:N117 N6 N121:N128</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1362" id="{0066001B-0019-401D-86B9-00610019003C}">
+          <x14:cfRule type="dataBar" priority="1362" id="{00B200FE-008F-4EBC-9276-007C006A0085}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12324,7 +12324,7 @@
           <xm:sqref>F18 F21 F15 F12 F46 F111:F117 F6 F25:F37 F121:F128</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1351" id="{00E80078-0087-4483-959B-00A3007800AE}">
+          <x14:cfRule type="dataBar" priority="1351" id="{000900AC-0026-43DE-B1F6-00ED00AB00B3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12336,7 +12336,7 @@
           <xm:sqref>R25:R46 R111:R117 R121:R128</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1326" id="{006300DE-00C6-4A80-8DBF-000800700020}">
+          <x14:cfRule type="dataBar" priority="1326" id="{00700083-007A-46F0-A9BE-00AC004D0031}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12348,7 +12348,7 @@
           <xm:sqref>F38:F45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1325" id="{00B90040-0010-4F7D-A56E-009500560013}">
+          <x14:cfRule type="dataBar" priority="1325" id="{00BF0064-0015-473A-9D6C-0079003E0030}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12360,7 +12360,7 @@
           <xm:sqref>F40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1322" id="{006900AC-0088-43BA-8B1D-006D00A10029}">
+          <x14:cfRule type="dataBar" priority="1322" id="{002300ED-001B-4D70-B3EA-001D00E1007F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12372,7 +12372,7 @@
           <xm:sqref>R28:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1318" id="{00F7006C-00AC-41D7-B762-003300500001}">
+          <x14:cfRule type="dataBar" priority="1318" id="{003300AE-0032-4D01-AA81-008500DB00C7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12384,7 +12384,7 @@
           <xm:sqref>N49:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1317" id="{004D00FF-003E-403A-B1CC-00600074001C}">
+          <x14:cfRule type="dataBar" priority="1317" id="{000500DF-009D-44D4-BCCD-001A005A007F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12396,7 +12396,7 @@
           <xm:sqref>F49:F61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1316" id="{00CE00CB-0039-44A5-A638-00F800940094}">
+          <x14:cfRule type="dataBar" priority="1316" id="{00ED00D5-0018-436E-AF22-00B3005900DC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12408,7 +12408,7 @@
           <xm:sqref>R49:R69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1315" id="{00C200FE-00C1-46C1-B874-0015003900DA}">
+          <x14:cfRule type="dataBar" priority="1315" id="{00D5008C-0016-4E0E-9806-002800F200F9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12420,7 +12420,7 @@
           <xm:sqref>F62:F69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1314" id="{00F900E0-00B2-40DD-B64A-004600310011}">
+          <x14:cfRule type="dataBar" priority="1314" id="{00C20025-0029-4843-AB50-007A001100F1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12432,7 +12432,7 @@
           <xm:sqref>F64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1311" id="{001300AE-0095-4D7F-A82B-009600400026}">
+          <x14:cfRule type="dataBar" priority="1311" id="{00B9005D-0011-47DD-B9F3-003200400083}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12444,7 +12444,7 @@
           <xm:sqref>R52:R69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1310" id="{00BA009D-00F1-48DF-B8C9-002500A6002A}">
+          <x14:cfRule type="dataBar" priority="1310" id="{002100C5-00A5-4328-BBFE-00CF0010006A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12456,7 +12456,7 @@
           <xm:sqref>N73:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1309" id="{008500AE-004D-4274-B1C8-004F00B2002A}">
+          <x14:cfRule type="dataBar" priority="1309" id="{00F5007A-0016-4804-9E22-008A00EE0097}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12468,7 +12468,7 @@
           <xm:sqref>F73:F85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1308" id="{00CD0055-004E-4BA7-8EFB-006E00F4007E}">
+          <x14:cfRule type="dataBar" priority="1308" id="{00A1002E-000D-4E1E-8780-00E700F50028}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12480,7 +12480,7 @@
           <xm:sqref>R73:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1307" id="{00AB0021-00DC-4D81-B037-002E00EB008E}">
+          <x14:cfRule type="dataBar" priority="1307" id="{00DC00E4-0056-4A71-9E36-00F90060004D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12492,7 +12492,7 @@
           <xm:sqref>F86:F93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1306" id="{0061001C-0017-4C37-8D18-007A00460082}">
+          <x14:cfRule type="dataBar" priority="1306" id="{00F000B1-007A-4C58-A54B-00B400B30067}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12504,7 +12504,7 @@
           <xm:sqref>F88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1303" id="{003600C3-00FB-44B8-868D-004D006B00CA}">
+          <x14:cfRule type="dataBar" priority="1303" id="{007A0061-0010-4252-A145-0095003B0068}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12516,7 +12516,7 @@
           <xm:sqref>R76:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1301" id="{000E0064-00E8-477F-88CF-0092003100EF}">
+          <x14:cfRule type="dataBar" priority="1301" id="{00A200C4-0013-4F55-B59F-00E500480005}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12528,7 +12528,7 @@
           <xm:sqref>R2:R8 R10:R21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1300" id="{00F000FF-003C-486E-9FEA-001B009200D3}">
+          <x14:cfRule type="dataBar" priority="1300" id="{007B00C1-00B1-4914-B147-00CD00BE0073}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12540,7 +12540,7 @@
           <xm:sqref>F110:F117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1299" id="{005B001C-006E-4D91-A072-005200790083}">
+          <x14:cfRule type="dataBar" priority="1299" id="{005700AD-00BC-41EF-B002-000B00750064}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12552,7 +12552,7 @@
           <xm:sqref>F112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1296" id="{005300C8-005C-4C64-91AD-0099006900D9}">
+          <x14:cfRule type="dataBar" priority="1296" id="{005700C3-0024-4152-A63F-00C3004200F7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12564,7 +12564,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1295" id="{0016001B-004E-4142-8283-00EA005A008E}">
+          <x14:cfRule type="dataBar" priority="1295" id="{00300065-003F-4FBC-9BEA-007A00A9006D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12576,7 +12576,7 @@
           <xm:sqref>R97:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1294" id="{00F6003E-006A-4173-A578-006A003700E0}">
+          <x14:cfRule type="dataBar" priority="1294" id="{0047008D-00D6-45E3-986A-0015003200FD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12588,7 +12588,7 @@
           <xm:sqref>F97:F109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1293" id="{00D900CF-00CD-4CFF-8705-00B1009100E3}">
+          <x14:cfRule type="dataBar" priority="1293" id="{004B0092-00B1-4754-BAEA-00040098004B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12600,7 +12600,7 @@
           <xm:sqref>N97:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1288" id="{005300ED-0032-48C5-A7C1-006A00680036}">
+          <x14:cfRule type="dataBar" priority="1288" id="{00E7009E-0058-407A-94EA-0095005600F4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12612,7 +12612,7 @@
           <xm:sqref>R28:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1287" id="{000500E5-007C-4B25-B0A1-006000D7008D}">
+          <x14:cfRule type="dataBar" priority="1287" id="{005400EE-000F-4B57-B96F-00AA00180001}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12624,7 +12624,7 @@
           <xm:sqref>R28:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1286" id="{009D001D-0092-4EBA-9208-0053005000B3}">
+          <x14:cfRule type="dataBar" priority="1286" id="{0024006B-00F3-46D9-BF7F-006600030041}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12636,7 +12636,7 @@
           <xm:sqref>R52:R69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1285" id="{00D100FB-00E1-409B-B50E-001200CE0023}">
+          <x14:cfRule type="dataBar" priority="1285" id="{0015002A-00F2-4D21-93FC-005F0070008B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12648,7 +12648,7 @@
           <xm:sqref>R52:R69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1284" id="{00250062-0058-4F98-8733-006B0066004A}">
+          <x14:cfRule type="dataBar" priority="1284" id="{001900AA-00FA-4A18-996B-005C00BF0048}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12660,7 +12660,7 @@
           <xm:sqref>R52:R69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1283" id="{00F1005B-00DA-433E-8A4F-00F500C20030}">
+          <x14:cfRule type="dataBar" priority="1283" id="{00A400BE-00C5-4163-BF0F-00D700540012}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12672,7 +12672,7 @@
           <xm:sqref>R52:R69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1282" id="{00630082-0035-4440-A359-001800AE002A}">
+          <x14:cfRule type="dataBar" priority="1282" id="{00A200C6-0033-4F17-B5A4-00C8002400C8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12684,7 +12684,7 @@
           <xm:sqref>R76:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1281" id="{00BF006F-0081-4B75-A003-008600940003}">
+          <x14:cfRule type="dataBar" priority="1281" id="{005F00DA-00AC-4117-B0FB-0081002500A3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12696,7 +12696,7 @@
           <xm:sqref>R76:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1280" id="{006200A5-0030-4832-ACAF-00CE00DA00E7}">
+          <x14:cfRule type="dataBar" priority="1280" id="{0043009D-00CC-4330-A085-00220036006B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12708,7 +12708,7 @@
           <xm:sqref>R76:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1279" id="{009F0023-0013-4A75-B0A0-00B8009A00F3}">
+          <x14:cfRule type="dataBar" priority="1279" id="{00020027-006B-443A-B87B-00AD00740020}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12720,7 +12720,7 @@
           <xm:sqref>R76:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1278" id="{00730065-0006-4470-B89A-0084003B00C1}">
+          <x14:cfRule type="dataBar" priority="1278" id="{00C6004A-006A-4D22-900B-00A400EF0090}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12732,7 +12732,7 @@
           <xm:sqref>R76:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1277" id="{005400CF-0080-486D-A44B-001100EB009A}">
+          <x14:cfRule type="dataBar" priority="1277" id="{00E30006-0065-4077-AA9C-008B00CB008F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12744,7 +12744,7 @@
           <xm:sqref>R76:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1276" id="{00C100EF-007A-4ACE-995E-00D4009D005A}">
+          <x14:cfRule type="dataBar" priority="1276" id="{0014000F-0003-4DF4-BB8E-00660028009C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12756,7 +12756,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1275" id="{007B0029-0015-48BA-AE6F-00F200A70014}">
+          <x14:cfRule type="dataBar" priority="1275" id="{00B800B4-00BE-4128-93DE-009700BC0078}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12768,7 +12768,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1274" id="{004D0033-00E3-49B3-910C-007D00AD0050}">
+          <x14:cfRule type="dataBar" priority="1274" id="{00520096-00A9-48C2-A264-005F005800AD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12780,7 +12780,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1273" id="{001E0090-002B-44C4-8209-005C004400CE}">
+          <x14:cfRule type="dataBar" priority="1273" id="{002200CF-00FF-4A86-B4D6-00F900210075}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12792,7 +12792,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1272" id="{00F30058-009A-43DE-831A-00AB006400C9}">
+          <x14:cfRule type="dataBar" priority="1272" id="{00B10031-00FE-4439-A501-00EF00360028}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12804,7 +12804,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1271" id="{00B00076-00A5-4060-A1B2-007C004A0041}">
+          <x14:cfRule type="dataBar" priority="1271" id="{0034009B-0018-4C87-942E-006300C800BB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12816,7 +12816,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1270" id="{00A50052-00A4-45D7-BA2F-007100F40052}">
+          <x14:cfRule type="dataBar" priority="1270" id="{00190085-009A-42A4-8E54-000400FA0070}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12828,7 +12828,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1269" id="{00A300CC-0071-47DA-A538-00E100AF00E9}">
+          <x14:cfRule type="dataBar" priority="1269" id="{00A50064-00D5-4B7D-B904-0005007E00BB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12840,7 +12840,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1268" id="{005200A7-0092-4411-BB60-003A007700D5}">
+          <x14:cfRule type="dataBar" priority="1268" id="{000D00F6-00F3-4D52-A503-00C20053000B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12852,7 +12852,7 @@
           <xm:sqref>R28:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1266" id="{001B00ED-00C3-4CC9-9827-004D002300DD}">
+          <x14:cfRule type="dataBar" priority="1266" id="{00E20077-008B-4C71-96AB-00F0005900BB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12864,7 +12864,7 @@
           <xm:sqref>R52:R69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1264" id="{00EC0034-0073-4D03-8704-0021005E00B7}">
+          <x14:cfRule type="dataBar" priority="1264" id="{00D10042-009A-4E16-AA57-0015007B0085}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12876,7 +12876,7 @@
           <xm:sqref>R76:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1262" id="{005B00A0-0065-4D86-B3CE-009900150022}">
+          <x14:cfRule type="dataBar" priority="1262" id="{0028003B-0078-411D-945B-001300480018}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12888,7 +12888,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1239" id="{004A003F-00B6-446D-B241-000F00DB00DC}">
+          <x14:cfRule type="dataBar" priority="1239" id="{00AB002A-0062-48F0-B956-006C00FD00CB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12900,7 +12900,7 @@
           <xm:sqref>F44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1238" id="{000700BE-0075-4D50-B6A7-0087008C00DA}">
+          <x14:cfRule type="dataBar" priority="1238" id="{002B000F-0065-46A5-AC89-00EE001A00BC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12912,7 +12912,7 @@
           <xm:sqref>F35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1237" id="{007500C2-00CA-4353-ACDE-009600DF00D3}">
+          <x14:cfRule type="dataBar" priority="1237" id="{00D600C8-0097-49BE-8DA8-0054002400E0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12924,7 +12924,7 @@
           <xm:sqref>F35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1236" id="{009E00C0-0013-45C1-8483-0072005C00DF}">
+          <x14:cfRule type="dataBar" priority="1236" id="{001F0024-00A7-4753-9877-006C00DB00DF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12936,7 +12936,7 @@
           <xm:sqref>N35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1235" id="{006000A6-00CB-4686-8464-008B00D000EE}">
+          <x14:cfRule type="dataBar" priority="1235" id="{00AF003F-0067-40F3-B3A7-003C009000A4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12948,7 +12948,7 @@
           <xm:sqref>R35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1234" id="{007600AF-00C2-4FA2-8BDC-0003002D0057}">
+          <x14:cfRule type="dataBar" priority="1234" id="{00730052-00EC-4B92-970A-00DC002D0081}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12960,7 +12960,7 @@
           <xm:sqref>R35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1233" id="{00EE006A-000F-4F0F-ADA7-004C004500A1}">
+          <x14:cfRule type="dataBar" priority="1233" id="{001C00A5-0031-4E3D-B6BD-006900A60010}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12972,7 +12972,7 @@
           <xm:sqref>R35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1232" id="{00DD00CA-0013-41EF-8269-005300DC006B}">
+          <x14:cfRule type="dataBar" priority="1232" id="{005C007F-003C-49B8-AD93-00180011000D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12984,7 +12984,7 @@
           <xm:sqref>R35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1231" id="{007800CA-00DF-4121-B8D6-0039005600E3}">
+          <x14:cfRule type="dataBar" priority="1231" id="{00A4006F-0030-4623-8DA9-00F000BC00CD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12996,7 +12996,7 @@
           <xm:sqref>R35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1230" id="{00310025-00CF-4F90-A47C-002000CE000C}">
+          <x14:cfRule type="dataBar" priority="1230" id="{00480063-001D-4437-B358-00CB004B005D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13008,7 +13008,7 @@
           <xm:sqref>F120:F122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1229" id="{00EB0011-0090-4680-ACED-002600710014}">
+          <x14:cfRule type="dataBar" priority="1229" id="{000B001E-00BC-46FE-9FBD-001700CC00C4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13020,7 +13020,7 @@
           <xm:sqref>F120</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1228" id="{005B0039-00E2-4177-BCC4-00180064006C}">
+          <x14:cfRule type="dataBar" priority="1228" id="{004000E3-00EB-4E73-B927-006B003600CE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13032,7 +13032,7 @@
           <xm:sqref>F120:F122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1227" id="{005E00D2-008F-4C51-9A98-00C500720038}">
+          <x14:cfRule type="dataBar" priority="1227" id="{0061006E-006F-4103-9AFA-000000D300A7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13044,7 +13044,7 @@
           <xm:sqref>N120:N122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1226" id="{00D5001F-0032-4CC1-A495-000D00F2005D}">
+          <x14:cfRule type="dataBar" priority="1226" id="{001B003A-00B4-4A57-9348-0051003A00BA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13056,7 +13056,7 @@
           <xm:sqref>R120:R122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1225" id="{0041000F-0009-4FD5-A275-00F8004500A3}">
+          <x14:cfRule type="dataBar" priority="1225" id="{00DB0089-003B-430D-A1CD-001D00510080}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13068,7 +13068,7 @@
           <xm:sqref>R120:R122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1224" id="{0042003F-00D7-430A-84F9-009D0027006D}">
+          <x14:cfRule type="dataBar" priority="1224" id="{00870024-0045-42E0-8B8D-006200F50071}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13080,7 +13080,7 @@
           <xm:sqref>N120:N122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1223" id="{00F100F9-006E-4C94-91E3-009C00040049}">
+          <x14:cfRule type="dataBar" priority="1223" id="{004E007D-00BF-4693-BCFC-005100240018}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13092,7 +13092,7 @@
           <xm:sqref>R120:R122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1222" id="{00DB00F6-00FE-4538-AB9A-00DF00060060}">
+          <x14:cfRule type="dataBar" priority="1222" id="{0002006C-007A-4182-92CA-004000CE00F9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13104,7 +13104,7 @@
           <xm:sqref>R120:R122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1221" id="{00640059-000F-4DF7-B681-00FF00EE0043}">
+          <x14:cfRule type="dataBar" priority="1221" id="{003600B4-000A-4CC4-A15A-0081008900CB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13116,7 +13116,7 @@
           <xm:sqref>R120:R122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1220" id="{00170083-0088-4BCE-B866-004800F70036}">
+          <x14:cfRule type="dataBar" priority="1220" id="{00730066-003F-465B-93CB-001A001600FF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13128,7 +13128,7 @@
           <xm:sqref>R120:R122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1219" id="{00ED0012-00AB-478D-8226-00B2001F008C}">
+          <x14:cfRule type="dataBar" priority="1219" id="{00700045-000C-4577-B033-008F00B70063}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13140,7 +13140,7 @@
           <xm:sqref>F41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1218" id="{003200C5-0004-46EF-80F7-000E00F100B1}">
+          <x14:cfRule type="dataBar" priority="1218" id="{00CA005F-002E-45FF-BCB2-00C1008500DA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13152,7 +13152,7 @@
           <xm:sqref>F43:F45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1217" id="{000A004D-00A3-46D3-BF09-004A00C400F2}">
+          <x14:cfRule type="dataBar" priority="1217" id="{00EA00B2-0056-4DEA-9179-00A200E000B7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13164,7 +13164,7 @@
           <xm:sqref>F43</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1216" id="{00AA0080-00CD-481D-8F84-004A0095009A}">
+          <x14:cfRule type="dataBar" priority="1216" id="{006F003B-0030-4B0B-92F3-00C900CC006C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13176,7 +13176,7 @@
           <xm:sqref>F43:F45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1215" id="{008F0066-00DC-42DE-B5ED-00CA003200EC}">
+          <x14:cfRule type="dataBar" priority="1215" id="{00B100CF-00AB-47D7-ABC6-006600CA00E7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13188,7 +13188,7 @@
           <xm:sqref>N43:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1214" id="{006A00EE-003E-4478-958A-0079007400CD}">
+          <x14:cfRule type="dataBar" priority="1214" id="{007600F9-006D-4DBE-AD25-000E00900030}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13200,7 +13200,7 @@
           <xm:sqref>R43:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1213" id="{007600E0-00A0-43DC-AFBF-005300380002}">
+          <x14:cfRule type="dataBar" priority="1213" id="{005E0021-00A4-46F2-894A-00F2009B004D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13212,7 +13212,7 @@
           <xm:sqref>R43:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1212" id="{00E400FD-005F-40F8-9E26-00DF002A0036}">
+          <x14:cfRule type="dataBar" priority="1212" id="{000200EB-0061-421B-8A38-002600EB0070}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13224,7 +13224,7 @@
           <xm:sqref>N43:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1211" id="{007200FF-00C4-4DA4-B9CD-005E00C80091}">
+          <x14:cfRule type="dataBar" priority="1211" id="{002C00B4-0030-46FC-85F6-00610051002B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13236,7 +13236,7 @@
           <xm:sqref>R43:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1210" id="{00B8001C-001D-4DB6-9171-002E00780039}">
+          <x14:cfRule type="dataBar" priority="1210" id="{007C00F5-0054-4E2F-9E5C-005B00C200C0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13248,7 +13248,7 @@
           <xm:sqref>R43:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1209" id="{004600A8-006E-4410-8E5C-008E006F0055}">
+          <x14:cfRule type="dataBar" priority="1209" id="{00FB0040-00D5-468B-AA64-00B300E700EF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13260,7 +13260,7 @@
           <xm:sqref>R43:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1208" id="{00770075-0097-4AE6-AE76-009900870099}">
+          <x14:cfRule type="dataBar" priority="1208" id="{00F200DD-0062-4DC7-8957-0077006600C0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13272,7 +13272,7 @@
           <xm:sqref>R43:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1207" id="{00D10075-00E6-4198-8883-00E700D3005F}">
+          <x14:cfRule type="dataBar" priority="1207" id="{002F00DB-00A9-426E-A6E5-00F5003E00B3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13284,7 +13284,7 @@
           <xm:sqref>R120:R122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1206" id="{001600CC-009E-48C1-AC71-008200A4005E}">
+          <x14:cfRule type="dataBar" priority="1206" id="{007A0016-00A3-428A-A1C1-00AE0036006B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13296,7 +13296,7 @@
           <xm:sqref>F120:F122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1205" id="{00620064-00F0-4EC9-B087-0048005B000E}">
+          <x14:cfRule type="dataBar" priority="1205" id="{005E0010-009B-439E-A325-005B00C9008A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13308,7 +13308,7 @@
           <xm:sqref>N120:N122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1195" id="{00F300D4-0069-4594-B9BF-00F300FD0077}">
+          <x14:cfRule type="dataBar" priority="1195" id="{009E00BB-0017-4BEA-B426-003900880001}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13320,7 +13320,7 @@
           <xm:sqref>F40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1194" id="{00FF00A5-006C-4CA1-8428-00F700BB003C}">
+          <x14:cfRule type="dataBar" priority="1194" id="{00C400F3-0029-4159-8729-004D00B00055}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13332,7 +13332,7 @@
           <xm:sqref>F30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1193" id="{00D400E8-00E0-44C6-9096-001300280010}">
+          <x14:cfRule type="dataBar" priority="1193" id="{00CE0064-0074-4244-A576-005E00A1005F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13344,7 +13344,7 @@
           <xm:sqref>F30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1192" id="{00970067-0056-4020-B239-00F20030003B}">
+          <x14:cfRule type="dataBar" priority="1192" id="{005C003A-00F3-4D5B-86FF-00E300BF003D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13356,7 +13356,7 @@
           <xm:sqref>N30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1191" id="{000000DC-00C8-41C3-92D3-00F4005A0054}">
+          <x14:cfRule type="dataBar" priority="1191" id="{00E00004-00E0-448B-80C7-00250074007B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13368,7 +13368,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1190" id="{00500025-007A-4C3F-AD71-00D400D30084}">
+          <x14:cfRule type="dataBar" priority="1190" id="{00DA00AD-0097-4B7A-BD94-00A400510090}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13380,7 +13380,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1189" id="{0053003D-0009-4A18-A732-0021003800A2}">
+          <x14:cfRule type="dataBar" priority="1189" id="{00BC004A-0028-427F-A8D6-00C4000B0038}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13392,7 +13392,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1188" id="{00DA00F0-00BF-4686-8C4F-0058002F0039}">
+          <x14:cfRule type="dataBar" priority="1188" id="{009C009F-00D3-4F21-A672-0098002D00E7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13404,7 +13404,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1187" id="{003100DD-009E-45AD-988D-00C200E40019}">
+          <x14:cfRule type="dataBar" priority="1187" id="{003400B2-0006-4BA4-BC93-000200C40047}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13416,7 +13416,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1186" id="{00CD0001-007B-4E2B-9045-005600B10071}">
+          <x14:cfRule type="dataBar" priority="1186" id="{002700AC-00CA-4CEE-A923-001D00570058}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13428,7 +13428,7 @@
           <xm:sqref>F30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1185" id="{00650020-0073-4E2C-ADEC-0036002200B4}">
+          <x14:cfRule type="dataBar" priority="1185" id="{00800010-00EE-4498-A2F1-00A3007000D5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13440,7 +13440,7 @@
           <xm:sqref>F30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1184" id="{00500002-00AF-4437-B6D5-00BF007800A2}">
+          <x14:cfRule type="dataBar" priority="1184" id="{00C300D9-0061-477C-BB67-00C200A9001B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13452,7 +13452,7 @@
           <xm:sqref>F30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1183" id="{00D50072-000A-4063-A833-002D00C50094}">
+          <x14:cfRule type="dataBar" priority="1183" id="{003A00FD-0047-4DE2-97A1-009500DB0025}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13464,7 +13464,7 @@
           <xm:sqref>N30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1182" id="{00F800B5-0087-4B44-B4EC-008600C800BC}">
+          <x14:cfRule type="dataBar" priority="1182" id="{00B900B4-00B9-4BE4-80AE-000C001A009E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13476,7 +13476,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1181" id="{0000003B-00E4-4A5E-85CB-00C400EB00A9}">
+          <x14:cfRule type="dataBar" priority="1181" id="{00610042-001E-4345-82EB-000D00570029}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13488,7 +13488,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1180" id="{003D00E4-002B-42A9-B770-002900FA005C}">
+          <x14:cfRule type="dataBar" priority="1180" id="{008B0006-0076-4966-A995-009D000400C7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13500,7 +13500,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1179" id="{00D80029-00F0-4F1C-91EB-007E001100F0}">
+          <x14:cfRule type="dataBar" priority="1179" id="{0081006E-0052-44E2-98D1-0055009B0052}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13512,7 +13512,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1178" id="{00DF00F5-0074-4736-B590-00BF00AF00B9}">
+          <x14:cfRule type="dataBar" priority="1178" id="{005D000B-00C2-4333-B0A1-000E007A006D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13524,7 +13524,7 @@
           <xm:sqref>R30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1170" id="{00FA00BE-00F0-429E-884D-00B500B9005F}">
+          <x14:cfRule type="dataBar" priority="1170" id="{00FD00C0-0061-4B36-8635-001F00180019}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13536,7 +13536,7 @@
           <xm:sqref>F37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1169" id="{000300D1-0072-4212-9B2A-008E00E700EA}">
+          <x14:cfRule type="dataBar" priority="1169" id="{00260057-0046-42D4-88F0-0040005D0065}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13548,7 +13548,7 @@
           <xm:sqref>F37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1168" id="{00F90077-0080-4940-A722-0057004F0083}">
+          <x14:cfRule type="dataBar" priority="1168" id="{006B0045-00C8-49FE-865E-005A00AC00E1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13560,7 +13560,7 @@
           <xm:sqref>N37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1167" id="{000B0044-00EB-44AB-A293-00F60037002F}">
+          <x14:cfRule type="dataBar" priority="1167" id="{002E00D3-00C8-4B15-BDEE-00BD00530042}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13572,7 +13572,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1166" id="{00D3003D-0086-45E9-A492-00C800F900A4}">
+          <x14:cfRule type="dataBar" priority="1166" id="{00B80014-004D-4B53-BAC1-008D00F200E0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13584,7 +13584,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1165" id="{00C00083-0038-453D-9358-006700CB006D}">
+          <x14:cfRule type="dataBar" priority="1165" id="{007D00A5-00DB-429B-82BF-0084005500AB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13596,7 +13596,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1164" id="{008900C0-00D7-4D5A-82C6-006000DA0087}">
+          <x14:cfRule type="dataBar" priority="1164" id="{000900F1-0086-45C7-92AA-004100FF0087}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13608,7 +13608,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1163" id="{004600C5-0032-4CA1-BB38-00EE00B6000E}">
+          <x14:cfRule type="dataBar" priority="1163" id="{0056001C-0052-4376-B9C3-007F00AE00D9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13620,7 +13620,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1162" id="{008100E9-00C5-4714-BC1C-0088008D002C}">
+          <x14:cfRule type="dataBar" priority="1162" id="{00A20050-0082-4CF7-B174-006D00AA0044}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13632,7 +13632,7 @@
           <xm:sqref>F37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1161" id="{000F008E-0084-4488-8573-000100500090}">
+          <x14:cfRule type="dataBar" priority="1161" id="{003600EF-00C6-42AF-B1C9-002100D400D7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13644,7 +13644,7 @@
           <xm:sqref>F37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1160" id="{00D40041-0097-48C5-8A11-00D700EE005E}">
+          <x14:cfRule type="dataBar" priority="1160" id="{008F0096-00AC-4FB6-857F-00BB003000C5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13656,7 +13656,7 @@
           <xm:sqref>F37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1159" id="{008E0035-0053-4D62-B9CA-008E002F004E}">
+          <x14:cfRule type="dataBar" priority="1159" id="{00AC0027-009A-4168-A143-007D0015005A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13668,7 +13668,7 @@
           <xm:sqref>N37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1158" id="{00140076-008C-4383-9616-00A300BE00E0}">
+          <x14:cfRule type="dataBar" priority="1158" id="{00ED00DE-0094-4116-9BF6-004400940044}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13680,7 +13680,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1157" id="{005A0074-006F-48FC-A524-00E1007700DC}">
+          <x14:cfRule type="dataBar" priority="1157" id="{008B004D-004F-44C6-8C58-006000FF0068}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13692,7 +13692,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1156" id="{003000F7-0054-49E2-BACF-0013004B005D}">
+          <x14:cfRule type="dataBar" priority="1156" id="{000F00C6-00AE-44B5-8592-001800080080}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13704,7 +13704,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1155" id="{00B80074-0055-40D8-A8AC-002000850084}">
+          <x14:cfRule type="dataBar" priority="1155" id="{002100D8-0007-48DD-81E5-00E0004300C3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13716,7 +13716,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1154" id="{008000AB-0023-40A4-8879-00AD00170013}">
+          <x14:cfRule type="dataBar" priority="1154" id="{0018009F-003B-41B0-80B3-005D001C009B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13728,7 +13728,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1153" id="{005900F1-0059-4DFC-8271-00E5008C009A}">
+          <x14:cfRule type="dataBar" priority="1153" id="{00CF008C-007C-4E4F-8C3E-002F00FF003A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13740,7 +13740,7 @@
           <xm:sqref>F37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1152" id="{00DC00B7-0073-4E58-A700-007C000400A4}">
+          <x14:cfRule type="dataBar" priority="1152" id="{00150049-00CB-4E52-88A1-000500A40084}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13752,7 +13752,7 @@
           <xm:sqref>N37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1151" id="{00400089-0036-472C-A0D9-00C200D700F8}">
+          <x14:cfRule type="dataBar" priority="1151" id="{00CB000E-0019-4730-8029-00410029000F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13764,7 +13764,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1150" id="{00F30072-0082-4359-850A-00D70036004E}">
+          <x14:cfRule type="dataBar" priority="1150" id="{00E000FD-001D-42A6-9F17-007D006B0035}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13776,7 +13776,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1149" id="{00540064-007B-40B0-854B-008A0057000E}">
+          <x14:cfRule type="dataBar" priority="1149" id="{002C003A-006D-45A8-8E5C-00E1002C001C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13788,7 +13788,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1148" id="{004C00B4-0092-4054-A939-00DB00E0007F}">
+          <x14:cfRule type="dataBar" priority="1148" id="{001A0078-00AF-4C0B-B4A0-006600400011}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13800,7 +13800,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1147" id="{00FB00D5-00A6-4EAD-9EEA-001D00760069}">
+          <x14:cfRule type="dataBar" priority="1147" id="{000700D3-0015-47D2-8CED-000700B900D8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13812,7 +13812,7 @@
           <xm:sqref>R37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1146" id="{003D0028-005F-442E-8A58-00ED00AC00DC}">
+          <x14:cfRule type="dataBar" priority="1146" id="{008A0006-00E9-446E-9601-00EC00510080}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13824,7 +13824,7 @@
           <xm:sqref>F121:F123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1145" id="{00AC00BC-00AB-422D-BBE0-004700B200B7}">
+          <x14:cfRule type="dataBar" priority="1145" id="{006500EA-0030-4454-A4FE-00F600E70015}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13836,7 +13836,7 @@
           <xm:sqref>F121:F123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1144" id="{0092002C-0038-4229-B6A8-00840097008C}">
+          <x14:cfRule type="dataBar" priority="1144" id="{00D70096-0041-47FF-BB46-00C800500070}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13848,7 +13848,7 @@
           <xm:sqref>N121:N123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1143" id="{00CB0056-00FD-41EF-8797-0027004900AE}">
+          <x14:cfRule type="dataBar" priority="1143" id="{003200D4-00B2-47B2-850E-00DF009D00FA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13860,7 +13860,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1142" id="{005A0015-0029-4EA3-9A8F-0000004300A9}">
+          <x14:cfRule type="dataBar" priority="1142" id="{00C000FC-005F-4BAA-B54F-005800C10003}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13872,7 +13872,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1141" id="{009400B5-007D-4608-A241-00C1005C00DB}">
+          <x14:cfRule type="dataBar" priority="1141" id="{00930000-0067-4222-81F0-007D00F20046}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13884,7 +13884,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1140" id="{002000CF-00A0-4071-9380-007400390014}">
+          <x14:cfRule type="dataBar" priority="1140" id="{0004008D-00A5-4B0A-A57D-000F00C900B7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13896,7 +13896,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1139" id="{009D00A5-00D2-41F4-BDB0-007B00F700EA}">
+          <x14:cfRule type="dataBar" priority="1139" id="{00220028-00A6-481F-9785-00D1006C0043}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13908,7 +13908,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1138" id="{00AA0012-008A-49CE-80BF-007500A50015}">
+          <x14:cfRule type="dataBar" priority="1138" id="{002600D1-0090-48DF-9F1D-009400800067}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13920,7 +13920,7 @@
           <xm:sqref>F122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1137" id="{00660083-0068-4B51-9A68-00B300D400E7}">
+          <x14:cfRule type="dataBar" priority="1137" id="{006E0037-00C1-4FB6-9250-00C1004F0082}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13932,7 +13932,7 @@
           <xm:sqref>F121:F123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1136" id="{00810033-0073-4997-B8F3-00A300F700A2}">
+          <x14:cfRule type="dataBar" priority="1136" id="{002F0099-00B2-49EC-A56F-00240046008A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13944,7 +13944,7 @@
           <xm:sqref>F121</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1135" id="{009600FB-0000-4081-8BE4-005B00AF006A}">
+          <x14:cfRule type="dataBar" priority="1135" id="{00770060-004C-4A10-87BF-0024006A001E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13956,7 +13956,7 @@
           <xm:sqref>F121:F123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1134" id="{00E2001E-0061-45FB-BFF2-004F007100A5}">
+          <x14:cfRule type="dataBar" priority="1134" id="{000600D2-005A-4D84-A4F2-008900F400CD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13968,7 +13968,7 @@
           <xm:sqref>N121:N123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1133" id="{00DB00ED-0054-4F39-8C0C-00D100D10035}">
+          <x14:cfRule type="dataBar" priority="1133" id="{00DF00CE-00E2-4755-8DB7-00AA009300A9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13980,7 +13980,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1132" id="{006D0064-0022-4B03-998F-00EF0090004B}">
+          <x14:cfRule type="dataBar" priority="1132" id="{00C30043-000D-4BA4-9889-007400F20028}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13992,7 +13992,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1131" id="{006500E9-00C7-4FBF-8B8C-00CB00BF00D1}">
+          <x14:cfRule type="dataBar" priority="1131" id="{008100FF-0060-43B4-9688-000000680077}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14004,7 +14004,7 @@
           <xm:sqref>N121:N123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1130" id="{00CF0016-00F7-4099-8E56-00D900380038}">
+          <x14:cfRule type="dataBar" priority="1130" id="{008C00DE-0000-43E3-9CAB-002E00880054}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14016,7 +14016,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1129" id="{008700DD-0043-4D3C-B291-005600E700C8}">
+          <x14:cfRule type="dataBar" priority="1129" id="{009300C8-00BA-496B-89C8-00EC00890094}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14028,7 +14028,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1128" id="{00C00044-00CF-46EE-89E6-006A00CC00D3}">
+          <x14:cfRule type="dataBar" priority="1128" id="{00C10014-00EB-4549-903A-00A8003C00AD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14040,7 +14040,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1127" id="{000F00B3-00FB-4ED7-B8FF-00120010008E}">
+          <x14:cfRule type="dataBar" priority="1127" id="{00CA0089-0048-4775-9291-004900150053}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14052,7 +14052,7 @@
           <xm:sqref>R121:R123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1126" id="{004B009C-0058-4A83-AF8C-0042008C0033}">
+          <x14:cfRule type="dataBar" priority="1126" id="{004C0040-0081-4EB8-8F59-00A200B700D1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14064,7 +14064,7 @@
           <xm:sqref>F43</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1125" id="{00080003-0029-4335-A4F4-004C00F20040}">
+          <x14:cfRule type="dataBar" priority="1125" id="{00940008-00FD-4DE7-B513-0035002D000A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14076,7 +14076,7 @@
           <xm:sqref>F44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1124" id="{00CB00A4-0024-413D-A64E-00DF006E00F5}">
+          <x14:cfRule type="dataBar" priority="1124" id="{00EF0044-00FA-419C-B358-00E600B0003A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14088,7 +14088,7 @@
           <xm:sqref>F43</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1123" id="{00E5001A-00CC-41B2-AF60-001900B60034}">
+          <x14:cfRule type="dataBar" priority="1123" id="{00A7004F-0081-40D6-860A-00F7008D000F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14100,7 +14100,7 @@
           <xm:sqref>F42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1122" id="{00F50026-004E-46B5-9157-00B2005C0058}">
+          <x14:cfRule type="dataBar" priority="1122" id="{007C003C-009B-4472-8FF3-005B00F10038}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14112,7 +14112,7 @@
           <xm:sqref>F40:F41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1121" id="{0092007E-0074-409C-90AB-007100730040}">
+          <x14:cfRule type="dataBar" priority="1121" id="{00A90044-00FA-456F-B0BC-00F1007100C8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14124,7 +14124,7 @@
           <xm:sqref>F40:F41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1120" id="{00B500EB-001A-4381-8E56-0076005D00E2}">
+          <x14:cfRule type="dataBar" priority="1120" id="{00340036-0071-4325-811A-002C002A00AA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14136,7 +14136,7 @@
           <xm:sqref>N40:N41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1119" id="{00290068-00DA-4ED1-9226-00C0000400D0}">
+          <x14:cfRule type="dataBar" priority="1119" id="{00E7007B-0008-48AE-A33F-00B9002D00FE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14148,7 +14148,7 @@
           <xm:sqref>R40:R41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1118" id="{00A900E1-002B-4069-B8F5-0005001A0037}">
+          <x14:cfRule type="dataBar" priority="1118" id="{003A00E9-0014-4972-ACB2-00D700D600FA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14160,7 +14160,7 @@
           <xm:sqref>R40:R41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1117" id="{00A900CD-009D-43C6-A935-001F0052009E}">
+          <x14:cfRule type="dataBar" priority="1117" id="{007F009D-002F-48D4-8EE7-00EA00DA0085}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14172,7 +14172,7 @@
           <xm:sqref>N40:N41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1116" id="{002D0031-00B3-495D-8184-00C8004300FA}">
+          <x14:cfRule type="dataBar" priority="1116" id="{003900B3-00FB-4B3B-B696-00C500CA0059}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14184,7 +14184,7 @@
           <xm:sqref>R40:R41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1115" id="{000300B2-0018-44CC-8C7F-00B000F200B8}">
+          <x14:cfRule type="dataBar" priority="1115" id="{006F00BE-0089-4075-80C7-000E006C0029}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14196,7 +14196,7 @@
           <xm:sqref>R40:R41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1114" id="{00810045-00D0-42E3-9B96-00EF00B70032}">
+          <x14:cfRule type="dataBar" priority="1114" id="{002F000C-00C4-44AA-85FE-00DB00960060}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14208,7 +14208,7 @@
           <xm:sqref>R40:R41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1113" id="{00FB0092-0089-4801-9634-00BC00640022}">
+          <x14:cfRule type="dataBar" priority="1113" id="{007F00F2-00C1-4326-8A62-002400F7009F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14220,7 +14220,7 @@
           <xm:sqref>R40:R41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1112" id="{00C60057-00A9-4D0E-962D-0077005A00CC}">
+          <x14:cfRule type="dataBar" priority="1112" id="{00DC0000-00B1-4AB3-BCDE-00FE00B8008B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14232,7 +14232,7 @@
           <xm:sqref>R40:R41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1111" id="{0051006B-0001-4F1F-8611-004F0007009B}">
+          <x14:cfRule type="dataBar" priority="1111" id="{00F70001-0072-4297-9F70-00B4000E001D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14244,7 +14244,7 @@
           <xm:sqref>F40:F41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1110" id="{004D001D-0032-4D2B-839E-00ED005A00B9}">
+          <x14:cfRule type="dataBar" priority="1110" id="{004000E2-00D6-46A1-A90D-00C900DD0008}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14256,7 +14256,7 @@
           <xm:sqref>N40:N41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1109" id="{00300092-00C8-4063-B03C-003600DA0096}">
+          <x14:cfRule type="dataBar" priority="1109" id="{00530072-00A6-4EC7-B036-00B4000600CD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14268,7 +14268,7 @@
           <xm:sqref>F40:F42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1108" id="{004E00F7-00B0-42B3-BB79-0059000A0023}">
+          <x14:cfRule type="dataBar" priority="1108" id="{003F00EE-0019-4C21-BC22-00190070005E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14280,7 +14280,7 @@
           <xm:sqref>F40:F42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1107" id="{00000028-0020-4F47-9988-00B5004600B7}">
+          <x14:cfRule type="dataBar" priority="1107" id="{001D00B6-00D3-4215-A74F-00D100A20027}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14292,7 +14292,7 @@
           <xm:sqref>N40:N42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1106" id="{00DD00F3-00BA-4A47-9F9A-009C0015007B}">
+          <x14:cfRule type="dataBar" priority="1106" id="{00230092-00B2-4756-BA87-00D0008000B0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14304,7 +14304,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1105" id="{00150027-0006-43F2-86CC-0074002A0094}">
+          <x14:cfRule type="dataBar" priority="1105" id="{004B00D2-0088-44EC-9661-0016004600B8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14316,7 +14316,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1104" id="{00E90011-003D-4A31-814D-004600810010}">
+          <x14:cfRule type="dataBar" priority="1104" id="{002D0059-004B-4505-B0D0-005D00EC00F9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14328,7 +14328,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1103" id="{006200CB-00E7-45E7-B85D-00BF00C70083}">
+          <x14:cfRule type="dataBar" priority="1103" id="{00AE0020-00A2-41FE-996E-00EC002B00EE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14340,7 +14340,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1102" id="{00B60020-00FC-4F22-916D-0008006800FC}">
+          <x14:cfRule type="dataBar" priority="1102" id="{005A009B-0091-40A2-B103-00FF00F00022}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14352,7 +14352,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1101" id="{00AB002E-00D5-409B-B2C5-00AD00940026}">
+          <x14:cfRule type="dataBar" priority="1101" id="{0033000F-00AC-4B3A-AA9B-00DA00B100D7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14364,7 +14364,7 @@
           <xm:sqref>F41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1100" id="{00350070-0080-4AB2-BB0C-006F00740056}">
+          <x14:cfRule type="dataBar" priority="1100" id="{00A500CB-00A7-46B7-B169-004D006C0098}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14376,7 +14376,7 @@
           <xm:sqref>F40:F42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1099" id="{00140091-00CC-4A17-A4EF-000000300047}">
+          <x14:cfRule type="dataBar" priority="1099" id="{007C007E-00C9-4659-BDEA-00A800B700D2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14388,7 +14388,7 @@
           <xm:sqref>F40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1098" id="{00BC000C-0078-4D96-9CAC-0057009A0034}">
+          <x14:cfRule type="dataBar" priority="1098" id="{00E600B6-0090-4A0F-9CA2-00F4007D00B9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14400,7 +14400,7 @@
           <xm:sqref>F40:F42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1097" id="{00E40053-0002-4F8E-8EF6-00D400B9000C}">
+          <x14:cfRule type="dataBar" priority="1097" id="{00D500AE-00B9-453D-8EEF-00AA00900041}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14412,7 +14412,7 @@
           <xm:sqref>N40:N42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1096" id="{008A005E-00DC-4C42-9D26-006C00C20077}">
+          <x14:cfRule type="dataBar" priority="1096" id="{00750082-003E-41A3-95D5-007300FC0025}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14424,7 +14424,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1095" id="{005F0038-004A-4B2B-91F1-00B9005F000C}">
+          <x14:cfRule type="dataBar" priority="1095" id="{00AD00CB-00C3-48F4-B82B-0045002B00F5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14436,7 +14436,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1094" id="{00140036-00C1-4607-9387-00B5008F00E4}">
+          <x14:cfRule type="dataBar" priority="1094" id="{00910036-00C0-464F-8DEA-000900BF0040}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14448,7 +14448,7 @@
           <xm:sqref>N40:N42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1093" id="{008400ED-000E-420D-AE5B-00BB000B007A}">
+          <x14:cfRule type="dataBar" priority="1093" id="{00BF0063-00BB-479A-B61C-000C00E00050}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14460,7 +14460,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1092" id="{0042009D-000C-4B36-98E1-00AD005900D0}">
+          <x14:cfRule type="dataBar" priority="1092" id="{000A00CF-001F-4515-BEE7-009C00D600B7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14472,7 +14472,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1091" id="{008500F5-009E-48A0-B8AF-00660056006B}">
+          <x14:cfRule type="dataBar" priority="1091" id="{001700EB-0024-41D7-92F9-00590014004A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14484,7 +14484,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1090" id="{00E50049-0036-4A6B-9883-00FF00AA002E}">
+          <x14:cfRule type="dataBar" priority="1090" id="{000500C4-009D-48B5-BE58-006700F500E4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14496,7 +14496,7 @@
           <xm:sqref>R40:R42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1089" id="{00E400D3-00DC-4913-AA8F-00EE00050041}">
+          <x14:cfRule type="dataBar" priority="1089" id="{004300D7-00F6-4A8C-81D9-009300D1007D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14508,7 +14508,7 @@
           <xm:sqref>F28:F45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1086" id="{00F700AE-0094-4A8C-B341-00F700800035}">
+          <x14:cfRule type="dataBar" priority="1086" id="{00DC00EC-006C-4792-927D-009D007300CC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14520,7 +14520,7 @@
           <xm:sqref>F52:F69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1085" id="{00E1000F-0082-47B3-B350-008D001400EA}">
+          <x14:cfRule type="dataBar" priority="1085" id="{004E006E-0006-4C6A-BD10-001A00450080}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14532,7 +14532,7 @@
           <xm:sqref>F76:F93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1081" id="{0086007D-0060-4C45-8DC9-0016000F002C}">
+          <x14:cfRule type="dataBar" priority="1081" id="{00F000B5-0046-4D72-AA5F-008100D500FB}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -14542,7 +14542,7 @@
           <xm:sqref>N10:N21 N4:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1080" id="{007D005C-00A7-4047-9035-00D4006B0065}">
+          <x14:cfRule type="dataBar" priority="1080" id="{000B00E6-00DE-473E-B78D-000700480017}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -14552,7 +14552,7 @@
           <xm:sqref>F4:F8 F10:F21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1079" id="{00D100AC-0096-47E7-B1C3-00E800530028}">
+          <x14:cfRule type="dataBar" priority="1079" id="{006F00C1-00D8-47EF-924E-00EC00830052}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14564,7 +14564,7 @@
           <xm:sqref>N28:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1078" id="{00E8003F-006B-47BC-95B3-005C003900AB}">
+          <x14:cfRule type="dataBar" priority="1078" id="{00DC00D6-0034-47E1-B809-00C600DB001E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14576,7 +14576,7 @@
           <xm:sqref>N52:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1077" id="{001A0045-00FD-4CB5-98A8-00800055007A}">
+          <x14:cfRule type="dataBar" priority="1077" id="{00B4006C-0042-449D-A74D-008C0057000A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14588,7 +14588,7 @@
           <xm:sqref>N76:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1076" id="{00E9002D-00EF-46C1-96EE-0093001A0068}">
+          <x14:cfRule type="dataBar" priority="1076" id="{00A400D4-003D-4C52-9948-00570074008A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14600,7 +14600,7 @@
           <xm:sqref>N100:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1075" id="{005700FC-004A-4DAC-96D8-009E00150043}">
+          <x14:cfRule type="dataBar" priority="1075" id="{00B7001E-004A-4599-A7CC-008900C000C0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14612,7 +14612,7 @@
           <xm:sqref>R4:R8 R10:R21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1074" id="{003E0028-00F4-4BC3-92EE-00B500580083}">
+          <x14:cfRule type="dataBar" priority="1074" id="{002300E3-0015-4119-904D-003F00E40025}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14624,7 +14624,7 @@
           <xm:sqref>R28:R45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1073" id="{000D0019-0043-44A5-9194-00FD00A80049}">
+          <x14:cfRule type="dataBar" priority="1073" id="{003C00BE-000C-44B2-BF80-009F0070006C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14636,7 +14636,7 @@
           <xm:sqref>R52:R69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1072" id="{00DF0008-00EA-419C-88DB-00BD00AC005D}">
+          <x14:cfRule type="dataBar" priority="1072" id="{00140077-00D9-4253-A1A2-000500160080}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14648,7 +14648,7 @@
           <xm:sqref>R76:R93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1071" id="{00730003-0005-45F0-B08E-000900A60000}">
+          <x14:cfRule type="dataBar" priority="1071" id="{006F00EA-00E2-4F4A-AB38-00C30000009A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14660,7 +14660,7 @@
           <xm:sqref>R100:R117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1010" id="{00F5005F-00DB-43AC-82BB-00B300B8005D}">
+          <x14:cfRule type="dataBar" priority="1010" id="{00AA0002-005A-443E-8416-0076002900C6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14672,7 +14672,7 @@
           <xm:sqref>R135:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1009" id="{00FC0035-000E-439F-AF80-00F4005C0083}">
+          <x14:cfRule type="dataBar" priority="1009" id="{002E00B8-0073-4EAE-8347-00B400A200CA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14684,7 +14684,7 @@
           <xm:sqref>F135:F141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1008" id="{00DD0035-0023-48DD-806B-001B00F300BA}">
+          <x14:cfRule type="dataBar" priority="1008" id="{003100F0-0077-4397-AEAA-000000BE0089}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14696,7 +14696,7 @@
           <xm:sqref>N135:N141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1007" id="{00A2002C-008C-4844-B803-0089003F00C9}">
+          <x14:cfRule type="dataBar" priority="1007" id="{005C0031-004E-4E96-936E-006400B40077}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14708,7 +14708,7 @@
           <xm:sqref>F134:F141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1006" id="{003D00E6-0022-47BA-82BE-00C300DF0044}">
+          <x14:cfRule type="dataBar" priority="1006" id="{00CB0060-003E-4101-B720-003C00A70077}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14720,7 +14720,7 @@
           <xm:sqref>F136</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1004" id="{00A3001A-009B-4BE8-9866-006500DA007E}">
+          <x14:cfRule type="dataBar" priority="1004" id="{001000BC-0000-4087-8B9A-0047001400E0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14732,7 +14732,7 @@
           <xm:sqref>N124:N141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1003" id="{00210049-002F-4858-B3C1-00F90035008E}">
+          <x14:cfRule type="dataBar" priority="1003" id="{00AC0087-00DD-4B34-8DF7-00ED00BD00BE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14744,7 +14744,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1002" id="{00A30054-0007-485F-991C-00DA00D2006E}">
+          <x14:cfRule type="dataBar" priority="1002" id="{00B10084-009E-453A-BC0D-006D00EB0091}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14756,7 +14756,7 @@
           <xm:sqref>R121:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1001" id="{00B800DE-007A-4039-B0E3-0094001700E6}">
+          <x14:cfRule type="dataBar" priority="1001" id="{00DF0013-00C7-46FE-A164-006700C00046}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14768,7 +14768,7 @@
           <xm:sqref>F121:F133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1000" id="{006D00E0-00F0-47DF-82F1-00D600440054}">
+          <x14:cfRule type="dataBar" priority="1000" id="{00180073-002A-4D5A-BB74-006D005A00DB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14780,7 +14780,7 @@
           <xm:sqref>N121:N141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="999" id="{007600A0-0021-4A08-9EC3-00D800D90026}">
+          <x14:cfRule type="dataBar" priority="999" id="{00CF00C7-00F5-4E3E-8F5D-006E006000E7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14792,7 +14792,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="998" id="{006800F6-007D-4D81-A38F-0029007A00F4}">
+          <x14:cfRule type="dataBar" priority="998" id="{001900CC-007B-44D3-A37A-00F7003500E0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14804,7 +14804,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="997" id="{00590086-00E7-4E04-AF19-0009008A0095}">
+          <x14:cfRule type="dataBar" priority="997" id="{00D50018-0074-40FA-8A25-00610033003B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14816,7 +14816,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="996" id="{00730077-0076-4F4D-AA6D-0096005C002B}">
+          <x14:cfRule type="dataBar" priority="996" id="{00970041-00AC-49B0-9549-0038008600CE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14828,7 +14828,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="995" id="{006500CE-0091-4A71-B495-00F10050004F}">
+          <x14:cfRule type="dataBar" priority="995" id="{0085001A-007A-4CA4-B58C-00B200AF000C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14840,7 +14840,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="994" id="{000A00F5-00AF-4375-AA2B-00B800F7000C}">
+          <x14:cfRule type="dataBar" priority="994" id="{00C7009C-006B-458C-856F-009F001100AF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14852,7 +14852,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="993" id="{00110097-005F-46E6-B28C-00D800FE0039}">
+          <x14:cfRule type="dataBar" priority="993" id="{003F006E-0019-4071-937B-000000FD009E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14864,7 +14864,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="992" id="{00F2007B-0093-44A3-A42D-001C002D00BB}">
+          <x14:cfRule type="dataBar" priority="992" id="{005F00E6-00AA-4552-B01E-006800A6009F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14876,7 +14876,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="991" id="{000A00BA-0019-44FE-8C56-004A006D00E3}">
+          <x14:cfRule type="dataBar" priority="991" id="{00C10083-00C3-4F12-9AA2-00A900980059}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14888,7 +14888,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="990" id="{005B008F-008D-4422-AEA0-009800730010}">
+          <x14:cfRule type="dataBar" priority="990" id="{002C0027-00E0-458E-A805-0044002200D4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14900,7 +14900,7 @@
           <xm:sqref>R124:R141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="989" id="{00820083-0030-48C7-9333-00990068008C}">
+          <x14:cfRule type="dataBar" priority="989" id="{00E0008D-0033-4141-86E0-00C5002800DD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14912,7 +14912,7 @@
           <xm:sqref>T4:T8 T10:T21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="987" id="{001600F3-0006-4133-8412-008B009F005D}">
+          <x14:cfRule type="dataBar" priority="987" id="{00F9008B-0015-44A0-8876-002F00F600D9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14924,7 +14924,7 @@
           <xm:sqref>T28:T45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="985" id="{0067007C-0026-4A56-AA7C-006B003D0073}">
+          <x14:cfRule type="dataBar" priority="985" id="{00CC0081-007A-4FF8-8C7E-00F7003400AD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14936,7 +14936,7 @@
           <xm:sqref>T52:T69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="983" id="{002E0016-007C-41A2-B25E-00EC00140099}">
+          <x14:cfRule type="dataBar" priority="983" id="{00820057-0054-47A5-8124-002D00C5009D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14948,7 +14948,7 @@
           <xm:sqref>T76:T93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="981" id="{003E002D-0023-48E0-83A1-00A000B000E4}">
+          <x14:cfRule type="dataBar" priority="981" id="{0029009D-005E-494F-82A1-00D0001C007C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14960,7 +14960,7 @@
           <xm:sqref>T100:T117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="979" id="{0032000C-0031-46BF-ACE9-003E00B800C3}">
+          <x14:cfRule type="dataBar" priority="979" id="{008F00ED-00E0-4CE1-AC5D-005500CC0054}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14972,7 +14972,7 @@
           <xm:sqref>T124:T141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="972" id="{0037002C-0021-4C9E-9427-00A40078006F}">
+          <x14:cfRule type="dataBar" priority="972" id="{00FC00D9-00D0-475F-B4F5-004F00E50014}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14984,7 +14984,7 @@
           <xm:sqref>T4:T8 T10:T21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="971" id="{00790005-0008-4B95-835E-00F200190035}">
+          <x14:cfRule type="dataBar" priority="971" id="{00D700BE-007F-4C5A-B020-002700060096}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -14994,7 +14994,7 @@
           <xm:sqref>T124:T141 T100:T117 T76:T93 T52:T69 T28:T45 T4:T8 T10:T21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="968" id="{008C00D7-0051-4DC9-BEB4-002400A500B8}">
+          <x14:cfRule type="dataBar" priority="968" id="{00400014-0032-4EEC-9EB0-0094008E009B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15006,7 +15006,7 @@
           <xm:sqref>F100:F117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="967" id="{00B600FB-008E-4E47-99D3-00820015000A}">
+          <x14:cfRule type="dataBar" priority="967" id="{005D006F-0022-4C49-9A7A-0034006900FE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15018,7 +15018,7 @@
           <xm:sqref>F124:F141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="966" id="{00F600DB-00A8-46C1-A09A-007B00A00006}">
+          <x14:cfRule type="dataBar" priority="966" id="{00240063-0043-438E-BF6A-006A00BE0007}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15030,7 +15030,7 @@
           <xm:sqref>N9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="965" id="{008E00CF-00D3-4FD6-9E15-00CE00CD00C1}">
+          <x14:cfRule type="dataBar" priority="965" id="{00A5007A-001E-4F09-B9E7-0060008A0049}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15042,7 +15042,7 @@
           <xm:sqref>F9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="964" id="{004E00CE-00FE-4F44-8D2A-002700F30079}">
+          <x14:cfRule type="dataBar" priority="964" id="{003F00D9-00A4-4D41-BE94-0090000F00AC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15054,7 +15054,7 @@
           <xm:sqref>R9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="963" id="{00E50011-0013-4ADE-9138-001700500014}">
+          <x14:cfRule type="dataBar" priority="963" id="{003700B3-008E-4230-A996-001F000E000D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15066,7 +15066,7 @@
           <xm:sqref>R9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="962" id="{00F5006A-0065-4D34-87B2-0089008C00B3}">
+          <x14:cfRule type="dataBar" priority="962" id="{00A900FF-0000-4160-9D9F-009D001D004C}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15076,7 +15076,7 @@
           <xm:sqref>N9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="961" id="{00850097-001A-470C-AFAE-004B00380032}">
+          <x14:cfRule type="dataBar" priority="961" id="{002A0039-00C7-4B7D-9A75-004D005F008B}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15086,7 +15086,7 @@
           <xm:sqref>F9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="960" id="{00D100A0-0095-4ABD-81FA-00C700BE000D}">
+          <x14:cfRule type="dataBar" priority="960" id="{007A0057-009C-456D-8CE5-00C300C900D6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15098,7 +15098,7 @@
           <xm:sqref>T9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="959" id="{007E00A8-003D-4ECB-87BC-002C00B800E5}">
+          <x14:cfRule type="dataBar" priority="959" id="{00510011-0084-4D05-9662-00D0007600AA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15110,7 +15110,7 @@
           <xm:sqref>T9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="958" id="{00C900F3-005C-4197-BEB0-00F2003200C9}">
+          <x14:cfRule type="dataBar" priority="958" id="{003A00AB-002C-4AAF-AC71-002C00AF00A1}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15120,7 +15120,7 @@
           <xm:sqref>T9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="957" id="{00670026-0069-4859-BA00-00D2003F0095}">
+          <x14:cfRule type="dataBar" priority="957" id="{00960033-0008-42C0-A78D-00CF00F8008B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15132,7 +15132,7 @@
           <xm:sqref>F8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="956" id="{006700B5-0059-4082-9F50-00B900ED0027}">
+          <x14:cfRule type="dataBar" priority="956" id="{003D00BA-0005-4B92-9605-00AE00F600D2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15144,7 +15144,7 @@
           <xm:sqref>N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="955" id="{00E8005A-00D3-471E-8860-002A00E10011}">
+          <x14:cfRule type="dataBar" priority="955" id="{00B000D2-0029-4D0E-9E54-0017008A007B}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15154,7 +15154,7 @@
           <xm:sqref>F4:F21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="954" id="{003E0065-00D9-49A9-877E-00E6004C0005}">
+          <x14:cfRule type="dataBar" priority="954" id="{00B600C2-005D-482A-9ECF-00B200FE00D8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15166,7 +15166,7 @@
           <xm:sqref>U4:U21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="953" id="{00C800D9-0005-49A0-AE07-00DF00370018}">
+          <x14:cfRule type="dataBar" priority="953" id="{006B00AC-00F2-4799-89FF-00BF00910056}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15178,7 +15178,7 @@
           <xm:sqref>U4:U21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="951" id="{00FD00DB-0062-40EB-9489-00AC009200F2}">
+          <x14:cfRule type="dataBar" priority="951" id="{00DB00B7-0065-465F-B37B-00AB005A00E8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15190,7 +15190,7 @@
           <xm:sqref>U9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="950" id="{00DD004A-0034-40D8-A924-00D900050043}">
+          <x14:cfRule type="dataBar" priority="950" id="{00D000AE-002D-4BF8-BD6B-005B00CF00EF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15202,7 +15202,7 @@
           <xm:sqref>U9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="949" id="{00220067-00DF-4109-81BB-007900300080}">
+          <x14:cfRule type="dataBar" priority="949" id="{0013000C-0019-44BD-A838-00570060002C}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15212,7 +15212,7 @@
           <xm:sqref>U9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="948" id="{003D007F-006D-444B-9B65-009400460016}">
+          <x14:cfRule type="dataBar" priority="948" id="{00A500AF-00D6-46BD-AF30-002900CB00AA}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15222,7 +15222,7 @@
           <xm:sqref>U4:U21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="947" id="{00D100E7-008C-4D8D-B890-00B1002B00FF}">
+          <x14:cfRule type="dataBar" priority="947" id="{00AF006B-00D7-43BF-8387-0020005A0030}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15234,7 +15234,7 @@
           <xm:sqref>U28:U45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="946" id="{00750048-007D-42F5-A363-003300C10092}">
+          <x14:cfRule type="dataBar" priority="946" id="{0020006E-005B-4FF4-B95C-00AD00C600A6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15246,7 +15246,7 @@
           <xm:sqref>U28:U45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="944" id="{00B700D8-0006-48A0-A1E9-009F00C100AD}">
+          <x14:cfRule type="dataBar" priority="944" id="{008A008C-0083-42DF-B35A-007600C600BB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15258,7 +15258,7 @@
           <xm:sqref>U33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="943" id="{00D800D6-00ED-45D9-A8C7-006E006C004D}">
+          <x14:cfRule type="dataBar" priority="943" id="{00BC00B1-007D-438B-8051-00CE00B5004E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15270,7 +15270,7 @@
           <xm:sqref>U33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="942" id="{00A60077-00AA-4714-8239-00C300870018}">
+          <x14:cfRule type="dataBar" priority="942" id="{004F0046-00B7-4FA9-93E9-004C00D100D8}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15280,7 +15280,7 @@
           <xm:sqref>U33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="941" id="{00D400D6-0058-4927-8006-001000AA006B}">
+          <x14:cfRule type="dataBar" priority="941" id="{00090091-005C-4A4E-8A05-00EE00F3007D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15292,7 +15292,7 @@
           <xm:sqref>U52:U69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="940" id="{00C80071-0063-467B-8C02-008A0075001A}">
+          <x14:cfRule type="dataBar" priority="940" id="{00D9008C-000E-428B-BD71-008200080022}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15304,7 +15304,7 @@
           <xm:sqref>U52:U69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="938" id="{00E50081-0037-48CC-A07D-006100DF00CF}">
+          <x14:cfRule type="dataBar" priority="938" id="{00AF000B-0097-40D7-AE77-00E5005A00C3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15316,7 +15316,7 @@
           <xm:sqref>U57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="937" id="{005A0078-0002-46EF-B7C9-008B004400BE}">
+          <x14:cfRule type="dataBar" priority="937" id="{008B0061-008D-4F0E-A6A6-004700570068}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15328,7 +15328,7 @@
           <xm:sqref>U57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="936" id="{00FB00A7-0091-48E1-846F-00BB008900AC}">
+          <x14:cfRule type="dataBar" priority="936" id="{00CE00D9-008E-48AB-9E03-00FD004F0081}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15338,7 +15338,7 @@
           <xm:sqref>U57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="935" id="{0064004A-0027-4594-A2D1-00B600310006}">
+          <x14:cfRule type="dataBar" priority="935" id="{002C00FB-005C-4F69-A19A-00D0005B0096}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15350,7 +15350,7 @@
           <xm:sqref>U76:U93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="934" id="{00A000B8-008E-4CE2-9227-000D00AB0007}">
+          <x14:cfRule type="dataBar" priority="934" id="{00E0003D-0086-4B77-93A7-007B00E000B6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15362,7 +15362,7 @@
           <xm:sqref>U76:U93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="932" id="{00F1001C-00EB-4645-AB27-0073004300D3}">
+          <x14:cfRule type="dataBar" priority="932" id="{00920077-0052-4611-8323-00F1008400DD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15374,7 +15374,7 @@
           <xm:sqref>U81</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="931" id="{006E0051-006B-4E68-95ED-00C400D70074}">
+          <x14:cfRule type="dataBar" priority="931" id="{0099001B-003B-4F02-BAE4-0062007400A1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15386,7 +15386,7 @@
           <xm:sqref>U81</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="930" id="{00360095-003A-4B2F-9609-00F00007009D}">
+          <x14:cfRule type="dataBar" priority="930" id="{00FD002B-00B5-4547-877C-00BA00EB0096}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15396,7 +15396,7 @@
           <xm:sqref>U81</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="929" id="{00040067-00C2-4131-B702-000900A200E5}">
+          <x14:cfRule type="dataBar" priority="929" id="{000B00ED-00C7-432D-BBD1-008A00A70096}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15408,7 +15408,7 @@
           <xm:sqref>U100:U117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="928" id="{003A003C-00E2-46C6-80E6-00C600DA0005}">
+          <x14:cfRule type="dataBar" priority="928" id="{00D300EF-006D-4A31-ADCD-00F600DF004B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15420,7 +15420,7 @@
           <xm:sqref>U100:U117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="926" id="{00090091-00E2-456C-A6DC-0090000100BA}">
+          <x14:cfRule type="dataBar" priority="926" id="{0022007D-003B-488C-B034-0020005100E1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15432,7 +15432,7 @@
           <xm:sqref>U105</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="925" id="{00A0004E-00D0-4EBB-8D50-003B008100E9}">
+          <x14:cfRule type="dataBar" priority="925" id="{0083006A-004D-4DED-9B4B-002100370026}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15444,7 +15444,7 @@
           <xm:sqref>U105</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="924" id="{001F00A8-00CE-4B1A-B86B-006700580073}">
+          <x14:cfRule type="dataBar" priority="924" id="{0007002C-007E-40BC-BE50-009000F400F4}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15454,7 +15454,7 @@
           <xm:sqref>U105</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="923" id="{000A00A9-00A7-4E50-BC1E-006A006E00A9}">
+          <x14:cfRule type="dataBar" priority="923" id="{00720061-0054-4590-87A4-00640023005D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15466,7 +15466,7 @@
           <xm:sqref>U124:U141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="922" id="{0005001E-00BE-411C-968E-002D003A00A8}">
+          <x14:cfRule type="dataBar" priority="922" id="{00E20054-00D3-4FBC-993E-0056008100A5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15478,7 +15478,7 @@
           <xm:sqref>U124:U141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="920" id="{009C009A-006C-4529-8C40-001E0059003F}">
+          <x14:cfRule type="dataBar" priority="920" id="{00B7007A-00B9-45C3-82F4-004F0076000A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15490,7 +15490,7 @@
           <xm:sqref>U129</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="919" id="{007800FE-00E8-47CF-99B0-0040000100C4}">
+          <x14:cfRule type="dataBar" priority="919" id="{00E60071-0005-4489-9D41-00D8000B00AE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15502,7 +15502,7 @@
           <xm:sqref>U129</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="918" id="{00B700B1-0091-450F-83D8-00E700680056}">
+          <x14:cfRule type="dataBar" priority="918" id="{00CF002A-00D6-442A-ADB4-007400D60028}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15512,7 +15512,7 @@
           <xm:sqref>U129</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="917" id="{00DB00EC-00EA-4D9C-88F3-00CC00DE00CB}">
+          <x14:cfRule type="dataBar" priority="917" id="{005E00F6-0056-4053-8904-000100800057}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15522,7 +15522,7 @@
           <xm:sqref>U28:U45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="916" id="{003B0009-006F-4B77-BB77-00D5000A0043}">
+          <x14:cfRule type="dataBar" priority="916" id="{00AD0046-00D0-43FF-9C30-0055004600CC}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15532,7 +15532,7 @@
           <xm:sqref>U52:U69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="915" id="{008800B8-0018-4D32-8499-001A00490070}">
+          <x14:cfRule type="dataBar" priority="915" id="{004B004A-0089-4E23-9EBC-0017001E00DB}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15542,7 +15542,7 @@
           <xm:sqref>U76:U93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="914" id="{00FC0047-00E1-4931-B52E-002F00A00080}">
+          <x14:cfRule type="dataBar" priority="914" id="{00EC0058-002E-4094-97DB-000400BE005F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15552,7 +15552,7 @@
           <xm:sqref>U100:U117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="913" id="{00400037-00CF-44FD-B3C9-00E3001300BF}">
+          <x14:cfRule type="dataBar" priority="913" id="{007C0060-00F6-46B0-A4F9-0000005A00AF}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15562,7 +15562,7 @@
           <xm:sqref>U124:U141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="912" id="{00ED008C-00B6-477C-B4AE-00AD000D00DA}">
+          <x14:cfRule type="dataBar" priority="912" id="{006100E9-0051-4086-BD34-000B00B6003C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15574,7 +15574,7 @@
           <xm:sqref>T124:T141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="911" id="{003F00BA-00E5-46BE-B48B-002D00A600FF}">
+          <x14:cfRule type="dataBar" priority="911" id="{00E900DE-000F-478A-BD71-00C50001006F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15586,7 +15586,7 @@
           <xm:sqref>T100:T117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="910" id="{008A00B2-0016-4ACA-96BC-00CF00E90085}">
+          <x14:cfRule type="dataBar" priority="910" id="{00C0004E-00CA-4411-91A8-007200E200CD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15598,7 +15598,7 @@
           <xm:sqref>T76:T93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="909" id="{003F0068-001D-4865-810A-00E60095002A}">
+          <x14:cfRule type="dataBar" priority="909" id="{00810050-0023-4E44-9EEA-00C2004E0024}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15610,7 +15610,7 @@
           <xm:sqref>T52:T69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="908" id="{00CA0094-001C-43CB-ABEA-00900015002A}">
+          <x14:cfRule type="dataBar" priority="908" id="{001C00C0-00A6-43AC-A113-00BD005B00D9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15622,7 +15622,7 @@
           <xm:sqref>T28:T45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="907" id="{002C00C0-00B6-4AA6-AF13-00FC00C100C3}">
+          <x14:cfRule type="dataBar" priority="907" id="{0061001A-008D-4094-AA11-00AF008500A7}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -15632,7 +15632,7 @@
           <xm:sqref>T4:T21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="906" id="{00D000F4-0095-4BA6-BBC2-00E2008F009F}">
+          <x14:cfRule type="dataBar" priority="906" id="{007B0041-0011-4257-BA32-00C3008C0070}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15644,7 +15644,7 @@
           <xm:sqref>S145:S148 S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="905" id="{002200CE-005F-44F7-B3F4-00F700DA002A}">
+          <x14:cfRule type="dataBar" priority="905" id="{00FF0025-00A0-4626-BB0E-00500003005F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15656,7 +15656,7 @@
           <xm:sqref>F145:F148 F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="904" id="{003E000A-005D-477B-8DCF-00C9005E0074}">
+          <x14:cfRule type="dataBar" priority="904" id="{003000C4-001E-4A88-8B6D-005E00E200FC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15668,7 +15668,7 @@
           <xm:sqref>N145:N148 N152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="903" id="{005B00F0-0080-40BC-9589-00BF0006001E}">
+          <x14:cfRule type="dataBar" priority="903" id="{00710099-007C-4B01-ADD2-0061007300A3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15680,7 +15680,7 @@
           <xm:sqref>F145:F146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="902" id="{00920085-00B9-4268-9DFE-00C500D3000F}">
+          <x14:cfRule type="dataBar" priority="902" id="{00CD00DB-0033-486E-ABAC-00F2005C0008}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15692,7 +15692,7 @@
           <xm:sqref>F145:F146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="901" id="{005100AD-00F0-4FDC-963A-0022007D0093}">
+          <x14:cfRule type="dataBar" priority="901" id="{00C7005C-0096-4ACB-81C5-0071002B0036}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15704,7 +15704,7 @@
           <xm:sqref>N145:N146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="900" id="{00F10008-009A-4CD3-9257-00900076004F}">
+          <x14:cfRule type="dataBar" priority="900" id="{007D0031-0034-45D9-85C4-007000BB0078}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15716,7 +15716,7 @@
           <xm:sqref>S145:S146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="899" id="{005700B8-00A6-4147-9AA7-00B500C700A0}">
+          <x14:cfRule type="dataBar" priority="899" id="{0017001A-004D-4B0E-A99E-00B4009200A8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15728,7 +15728,7 @@
           <xm:sqref>S145:S146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="898" id="{00CA0073-0092-4137-896D-000C007D0079}">
+          <x14:cfRule type="dataBar" priority="898" id="{007500E5-0051-423F-8DC8-0076000C00AA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15740,7 +15740,7 @@
           <xm:sqref>N145:N146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="897" id="{00D5003C-0002-4686-88E1-00550095000F}">
+          <x14:cfRule type="dataBar" priority="897" id="{0066000F-002F-42ED-A39B-00D20057007C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15752,7 +15752,7 @@
           <xm:sqref>S145:S146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="896" id="{0008003C-00A7-4A67-B900-009F00CD0078}">
+          <x14:cfRule type="dataBar" priority="896" id="{005C0040-0098-49B4-A543-0067007F00EA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15764,7 +15764,7 @@
           <xm:sqref>S145:S146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="895" id="{0011000D-001C-4D98-9AF7-006400F2006E}">
+          <x14:cfRule type="dataBar" priority="895" id="{00EC0050-001F-4842-882C-000500F5002A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15776,7 +15776,7 @@
           <xm:sqref>S145:S146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="894" id="{00BA009B-0065-49AB-9788-00F20019009A}">
+          <x14:cfRule type="dataBar" priority="894" id="{009400DF-00EA-4918-BE54-000400C6002B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15788,7 +15788,7 @@
           <xm:sqref>S145:S146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="893" id="{006C0056-00E2-41F3-BF6E-00A600F100FB}">
+          <x14:cfRule type="dataBar" priority="893" id="{00CB0094-00EC-45E1-95AC-00DC00B20041}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15800,7 +15800,7 @@
           <xm:sqref>S145:S146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="892" id="{000A001F-00F4-439C-A92F-00B700F500AF}">
+          <x14:cfRule type="dataBar" priority="892" id="{00BE007B-00CF-4893-9862-008E00FB006B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15812,7 +15812,7 @@
           <xm:sqref>F145:F146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="891" id="{003A008F-00CD-43A0-A433-00C0008300E6}">
+          <x14:cfRule type="dataBar" priority="891" id="{00CA00F3-0047-469F-A2CA-00F7008000C4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15824,7 +15824,7 @@
           <xm:sqref>N145:N146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="890" id="{00E1004D-00A6-4AE6-99D1-000B008100E7}">
+          <x14:cfRule type="dataBar" priority="890" id="{002200BA-0014-44E1-9394-003400F7000D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15836,7 +15836,7 @@
           <xm:sqref>F145:F147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="889" id="{008500F7-00B8-41D5-9030-006200F30097}">
+          <x14:cfRule type="dataBar" priority="889" id="{00EE0072-00E5-4482-BED5-0051009600C6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15848,7 +15848,7 @@
           <xm:sqref>F145:F147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="888" id="{00880054-00BB-4CA2-8AFE-009C00AE00AD}">
+          <x14:cfRule type="dataBar" priority="888" id="{00930032-0089-42CF-9190-000D000000E1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15860,7 +15860,7 @@
           <xm:sqref>N145:N147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="887" id="{00C90018-0095-4EE2-9944-00060014003E}">
+          <x14:cfRule type="dataBar" priority="887" id="{007E0073-008D-4B70-915A-009A00290009}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15872,7 +15872,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="886" id="{006100DE-00A8-45CA-882B-005B00230016}">
+          <x14:cfRule type="dataBar" priority="886" id="{00820088-005D-46BC-83B6-00A300A80084}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15884,7 +15884,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="885" id="{00A700F6-00E3-49F9-9FAD-00EC0041009B}">
+          <x14:cfRule type="dataBar" priority="885" id="{00A00064-009B-4DBF-909E-002900D900F4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15896,7 +15896,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="884" id="{008B00BD-0044-474D-9E9C-00F000920092}">
+          <x14:cfRule type="dataBar" priority="884" id="{000400FE-0047-48FB-9DB3-00140072009B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15908,7 +15908,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="883" id="{006F0004-0082-4B59-A0C1-006A00C30059}">
+          <x14:cfRule type="dataBar" priority="883" id="{00AA005F-0021-4925-8CDD-00AD00980070}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15920,7 +15920,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="882" id="{00A300D1-004B-4E08-A5C6-006C005F00A6}">
+          <x14:cfRule type="dataBar" priority="882" id="{00540007-0098-4F60-A25B-0010000200C9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15932,7 +15932,7 @@
           <xm:sqref>F146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="881" id="{0033002C-000A-41A1-A7F7-001400BE008C}">
+          <x14:cfRule type="dataBar" priority="881" id="{006600D1-002F-48CB-8109-00CA00300072}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15944,7 +15944,7 @@
           <xm:sqref>F145:F147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="880" id="{00BA0075-0025-4C61-B2B9-0068001D009C}">
+          <x14:cfRule type="dataBar" priority="880" id="{009D00A0-00D0-472C-AB77-00D100E500A1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15956,7 +15956,7 @@
           <xm:sqref>F145</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="879" id="{000700B1-00F9-4461-91CF-00F500DF00E8}">
+          <x14:cfRule type="dataBar" priority="879" id="{00380038-00DD-4C6F-A4A3-007E004E0068}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15968,7 +15968,7 @@
           <xm:sqref>F145:F147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="878" id="{00F40004-0049-4168-BB43-0077001D0059}">
+          <x14:cfRule type="dataBar" priority="878" id="{00520093-00C4-4BE0-9F64-00BD004800DF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15980,7 +15980,7 @@
           <xm:sqref>N145:N147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="877" id="{00C000DC-00A6-4E23-9D60-007A00190007}">
+          <x14:cfRule type="dataBar" priority="877" id="{002E0025-0054-478D-BF57-0083005E00F4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -15992,7 +15992,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="876" id="{005100DF-001E-4269-AAE2-00A9004400C3}">
+          <x14:cfRule type="dataBar" priority="876" id="{002F0003-006A-4AC7-BF97-00CA00F7003A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16004,7 +16004,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="875" id="{00270066-0044-4FCE-A4A0-009300D500FD}">
+          <x14:cfRule type="dataBar" priority="875" id="{003E005F-00F5-435E-A93A-00BD008100B8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16016,7 +16016,7 @@
           <xm:sqref>N145:N147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="874" id="{002E00BE-008D-4827-9A02-008800DE0061}">
+          <x14:cfRule type="dataBar" priority="874" id="{00D40070-0011-41E0-9FD7-007D001C003D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16028,7 +16028,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="873" id="{00A20089-00B2-4EDF-843C-00D6003800A6}">
+          <x14:cfRule type="dataBar" priority="873" id="{0082002A-00B9-4F48-BE75-009300F4006F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16040,7 +16040,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="872" id="{004F00B1-00A7-4551-BFC2-00C7003300F6}">
+          <x14:cfRule type="dataBar" priority="872" id="{001700A6-00EC-495E-99D7-00E900F400B0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16052,7 +16052,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="871" id="{00E90072-0014-4788-8B34-00AE0044007C}">
+          <x14:cfRule type="dataBar" priority="871" id="{0097000A-009E-4659-B361-003E0064006E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16064,7 +16064,7 @@
           <xm:sqref>S145:S147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="870" id="{002D0047-0072-4E87-9BEA-00B300FA00F2}">
+          <x14:cfRule type="dataBar" priority="870" id="{0008006F-0025-4399-9DAB-00B5008800BA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16076,7 +16076,7 @@
           <xm:sqref>S161:S163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="869" id="{00C7002C-0080-49D0-8D9E-00F7001E00AA}">
+          <x14:cfRule type="dataBar" priority="869" id="{006C00E4-002E-43BC-9372-000400030019}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16088,7 +16088,7 @@
           <xm:sqref>F161:F163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="868" id="{00160054-00D7-4A9A-89BE-002600F300B3}">
+          <x14:cfRule type="dataBar" priority="868" id="{00280097-0089-45BA-B0A6-00E300CD0022}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16100,7 +16100,7 @@
           <xm:sqref>N161:N163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="867" id="{0009008D-00D3-4216-A33D-00610002001B}">
+          <x14:cfRule type="dataBar" priority="867" id="{002E00DE-00FF-4174-8884-00F400D600ED}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16112,7 +16112,7 @@
           <xm:sqref>F160:F163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="866" id="{005D0082-006A-46B2-BBE3-0022004000CD}">
+          <x14:cfRule type="dataBar" priority="866" id="{00D20028-0039-40B8-8D5A-00C900930087}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16124,7 +16124,7 @@
           <xm:sqref>F162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="843" id="{00AD001F-0012-47FA-9C4A-00E600790088}">
+          <x14:cfRule type="dataBar" priority="843" id="{007C0064-0018-455A-ABAF-0034002C003C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16136,7 +16136,7 @@
           <xm:sqref>U154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="842" id="{003900B7-0006-481D-9DB4-00B200460006}">
+          <x14:cfRule type="dataBar" priority="842" id="{00BE00C8-0094-4FD0-A94B-00FC004700E6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16148,7 +16148,7 @@
           <xm:sqref>U154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="841" id="{00B80028-0069-46EB-80AA-00DC00180008}">
+          <x14:cfRule type="dataBar" priority="841" id="{0042000C-00E3-42BB-9FE7-000500BC006A}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16158,7 +16158,7 @@
           <xm:sqref>U154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="840" id="{003C00B9-0090-49B4-9081-000D004A00AA}">
+          <x14:cfRule type="dataBar" priority="840" id="{004B0000-008A-400F-A9C8-006200D60076}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16170,7 +16170,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="839" id="{00B800B1-00B4-4AB2-BFBE-009500A00009}">
+          <x14:cfRule type="dataBar" priority="839" id="{0033008C-00A7-4F4D-8C41-0043003400B6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16182,7 +16182,7 @@
           <xm:sqref>F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="838" id="{00720051-0010-426A-8B4F-0059006300FA}">
+          <x14:cfRule type="dataBar" priority="838" id="{0087007C-009B-4A1D-BD46-00D3008900EE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16194,7 +16194,7 @@
           <xm:sqref>N149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="837" id="{004100CB-00B9-4B97-B917-0091002D0028}">
+          <x14:cfRule type="dataBar" priority="837" id="{00DA0055-0071-4364-9EF2-006500810057}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16206,7 +16206,7 @@
           <xm:sqref>F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="836" id="{007200F5-0057-4469-922F-009D00D90004}">
+          <x14:cfRule type="dataBar" priority="836" id="{00F900A1-0009-4642-A2CE-000900B80047}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16218,7 +16218,7 @@
           <xm:sqref>N149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="835" id="{00390062-0027-4D3E-B63E-0076008A00F7}">
+          <x14:cfRule type="dataBar" priority="835" id="{007900BE-0096-4D8B-913C-000900E4003E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16230,7 +16230,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="834" id="{00F30067-00A2-41CB-BD13-005100BB008A}">
+          <x14:cfRule type="dataBar" priority="834" id="{008300C3-00B4-432C-AAD8-00380091001F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16242,7 +16242,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="833" id="{00B600A7-00D1-4CB2-94AE-000600F800CF}">
+          <x14:cfRule type="dataBar" priority="833" id="{00E10075-00EC-4A99-AE50-009600280036}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16254,7 +16254,7 @@
           <xm:sqref>F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="832" id="{00930086-0063-409C-9CBB-006E004500AA}">
+          <x14:cfRule type="dataBar" priority="832" id="{00C500DF-00D9-4387-9583-0037007E00A4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16266,7 +16266,7 @@
           <xm:sqref>N149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="831" id="{00AD0065-009E-4F23-BEBC-003C00FC00ED}">
+          <x14:cfRule type="dataBar" priority="831" id="{009E00C2-000E-457F-B180-005000E900BD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16278,7 +16278,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="830" id="{00270017-0009-4D58-B948-00A200B60059}">
+          <x14:cfRule type="dataBar" priority="830" id="{00E5004F-009D-49AF-9E64-00DA00FA009F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16290,7 +16290,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="829" id="{00990069-0035-49EF-9942-008E001D0001}">
+          <x14:cfRule type="dataBar" priority="829" id="{0075003F-00F4-49D1-9B60-007F00E500C5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16302,7 +16302,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="828" id="{002900A9-0033-463B-8E3F-00AD00D8007A}">
+          <x14:cfRule type="dataBar" priority="828" id="{000D00BF-003B-4C50-B1C1-005C00770072}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16314,7 +16314,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="827" id="{00DE00FF-00BA-4284-81B5-005500E6002F}">
+          <x14:cfRule type="dataBar" priority="827" id="{00BE0041-0019-411E-B23B-005600100024}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16326,7 +16326,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="826" id="{00AC00EF-001A-43AA-9D38-000200A10070}">
+          <x14:cfRule type="dataBar" priority="826" id="{007D00A7-00D8-44B8-89B2-0089001B0013}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16338,7 +16338,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="825" id="{002D00C0-00C9-4CB3-88CB-005F007D0037}">
+          <x14:cfRule type="dataBar" priority="825" id="{008E0005-001B-401B-A10D-00DC002700BE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16350,7 +16350,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="824" id="{00CF0005-00ED-4BA0-9A59-0044006D00A1}">
+          <x14:cfRule type="dataBar" priority="824" id="{00C100F0-0047-4E9C-8040-008800610092}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16362,7 +16362,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="823" id="{00840036-0020-4214-85A8-0021005A00D3}">
+          <x14:cfRule type="dataBar" priority="823" id="{00730034-00A6-455F-94B4-006400460057}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16374,7 +16374,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="822" id="{008A0018-003C-4252-87E4-004C003800C2}">
+          <x14:cfRule type="dataBar" priority="822" id="{005400F7-00DD-4C96-A376-003500BD00C1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16386,7 +16386,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="821" id="{00E2009A-0070-4041-BF0C-00B0007800B9}">
+          <x14:cfRule type="dataBar" priority="821" id="{008100AD-00E8-4BEF-A76F-00E300D30004}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16398,7 +16398,7 @@
           <xm:sqref>T149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="820" id="{009F004C-00C4-40CB-B7DA-00BE00DE00DD}">
+          <x14:cfRule type="dataBar" priority="820" id="{00D400A7-0054-4C7D-9273-006400350049}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16410,7 +16410,7 @@
           <xm:sqref>T149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="819" id="{005000B7-002D-408E-A706-00F7006D001E}">
+          <x14:cfRule type="dataBar" priority="819" id="{0073006D-007E-4FB1-BFBF-004A000B009A}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16420,7 +16420,7 @@
           <xm:sqref>T149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="818" id="{00F90042-00D5-4940-971F-00BC00040065}">
+          <x14:cfRule type="dataBar" priority="818" id="{00830026-00E4-4B7F-AE48-00ED00A2003C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16432,7 +16432,7 @@
           <xm:sqref>U149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="817" id="{00400070-0000-4663-81D9-006600F2004D}">
+          <x14:cfRule type="dataBar" priority="817" id="{003B0028-0050-46F2-9F1F-00A3000900B8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16444,7 +16444,7 @@
           <xm:sqref>U149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="816" id="{00110048-000A-44F2-A426-00BE002E00DE}">
+          <x14:cfRule type="dataBar" priority="816" id="{007B00D7-00C8-41E0-A4B9-0021008C0086}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16454,7 +16454,7 @@
           <xm:sqref>U149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="814" id="{00D20056-00FB-446C-B743-0044003F0078}">
+          <x14:cfRule type="dataBar" priority="814" id="{00DC00F8-00E2-45A0-9014-0075002200D4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16466,7 +16466,7 @@
           <xm:sqref>F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="813" id="{00340039-00CC-4CE7-A8D0-008A001200FF}">
+          <x14:cfRule type="dataBar" priority="813" id="{00820087-00D4-49CA-A5CD-00AE00E50084}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16478,7 +16478,7 @@
           <xm:sqref>N151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="812" id="{007D0062-0032-449F-BBFA-00C2009F00BE}">
+          <x14:cfRule type="dataBar" priority="812" id="{0001000B-0051-467B-943C-0029002A00DE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16490,7 +16490,7 @@
           <xm:sqref>F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="811" id="{00A20064-006F-4D2A-A3F5-002600200061}">
+          <x14:cfRule type="dataBar" priority="811" id="{00C90039-00DB-46F5-81AB-0004002D00DE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16502,7 +16502,7 @@
           <xm:sqref>N151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="808" id="{00A300ED-00FE-4CA4-94F2-00A800A800AE}">
+          <x14:cfRule type="dataBar" priority="808" id="{0015007A-0047-4790-A1F9-004F00AE00FD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16514,7 +16514,7 @@
           <xm:sqref>F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="807" id="{0001002D-001C-4643-AC27-00E300770011}">
+          <x14:cfRule type="dataBar" priority="807" id="{00DB0079-00A0-42FD-88C0-00190029002D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16526,7 +16526,7 @@
           <xm:sqref>N151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="790" id="{008300D7-0085-4122-B3D1-002300EF00BB}">
+          <x14:cfRule type="dataBar" priority="790" id="{00D10047-00B7-47F3-971D-00AB00A200CB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16538,7 +16538,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="789" id="{001B0072-003B-476C-9878-00D600FD00A5}">
+          <x14:cfRule type="dataBar" priority="789" id="{002400A3-00C9-4326-9A81-0090004B00E4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16550,7 +16550,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="788" id="{002A002B-0023-4619-AAEF-0036001A00E3}">
+          <x14:cfRule type="dataBar" priority="788" id="{0066001D-003C-4839-8FF5-00C200F20078}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16562,7 +16562,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="787" id="{00E500DE-004F-4F2A-B945-0022000E009A}">
+          <x14:cfRule type="dataBar" priority="787" id="{00A2003E-00D6-45D7-A7D9-005D00360065}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16574,7 +16574,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="786" id="{002B00E4-0016-4586-87B3-003F0001003F}">
+          <x14:cfRule type="dataBar" priority="786" id="{0085003D-002F-46A1-A336-00E800EA0078}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16586,7 +16586,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="785" id="{00D9009B-006D-48F5-BEC3-00FB00BA0013}">
+          <x14:cfRule type="dataBar" priority="785" id="{000F00C4-0001-4397-8DFC-005E00CD007A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16598,7 +16598,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="784" id="{008E00CA-008B-47F4-8C6A-006000D10087}">
+          <x14:cfRule type="dataBar" priority="784" id="{00280093-0035-4BC3-BBC8-0017008600F3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16610,7 +16610,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="783" id="{007B00A8-0049-4A3C-9FC1-006B00ED0099}">
+          <x14:cfRule type="dataBar" priority="783" id="{004000E4-00CA-40C7-9091-008B00F1006B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16622,7 +16622,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="782" id="{001100FD-00C0-49FD-9916-00DC00E7004B}">
+          <x14:cfRule type="dataBar" priority="782" id="{007500DA-00E9-4FFB-8DAE-00AC00CC00B4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16634,7 +16634,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="781" id="{00EC0049-002C-4B65-994E-009100F8007B}">
+          <x14:cfRule type="dataBar" priority="781" id="{002D005D-00DA-413A-AAC4-0016003800B7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16646,7 +16646,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="780" id="{00CF007F-0057-4535-A9B0-008D00AA00FD}">
+          <x14:cfRule type="dataBar" priority="780" id="{0015004C-00EE-49A9-9B93-005A00740061}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16658,7 +16658,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="779" id="{007E00FC-003B-4933-80FA-009200EA0044}">
+          <x14:cfRule type="dataBar" priority="779" id="{005600E6-003C-42A2-B5B1-005700D800DF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16670,7 +16670,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="778" id="{00140031-004D-4099-90F5-005000D90022}">
+          <x14:cfRule type="dataBar" priority="778" id="{00330079-0085-4D7C-9F01-00AB00920008}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16682,7 +16682,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="764" id="{00EB0096-00CE-4EEE-9B03-008500C20045}">
+          <x14:cfRule type="dataBar" priority="764" id="{00CB0025-00DE-416A-9F2E-0081008F00BD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16694,7 +16694,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="763" id="{00BF007D-005B-4F7B-9CB8-00DC00230078}">
+          <x14:cfRule type="dataBar" priority="763" id="{004C0011-003B-436D-9333-00EF007F0052}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16706,7 +16706,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="762" id="{006D00F7-003D-434A-976D-0040000F0045}">
+          <x14:cfRule type="dataBar" priority="762" id="{00AD000B-00D9-4AA4-B61A-00F300680013}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16718,7 +16718,7 @@
           <xm:sqref>N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="746" id="{00D900C4-00BE-4C94-8A90-008D00470016}">
+          <x14:cfRule type="dataBar" priority="746" id="{00F9001B-002A-413B-AF7D-00B100B6006C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16730,7 +16730,7 @@
           <xm:sqref>F160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="742" id="{00900059-0019-4817-86E9-008300490080}">
+          <x14:cfRule type="dataBar" priority="742" id="{00CC00EF-0015-467A-8544-00F0009C00BA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16742,7 +16742,7 @@
           <xm:sqref>F160:F162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="738" id="{00D50077-00BB-4F90-ABE5-003E0035003D}">
+          <x14:cfRule type="dataBar" priority="738" id="{002D004F-00D9-4D19-98E0-00C800DE0095}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16754,7 +16754,7 @@
           <xm:sqref>F160:F163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="734" id="{000B0082-0044-4DF5-A652-004D00B800CA}">
+          <x14:cfRule type="dataBar" priority="734" id="{00870093-00EE-441B-9257-00E200420042}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16766,7 +16766,7 @@
           <xm:sqref>T154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="733" id="{004D00F8-007E-46CD-83A5-00BA000F008B}">
+          <x14:cfRule type="dataBar" priority="733" id="{002900D9-008A-4A6F-A586-006F004400A4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16778,7 +16778,7 @@
           <xm:sqref>T154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="732" id="{00D2006F-0014-4795-8C53-00BB007B00C7}">
+          <x14:cfRule type="dataBar" priority="732" id="{0074006D-003C-41DF-A033-004D00C90026}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16788,7 +16788,7 @@
           <xm:sqref>T154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="731" id="{003200AE-0001-4268-A2F9-008A00AD0049}">
+          <x14:cfRule type="dataBar" priority="731" id="{00510060-00C5-420F-9714-00760035001A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16800,7 +16800,7 @@
           <xm:sqref>T160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="730" id="{00CB00B9-00C9-4E40-99DD-004700FB00B9}">
+          <x14:cfRule type="dataBar" priority="730" id="{00D500AA-00CB-4431-BFE8-003700430007}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16812,7 +16812,7 @@
           <xm:sqref>T160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="729" id="{00BA00F2-00E3-4BF2-A6E3-00EB007400D8}">
+          <x14:cfRule type="dataBar" priority="729" id="{00CB00A7-008E-47A4-89C7-00B5001A000F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16822,7 +16822,7 @@
           <xm:sqref>T160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="728" id="{000A00C6-0008-45C1-A633-009900AD005F}">
+          <x14:cfRule type="dataBar" priority="728" id="{004A00AB-00D8-4F30-9C26-006B00F40058}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16834,7 +16834,7 @@
           <xm:sqref>T159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="727" id="{000B004F-0091-4D51-8CAA-00E3005000B5}">
+          <x14:cfRule type="dataBar" priority="727" id="{00EE006E-00DE-49E7-839F-007E0021000E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16846,7 +16846,7 @@
           <xm:sqref>T159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="726" id="{00390098-0073-4060-AF5A-00B90097008D}">
+          <x14:cfRule type="dataBar" priority="726" id="{00800028-00BC-4C70-B85A-001100A50021}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16856,7 +16856,7 @@
           <xm:sqref>T159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="716" id="{00C60093-00D1-4C67-A4AE-00DE008300E7}">
+          <x14:cfRule type="dataBar" priority="716" id="{00C40045-00A6-426C-AA97-00FE00DD00D6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16868,7 +16868,7 @@
           <xm:sqref>U154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="715" id="{00E9004A-0080-4234-A0F3-00BA002C007E}">
+          <x14:cfRule type="dataBar" priority="715" id="{00970015-00A6-4489-9655-00FB00B1009A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16880,7 +16880,7 @@
           <xm:sqref>U154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="713" id="{004C002C-0056-4FBF-8DD8-0006002E00D0}">
+          <x14:cfRule type="dataBar" priority="713" id="{0093009D-0022-4172-9ED9-00B4009300C7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16892,7 +16892,7 @@
           <xm:sqref>U160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="712" id="{00400086-00B2-4D59-AC34-001900E600ED}">
+          <x14:cfRule type="dataBar" priority="712" id="{004000B8-000E-446A-A150-00E600AE00C8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16904,7 +16904,7 @@
           <xm:sqref>U160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="711" id="{00B40062-00AD-4536-AD4F-001900650035}">
+          <x14:cfRule type="dataBar" priority="711" id="{00F7001B-0000-465D-913E-00BB00B700EB}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16914,7 +16914,7 @@
           <xm:sqref>U160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="710" id="{006C00F7-003F-4A9C-B32B-00F4001C00D9}">
+          <x14:cfRule type="dataBar" priority="710" id="{008400D2-00D8-4DBC-B76C-00C2001600B1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16926,7 +16926,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="709" id="{00410079-00BA-4D54-AB9E-008E00FE006D}">
+          <x14:cfRule type="dataBar" priority="709" id="{00710071-00CF-40A9-BE7F-00320087006B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -16938,7 +16938,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="708" id="{007A0039-0015-4C44-9D33-008E009200A0}">
+          <x14:cfRule type="dataBar" priority="708" id="{00500029-0062-4165-B816-00AA0057007E}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16948,7 +16948,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="701" id="{00D90064-0079-4A00-B9D3-00160053007A}">
+          <x14:cfRule type="dataBar" priority="701" id="{0096006E-00C3-4CE4-818B-00A800E40019}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16958,7 +16958,7 @@
           <xm:sqref>N148:N149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="699" id="{0005009E-00DF-4898-8019-00E700590095}">
+          <x14:cfRule type="dataBar" priority="699" id="{0074001A-00A3-4008-A818-00D1003000DA}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16968,7 +16968,7 @@
           <xm:sqref>F148:F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="697" id="{00870072-00AA-43E7-BFE2-0031002C00DD}">
+          <x14:cfRule type="dataBar" priority="697" id="{009A0045-00C2-431C-AABA-0051004D002A}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -16980,7 +16980,7 @@
           <xm:sqref>F148:F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="696" id="{008F00FB-00BA-4A15-9AE5-00810000003D}">
+          <x14:cfRule type="dataBar" priority="696" id="{006B00CF-00AC-4552-9E9A-008300EF0019}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -16992,7 +16992,7 @@
           <xm:sqref>F148:F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="694" id="{002000E7-00A4-4D8B-A1AD-003F0012000D}">
+          <x14:cfRule type="dataBar" priority="694" id="{0014000A-0050-4E3A-AE40-00E200770090}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -17004,7 +17004,7 @@
           <xm:sqref>F148:F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="690" id="{008A009A-00F1-4CAD-9C4E-005200CE00FD}">
+          <x14:cfRule type="dataBar" priority="690" id="{00A900FD-00C5-4A7F-A5BE-00AB00DB0080}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -17016,7 +17016,7 @@
           <xm:sqref>N148:N149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="637" id="{00B3008C-002D-4576-8B8B-00BB00CB001D}">
+          <x14:cfRule type="dataBar" priority="637" id="{002A00C9-00C3-4111-8C26-007D004E0012}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17026,7 +17026,7 @@
           <xm:sqref>N148:N149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="636" id="{00D500D3-0030-45C7-B927-0034000D002E}">
+          <x14:cfRule type="dataBar" priority="636" id="{00880070-0078-4BF8-9C17-00A9004C00B2}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17036,7 +17036,7 @@
           <xm:sqref>T148:T149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="635" id="{00B300ED-00C9-47B6-97A8-00E200120042}">
+          <x14:cfRule type="dataBar" priority="635" id="{0022003E-0007-47A2-858B-00FD005200EF}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17046,7 +17046,7 @@
           <xm:sqref>U148:U149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="634" id="{004E00D0-00E2-4131-84F0-004800400098}">
+          <x14:cfRule type="dataBar" priority="634" id="{00C1000B-00A8-45AE-AAED-00AB00E900E3}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17056,7 +17056,7 @@
           <xm:sqref>U148:U149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="632" id="{00E700D7-00DF-44B9-A24A-0053008B00AE}">
+          <x14:cfRule type="dataBar" priority="632" id="{00FE0032-00B9-4F4C-9772-00F0008900F7}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17066,7 +17066,7 @@
           <xm:sqref>F148:F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="631" id="{007D0088-00FD-453B-9306-002A000B00EC}">
+          <x14:cfRule type="dataBar" priority="631" id="{00420087-0073-4453-AFE8-000300DB0006}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17078,7 +17078,7 @@
           <xm:sqref>S150 S157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="630" id="{00CC007A-0038-4834-91B6-004A006B0010}">
+          <x14:cfRule type="dataBar" priority="630" id="{006E0089-00AA-428B-92E2-006C008400C5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17090,7 +17090,7 @@
           <xm:sqref>F150 F157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="629" id="{005300F7-00E2-46A5-976E-001200C20078}">
+          <x14:cfRule type="dataBar" priority="629" id="{00D40002-00DC-4DDD-99A3-00D000350093}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17102,7 +17102,7 @@
           <xm:sqref>N150 N157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="610" id="{0015000D-004E-4029-9943-0077004A006D}">
+          <x14:cfRule type="dataBar" priority="610" id="{00B200AF-000F-40AC-B447-00DC00F20065}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17114,7 +17114,7 @@
           <xm:sqref>S164:S167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="609" id="{00450012-0051-4135-95EE-00C900380059}">
+          <x14:cfRule type="dataBar" priority="609" id="{00EA0080-0037-4A25-A73E-00B000B200EA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17126,7 +17126,7 @@
           <xm:sqref>F164:F167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="608" id="{000D00BD-0086-4695-B77C-000C005D00BC}">
+          <x14:cfRule type="dataBar" priority="608" id="{002900B5-00DB-4E96-A0B6-005100EC00BB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17138,7 +17138,7 @@
           <xm:sqref>N164:N167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="607" id="{001F0040-00AD-45B1-9EB6-00B600CF0048}">
+          <x14:cfRule type="dataBar" priority="607" id="{00C700C2-006D-4662-8FD3-006B00860010}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17150,7 +17150,7 @@
           <xm:sqref>F163:F167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="606" id="{005F0037-0053-4605-B1CD-004500B700F8}">
+          <x14:cfRule type="dataBar" priority="606" id="{009800BE-0027-41AD-B460-0078009E0060}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17162,7 +17162,7 @@
           <xm:sqref>F165</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="605" id="{000E0006-0006-4F51-AC5D-00F40000008B}">
+          <x14:cfRule type="dataBar" priority="605" id="{006100EA-0056-45A6-BC98-00D6006E00DA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17174,7 +17174,7 @@
           <xm:sqref>U158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="604" id="{00E00005-00BC-4798-9438-00FF00120063}">
+          <x14:cfRule type="dataBar" priority="604" id="{00260003-005E-4D16-A6D8-00A8003B0043}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17186,7 +17186,7 @@
           <xm:sqref>U158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="603" id="{0061005C-000E-4369-92D5-00CE00BB008C}">
+          <x14:cfRule type="dataBar" priority="603" id="{003B000D-00D6-4ADB-8D08-0014006E00E4}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17196,7 +17196,7 @@
           <xm:sqref>U158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="602" id="{0080002A-00B9-48F5-9813-008200A200C6}">
+          <x14:cfRule type="dataBar" priority="602" id="{008600BA-0005-41AC-8BAA-004700850074}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17208,7 +17208,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="601" id="{00880019-0046-4325-920D-0040001E00B9}">
+          <x14:cfRule type="dataBar" priority="601" id="{0029007B-0070-48E6-B599-008600900074}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17220,7 +17220,7 @@
           <xm:sqref>F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="600" id="{006000D1-0086-4BD4-AEF3-008100180058}">
+          <x14:cfRule type="dataBar" priority="600" id="{006600E8-0006-4282-B035-0003002400AB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17232,7 +17232,7 @@
           <xm:sqref>N151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="599" id="{0073000C-00FA-41AD-B8D2-009E009F0042}">
+          <x14:cfRule type="dataBar" priority="599" id="{0047008B-00B9-4FD2-922A-00AC00FC0074}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17244,7 +17244,7 @@
           <xm:sqref>F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="598" id="{00010011-0069-4A48-9F03-003F008E009C}">
+          <x14:cfRule type="dataBar" priority="598" id="{004C0071-0023-44D8-B4E7-006900D2003E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17256,7 +17256,7 @@
           <xm:sqref>N151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="597" id="{00F10035-0025-4F98-B379-000C00520088}">
+          <x14:cfRule type="dataBar" priority="597" id="{001200C3-00E1-4467-AB75-006600F700B3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17268,7 +17268,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="596" id="{007F0072-00B2-4B3D-9C77-00E100B6003D}">
+          <x14:cfRule type="dataBar" priority="596" id="{004000ED-00BD-43CC-90C9-00D400C60005}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17280,7 +17280,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="595" id="{00A70072-0036-450B-BF82-002A00100051}">
+          <x14:cfRule type="dataBar" priority="595" id="{009000D3-001A-4B52-9B9A-008F009900B9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17292,7 +17292,7 @@
           <xm:sqref>F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="594" id="{00A3000E-004A-4D1B-B2F2-003900B100C4}">
+          <x14:cfRule type="dataBar" priority="594" id="{00120011-00EC-4C5F-A584-007B003C00ED}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17304,7 +17304,7 @@
           <xm:sqref>N151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="593" id="{007D0026-0085-4E40-98B3-0050001A009C}">
+          <x14:cfRule type="dataBar" priority="593" id="{005E005C-006E-4D58-B321-00AB007700E3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17316,7 +17316,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="592" id="{000B00F8-0002-4BBA-8196-008F0007003C}">
+          <x14:cfRule type="dataBar" priority="592" id="{00A70040-00D3-4EEE-BC8D-00E500310034}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17328,7 +17328,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="591" id="{001C00C5-007D-4C58-9E3D-000A00220012}">
+          <x14:cfRule type="dataBar" priority="591" id="{00D7004F-0006-41EA-80B0-003300D0006C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17340,7 +17340,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="590" id="{00E500EC-0037-4848-A37E-002900FE002E}">
+          <x14:cfRule type="dataBar" priority="590" id="{009900B3-00AD-49B6-8C17-009C00CA0042}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17352,7 +17352,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="589" id="{00FE000F-0040-43C2-8617-001A003C0051}">
+          <x14:cfRule type="dataBar" priority="589" id="{000200DB-0040-40CD-B59F-00E3005F0024}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17364,7 +17364,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="588" id="{00B3000D-006F-4BA0-BED2-0077009E0047}">
+          <x14:cfRule type="dataBar" priority="588" id="{00000006-0043-4F93-8D59-000200C00071}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17376,7 +17376,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="587" id="{00C30005-0095-4D94-8FC6-00D000170091}">
+          <x14:cfRule type="dataBar" priority="587" id="{008300D5-000E-4640-A285-00BF003A0013}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17388,7 +17388,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="586" id="{00B700C1-00F9-4565-830D-000C002E0093}">
+          <x14:cfRule type="dataBar" priority="586" id="{00430029-00D8-421F-B83C-0024007100D9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17400,7 +17400,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="585" id="{006200F5-0057-4F1B-88C4-004800DB0035}">
+          <x14:cfRule type="dataBar" priority="585" id="{00BD0006-009B-4C4C-898C-00C0000C0037}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17412,7 +17412,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="584" id="{006C0049-0071-4ADB-AB85-0064006C00F6}">
+          <x14:cfRule type="dataBar" priority="584" id="{005F00EF-0023-4A4C-A916-001C0009005C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17424,7 +17424,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="583" id="{004300E0-005B-46AF-93E3-0055001A0088}">
+          <x14:cfRule type="dataBar" priority="583" id="{00960020-0031-48BD-AC70-005C00AE005D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17436,7 +17436,7 @@
           <xm:sqref>T151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="582" id="{001B00A6-00E0-4CE5-B8D7-001F00EC0089}">
+          <x14:cfRule type="dataBar" priority="582" id="{00540005-004E-421D-A2C6-0025004500A3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17448,7 +17448,7 @@
           <xm:sqref>T151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="581" id="{003C0038-0008-4F46-AA97-001200EE00BB}">
+          <x14:cfRule type="dataBar" priority="581" id="{00BD0065-005F-4761-9F16-005800C6005B}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17458,7 +17458,7 @@
           <xm:sqref>T151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="580" id="{009600BC-001C-420D-93CA-00D2009C0074}">
+          <x14:cfRule type="dataBar" priority="580" id="{00010013-009C-4FA4-AFBF-00AD00810068}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17470,7 +17470,7 @@
           <xm:sqref>U151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="579" id="{00F60028-0093-4D6D-A6F3-00B300120036}">
+          <x14:cfRule type="dataBar" priority="579" id="{0044009E-00BF-4CA1-BF21-009F006F004B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17482,7 +17482,7 @@
           <xm:sqref>U151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="578" id="{00E20080-008B-4427-9C95-00E50047007F}">
+          <x14:cfRule type="dataBar" priority="578" id="{006D0075-000B-4412-8BD5-000600C30004}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17492,7 +17492,7 @@
           <xm:sqref>U151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="571" id="{000F00FC-00F1-499A-AD00-00B80092007A}">
+          <x14:cfRule type="dataBar" priority="571" id="{009500F0-0079-432D-940D-001400CE00D1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17504,7 +17504,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="570" id="{00200031-001B-4AEA-9CF3-005F00CE008D}">
+          <x14:cfRule type="dataBar" priority="570" id="{008500A1-005C-483A-834D-0049009D00FB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17516,7 +17516,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="569" id="{00F60091-002E-4A77-ADF5-000600E4002D}">
+          <x14:cfRule type="dataBar" priority="569" id="{000400B0-002B-4DFF-8E9D-008D004000CB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17528,7 +17528,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="568" id="{007C0080-00DB-4502-B462-005B00760076}">
+          <x14:cfRule type="dataBar" priority="568" id="{0093006D-009B-4DC2-975B-002500B600EE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17540,7 +17540,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="567" id="{00B70017-0038-4529-9322-003C0038006E}">
+          <x14:cfRule type="dataBar" priority="567" id="{00F6002B-00B7-4DFB-BDD9-00C600820069}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17552,7 +17552,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="566" id="{00BF0011-0083-4792-942B-005200760006}">
+          <x14:cfRule type="dataBar" priority="566" id="{009B0013-0037-41D0-B836-009600740054}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17564,7 +17564,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="565" id="{00BC00D4-00EB-4F46-A3A7-005A00170067}">
+          <x14:cfRule type="dataBar" priority="565" id="{00BA007A-00B8-49CB-862D-000800A00077}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17576,7 +17576,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="564" id="{007900DF-00D9-480B-9F1F-005900300061}">
+          <x14:cfRule type="dataBar" priority="564" id="{00A400C4-0028-4D3B-B860-00BA00A0006F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17588,7 +17588,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="563" id="{005A00F2-0099-4753-8E5F-0082001B0012}">
+          <x14:cfRule type="dataBar" priority="563" id="{0096009C-0065-4242-A3FC-003A008B00AA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17600,7 +17600,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="562" id="{002E0061-005C-45C7-8FC1-004B00440010}">
+          <x14:cfRule type="dataBar" priority="562" id="{00E00044-0038-4469-9CE1-0025003200D9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17612,7 +17612,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="561" id="{00080076-00E1-43A6-AEE1-000C00BB0074}">
+          <x14:cfRule type="dataBar" priority="561" id="{0074005E-00D1-4F05-8B79-0056004C00D9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17624,7 +17624,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="560" id="{00BB0096-004B-4DA9-B902-006B00CF0011}">
+          <x14:cfRule type="dataBar" priority="560" id="{00EB0050-0069-4241-AC77-00A500190071}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17636,7 +17636,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="559" id="{00C10014-00E9-42B1-9216-00F600180066}">
+          <x14:cfRule type="dataBar" priority="559" id="{00C800CD-002C-4CEF-908D-0090008A00F4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17648,7 +17648,7 @@
           <xm:sqref>S151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="558" id="{002F0023-00C5-43BB-BB88-0063005F002D}">
+          <x14:cfRule type="dataBar" priority="558" id="{000300A7-00B5-452A-88DE-007100F2005E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17660,7 +17660,7 @@
           <xm:sqref>S158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="557" id="{0022002F-005F-4E11-8494-00E900300080}">
+          <x14:cfRule type="dataBar" priority="557" id="{0040007B-0006-4ECF-8AC4-00A800FE0002}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17672,7 +17672,7 @@
           <xm:sqref>F158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="556" id="{004C0093-00D4-42E5-9181-003E009A002F}">
+          <x14:cfRule type="dataBar" priority="556" id="{007E004B-003C-4C89-933C-00EC0020001F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17684,7 +17684,7 @@
           <xm:sqref>N158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="555" id="{00A0005F-001A-4572-97E8-0006008900EC}">
+          <x14:cfRule type="dataBar" priority="555" id="{0067007D-0081-4608-9FA3-00B400DC00C6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17696,7 +17696,7 @@
           <xm:sqref>S158:S160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="554" id="{00080064-00B8-4A88-B7F9-009500C30079}">
+          <x14:cfRule type="dataBar" priority="554" id="{00A500A1-00D6-4BA3-83B5-002E00EE0073}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17708,7 +17708,7 @@
           <xm:sqref>F158:F160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="553" id="{00DC001B-005E-4CAD-930C-002F004D00E8}">
+          <x14:cfRule type="dataBar" priority="553" id="{006F00E3-0027-4350-A9B6-00AC004900D4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17720,7 +17720,7 @@
           <xm:sqref>N158:N160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="552" id="{001B002A-0047-4E2E-ACA0-00B4005A00F9}">
+          <x14:cfRule type="dataBar" priority="552" id="{00D1004F-001B-410B-875E-00D000CF0047}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17732,7 +17732,7 @@
           <xm:sqref>S158:S161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="551" id="{00C300E3-0018-4A4A-8A04-00B9003000D0}">
+          <x14:cfRule type="dataBar" priority="551" id="{00F80067-0003-4A85-AC81-0086000300F7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17744,7 +17744,7 @@
           <xm:sqref>F158:F161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="550" id="{0019006C-005C-4430-9F99-00F8007800DB}">
+          <x14:cfRule type="dataBar" priority="550" id="{003F003A-0038-496B-B241-0096009500F1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17756,7 +17756,7 @@
           <xm:sqref>N158:N161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="549" id="{00F30032-002E-41FA-BB40-0012009B00A9}">
+          <x14:cfRule type="dataBar" priority="549" id="{00550041-00C5-4D0E-8B4E-00E200E60081}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17768,7 +17768,7 @@
           <xm:sqref>F163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="548" id="{00FE00D1-00FC-482D-A85D-00D100E60088}">
+          <x14:cfRule type="dataBar" priority="548" id="{00240070-0075-492C-B968-002600110094}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17780,7 +17780,7 @@
           <xm:sqref>F163:F165</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="547" id="{007E003A-0024-47A3-B4E0-0041008A002C}">
+          <x14:cfRule type="dataBar" priority="547" id="{00EA00F6-008B-4AF9-B1A7-002400F60079}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17792,7 +17792,7 @@
           <xm:sqref>F163:F167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="546" id="{003800E5-004E-4D8E-97A0-00E20032009C}">
+          <x14:cfRule type="dataBar" priority="546" id="{004600CB-00B9-4DC5-A047-007F008D0020}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17804,7 +17804,7 @@
           <xm:sqref>T159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="545" id="{00AE00D6-00C1-4A26-899B-008E00F800E9}">
+          <x14:cfRule type="dataBar" priority="545" id="{00080003-0059-4773-B84E-001800AE009F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17816,7 +17816,7 @@
           <xm:sqref>T159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="544" id="{00D000D3-0036-45A4-AD29-006400A800A7}">
+          <x14:cfRule type="dataBar" priority="544" id="{001800BA-0018-439F-9D98-00A70029006A}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17826,7 +17826,7 @@
           <xm:sqref>T159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="543" id="{00D400E2-0082-4738-AA94-0047001400C0}">
+          <x14:cfRule type="dataBar" priority="543" id="{008A00F2-000C-4F69-8482-001600DE000E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17838,7 +17838,7 @@
           <xm:sqref>T158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="542" id="{00FB007B-0086-4212-805D-00A000C400B4}">
+          <x14:cfRule type="dataBar" priority="542" id="{00CA00A5-00E1-4B2A-872C-001600710099}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17850,7 +17850,7 @@
           <xm:sqref>T158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="541" id="{00720052-00B5-4BCA-8D83-00DF0009007E}">
+          <x14:cfRule type="dataBar" priority="541" id="{0080000B-007A-4E16-A372-007700BD008F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17860,7 +17860,7 @@
           <xm:sqref>T158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="540" id="{00AD00D2-001A-46EC-A9BC-004700B6005D}">
+          <x14:cfRule type="dataBar" priority="540" id="{00D9005B-00D1-44CA-AB7F-001600B200A4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17872,7 +17872,7 @@
           <xm:sqref>T163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="539" id="{0050003A-00F2-489B-9922-00100019002E}">
+          <x14:cfRule type="dataBar" priority="539" id="{001700A3-00D3-427D-9155-00E1007100AF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17884,7 +17884,7 @@
           <xm:sqref>T163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="538" id="{00DE00C4-000E-4A60-BB96-009300DA00B6}">
+          <x14:cfRule type="dataBar" priority="538" id="{002A0039-001A-409A-8CDC-007500B90045}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17894,7 +17894,7 @@
           <xm:sqref>T163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="537" id="{00B60054-00D4-4E58-BB8F-008200A30017}">
+          <x14:cfRule type="dataBar" priority="537" id="{00CF006D-0038-422B-B86D-002D00B100D7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17906,7 +17906,7 @@
           <xm:sqref>T162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="536" id="{00E30024-0089-4CB5-8AD3-00B7009B008B}">
+          <x14:cfRule type="dataBar" priority="536" id="{0004008E-006D-4E55-BD19-0012008400EA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17918,7 +17918,7 @@
           <xm:sqref>T162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="535" id="{00DE008E-0083-4827-A131-0049003500A3}">
+          <x14:cfRule type="dataBar" priority="535" id="{00870073-00C0-4542-B697-001D006F00DE}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17928,7 +17928,7 @@
           <xm:sqref>T162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="534" id="{0047009C-006A-472F-BE3F-00A60021005D}">
+          <x14:cfRule type="dataBar" priority="534" id="{00DA003E-0030-4A03-BC1D-00F700E80079}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17940,7 +17940,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="533" id="{007E001C-007D-4CF3-944B-0029001F000D}">
+          <x14:cfRule type="dataBar" priority="533" id="{008D00DC-0035-4BA3-8F08-00C8006B00E1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17952,7 +17952,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="532" id="{000000B0-001A-475D-912E-00F600D30018}">
+          <x14:cfRule type="dataBar" priority="532" id="{003B0013-00D0-455C-A4F1-004200EF00B9}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17962,7 +17962,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="531" id="{00D90055-00CD-487C-957E-003E00F9004F}">
+          <x14:cfRule type="dataBar" priority="531" id="{006A0009-000A-42F1-B1B7-00970030003F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17974,7 +17974,7 @@
           <xm:sqref>U158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="530" id="{00730065-0034-4A66-85EC-009700FB00EE}">
+          <x14:cfRule type="dataBar" priority="530" id="{001200D0-00BC-4E31-B598-007E000000F2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17986,7 +17986,7 @@
           <xm:sqref>U158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="529" id="{002300C5-00F5-490B-8523-00D9008E0053}">
+          <x14:cfRule type="dataBar" priority="529" id="{00870058-00FC-43CD-A342-001F00980027}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -17998,7 +17998,7 @@
           <xm:sqref>U163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="528" id="{00250026-00A0-44D5-B043-00F000BB00C9}">
+          <x14:cfRule type="dataBar" priority="528" id="{00AA0082-00A8-496B-9715-0095009A00EB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18010,7 +18010,7 @@
           <xm:sqref>U163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="527" id="{002000EE-00F1-4D31-8CA4-009C00640099}">
+          <x14:cfRule type="dataBar" priority="527" id="{00160034-0036-4523-8E60-002C001900D9}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18020,7 +18020,7 @@
           <xm:sqref>U163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="526" id="{000D00C6-00A3-45BA-A7B5-003E008600EC}">
+          <x14:cfRule type="dataBar" priority="526" id="{0097007A-00DB-4C6F-BFFD-000B00B30036}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18032,7 +18032,7 @@
           <xm:sqref>U162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="525" id="{005E005F-0018-4195-9DDD-0053009F0031}">
+          <x14:cfRule type="dataBar" priority="525" id="{008000C8-00B9-4295-BDC9-006100990073}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18044,7 +18044,7 @@
           <xm:sqref>U162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="524" id="{008800CE-00AA-49EF-9AD1-0084004F00D3}">
+          <x14:cfRule type="dataBar" priority="524" id="{00DF0069-004A-4406-AF2D-00C8005D0054}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18054,7 +18054,7 @@
           <xm:sqref>U162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="523" id="{00470060-008B-4F5B-80CD-009D006A000E}">
+          <x14:cfRule type="dataBar" priority="523" id="{0002009D-00DD-4FCC-B316-00A900960064}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18064,7 +18064,7 @@
           <xm:sqref>N150:N151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="522" id="{007200D8-0060-4141-BB7C-009A009E0011}">
+          <x14:cfRule type="dataBar" priority="522" id="{00F80097-00E4-4184-8E5B-006A00A90090}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18076,7 +18076,7 @@
           <xm:sqref>N150:N151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="521" id="{001800F2-000D-4144-9052-00AE002C00FF}">
+          <x14:cfRule type="dataBar" priority="521" id="{00060093-0001-4FB2-93B9-003900F8007D}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18086,7 +18086,7 @@
           <xm:sqref>F150:F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="520" id="{002F00D3-008F-4720-9BF7-00C10076005C}">
+          <x14:cfRule type="dataBar" priority="520" id="{000A0043-002E-4FA6-BB1D-00C5005B005E}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18098,7 +18098,7 @@
           <xm:sqref>F150:F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="519" id="{000D009B-00CF-43FB-9F68-006F007000F9}">
+          <x14:cfRule type="dataBar" priority="519" id="{005A0093-002F-4BCA-9700-009100EC00C4}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18110,7 +18110,7 @@
           <xm:sqref>F150:F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="518" id="{00950020-00B1-4695-85BE-00D80035006D}">
+          <x14:cfRule type="dataBar" priority="518" id="{005E0054-00F1-49E1-B2A9-005A00FD00D8}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18122,7 +18122,7 @@
           <xm:sqref>F150:F151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="517" id="{00370039-001C-48DB-960F-002900CE00DD}">
+          <x14:cfRule type="dataBar" priority="517" id="{00ED00A2-0005-428E-A2AA-0071008D00EA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18134,7 +18134,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="516" id="{008200E2-0055-4789-8C7C-008200FA0092}">
+          <x14:cfRule type="dataBar" priority="516" id="{005A0010-0095-4095-8B1A-005100670060}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18146,7 +18146,7 @@
           <xm:sqref>F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="515" id="{008D00CD-0072-4A20-AD21-00D6005100C5}">
+          <x14:cfRule type="dataBar" priority="515" id="{00A900A6-007D-49D1-BFFD-00EA00A20081}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18158,7 +18158,7 @@
           <xm:sqref>N152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="514" id="{003400D2-005B-4257-BFB2-003B00A600A7}">
+          <x14:cfRule type="dataBar" priority="514" id="{00DC00BA-005A-4AF2-8CF1-00050000007A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18170,7 +18170,7 @@
           <xm:sqref>F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="513" id="{00AA003B-008F-4617-8857-005500FB0029}">
+          <x14:cfRule type="dataBar" priority="513" id="{00910063-001A-4530-BF9E-0078002B00E7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18182,7 +18182,7 @@
           <xm:sqref>N152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="512" id="{00D70095-003F-4612-A3FA-005D00BD0089}">
+          <x14:cfRule type="dataBar" priority="512" id="{00CB0070-00A8-4549-B8BF-009700B40081}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18194,7 +18194,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="511" id="{0085003D-0065-42DE-857D-0097006C0090}">
+          <x14:cfRule type="dataBar" priority="511" id="{005300C4-00BC-4DD8-A694-0016005B004A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18206,7 +18206,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="510" id="{00FC0096-0094-42D3-BD42-00C20078000B}">
+          <x14:cfRule type="dataBar" priority="510" id="{000B008B-0068-4623-8EDF-00AE00C900BD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18218,7 +18218,7 @@
           <xm:sqref>F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="509" id="{00040051-003B-487A-AD12-000000EB0090}">
+          <x14:cfRule type="dataBar" priority="509" id="{009E0055-00E4-4C1D-9122-008100030094}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18230,7 +18230,7 @@
           <xm:sqref>N152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="508" id="{007D00E1-00AC-46ED-983B-001700AE00F8}">
+          <x14:cfRule type="dataBar" priority="508" id="{00DF00AD-0025-4995-A1F7-00B400ED0098}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18242,7 +18242,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="507" id="{00E8007C-006A-43DD-8672-002D00780018}">
+          <x14:cfRule type="dataBar" priority="507" id="{003D00AB-00BE-4180-A33E-00FA00C30080}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18254,7 +18254,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="506" id="{006300B1-00E0-46D3-BDA8-004A003E00E2}">
+          <x14:cfRule type="dataBar" priority="506" id="{005600B6-0077-4FC2-832C-00EC005A0087}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18266,7 +18266,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="505" id="{00E4004A-005C-4BEC-98FE-000A00B100CC}">
+          <x14:cfRule type="dataBar" priority="505" id="{00B30035-0070-401B-B43C-001B0037007A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18278,7 +18278,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="504" id="{00260075-00CF-470E-95D5-00EE0061000A}">
+          <x14:cfRule type="dataBar" priority="504" id="{008E00D1-0042-490E-A1AB-009500E9005D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18290,7 +18290,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="503" id="{00F0000E-0099-440D-BA9C-001D00A30048}">
+          <x14:cfRule type="dataBar" priority="503" id="{001100C3-0092-4989-B9CB-00E700CB0006}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18302,7 +18302,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="502" id="{0005000D-0057-4339-ABB6-00A5005800D7}">
+          <x14:cfRule type="dataBar" priority="502" id="{00A00005-0072-4F26-AB3C-00BC00AF00EC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18314,7 +18314,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="501" id="{007E00D9-0096-4B74-ABF2-004B00180008}">
+          <x14:cfRule type="dataBar" priority="501" id="{00EE0077-006C-4F91-BB39-0037002000A9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18326,7 +18326,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="500" id="{00DF002C-00EC-4E97-9BC4-007600C800F7}">
+          <x14:cfRule type="dataBar" priority="500" id="{005500F2-00B2-4E4F-AAE8-00E1000D0055}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18338,7 +18338,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="499" id="{00B9008C-0013-4AE2-9F46-00050049008F}">
+          <x14:cfRule type="dataBar" priority="499" id="{00580018-009E-486C-9462-00DB00D9007E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18350,7 +18350,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="498" id="{009100A9-0071-4789-AF92-00640032006B}">
+          <x14:cfRule type="dataBar" priority="498" id="{00EF0013-000D-4F46-A261-000700D4004D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18362,7 +18362,7 @@
           <xm:sqref>T152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="497" id="{0082007C-0060-4A8B-B557-008600F50089}">
+          <x14:cfRule type="dataBar" priority="497" id="{000C00AD-002B-4EB6-967A-00B3004A002D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18374,7 +18374,7 @@
           <xm:sqref>T152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="496" id="{006D009F-00B4-47DE-9882-008800F20028}">
+          <x14:cfRule type="dataBar" priority="496" id="{00BE00DD-0062-4840-90A6-0070008E0038}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18384,7 +18384,7 @@
           <xm:sqref>T152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="495" id="{00220098-0096-45B7-9F17-000A00A400FD}">
+          <x14:cfRule type="dataBar" priority="495" id="{00A40000-00DE-4A57-BAE9-00C600B8003C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18396,7 +18396,7 @@
           <xm:sqref>U152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="494" id="{00F700E3-0070-446E-AD39-00C700FC00C8}">
+          <x14:cfRule type="dataBar" priority="494" id="{004200E9-002B-4A15-A6E5-0018000800B3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18408,7 +18408,7 @@
           <xm:sqref>U152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="493" id="{00F10073-0071-4AC9-A489-00F500690065}">
+          <x14:cfRule type="dataBar" priority="493" id="{00FF0038-00AE-4BC7-9BDC-0001009C0076}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18418,7 +18418,7 @@
           <xm:sqref>U152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="492" id="{00AC00AF-0050-49AF-A6BF-00B100FB0063}">
+          <x14:cfRule type="dataBar" priority="492" id="{0047003B-0064-420B-BC6A-008700A8003C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18430,7 +18430,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="491" id="{001800CD-0023-4850-AE82-008B00B900F4}">
+          <x14:cfRule type="dataBar" priority="491" id="{00920018-00EF-4DDF-A779-00EF0001001C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18442,7 +18442,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="490" id="{006A0085-004D-4705-83AA-006A00940020}">
+          <x14:cfRule type="dataBar" priority="490" id="{00D1004F-0075-4B5B-94AB-008C003000F7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18454,7 +18454,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="489" id="{004F0071-00CE-44EB-9F66-005B007A00B6}">
+          <x14:cfRule type="dataBar" priority="489" id="{003A00D8-0036-46FE-8B6B-00FE00500011}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18466,7 +18466,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="488" id="{00660024-0040-4872-980D-0091002200C9}">
+          <x14:cfRule type="dataBar" priority="488" id="{00E00031-00F1-48C3-8123-00B6005F00DF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18478,7 +18478,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="487" id="{00F20062-00DF-46D2-9117-001100AF00FA}">
+          <x14:cfRule type="dataBar" priority="487" id="{00070064-006B-4D0F-A37A-0053002000F2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18490,7 +18490,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="486" id="{00D000E3-0006-4A19-AE76-008000CC0073}">
+          <x14:cfRule type="dataBar" priority="486" id="{007700C8-0062-4265-994E-001300F0009B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18502,7 +18502,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="485" id="{00D500BB-00C1-470C-8205-0050003E0080}">
+          <x14:cfRule type="dataBar" priority="485" id="{00DC00EA-0028-4AFD-B88B-005000C600B2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18514,7 +18514,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="484" id="{008600BD-0071-4E8C-AF25-004D004C00E4}">
+          <x14:cfRule type="dataBar" priority="484" id="{0085002B-00F7-4F92-8395-00C600A10088}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18526,7 +18526,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="483" id="{002100E5-0033-4AAD-A1B3-00D000CE0020}">
+          <x14:cfRule type="dataBar" priority="483" id="{0086002D-00BB-46EA-8B6B-0057007F0017}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18538,7 +18538,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="482" id="{00EC00E9-007C-466B-A69D-0099006500FF}">
+          <x14:cfRule type="dataBar" priority="482" id="{00560088-0045-44A3-8713-007D004100AC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18550,7 +18550,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="481" id="{00DE009B-0013-47FA-AA1F-0058003900BA}">
+          <x14:cfRule type="dataBar" priority="481" id="{008900E5-00F1-4A01-8501-000600D8000C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18562,7 +18562,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="480" id="{00790072-00F2-4A59-878A-003500E8005F}">
+          <x14:cfRule type="dataBar" priority="480" id="{00B900A9-0000-43A2-8728-00D400AB0092}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18574,7 +18574,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="479" id="{0075008F-0051-4B75-BBF9-006C004200C0}">
+          <x14:cfRule type="dataBar" priority="479" id="{006800EF-000D-45BC-BD13-00DF0000007F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18584,7 +18584,7 @@
           <xm:sqref>N152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="478" id="{005F000E-0077-41A5-AD4E-008E002800B6}">
+          <x14:cfRule type="dataBar" priority="478" id="{00BE0047-0002-46B2-86B4-0079006C004E}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18596,7 +18596,7 @@
           <xm:sqref>N152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="477" id="{00D80089-00C1-4D79-AB0B-0026006600B0}">
+          <x14:cfRule type="dataBar" priority="477" id="{00D10064-00AC-443F-AB68-00C7004E00DA}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18606,7 +18606,7 @@
           <xm:sqref>F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="476" id="{0070007D-0035-40B0-85BC-00C300BE00AA}">
+          <x14:cfRule type="dataBar" priority="476" id="{00B800B2-009F-4139-A775-00F500390057}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18618,7 +18618,7 @@
           <xm:sqref>F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="475" id="{00F00062-006D-443A-932C-00DE00E90078}">
+          <x14:cfRule type="dataBar" priority="475" id="{00EC00C3-0011-4A9E-9599-00210091009F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18630,7 +18630,7 @@
           <xm:sqref>F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="474" id="{0017009A-0020-4F67-B3B6-001200F00096}">
+          <x14:cfRule type="dataBar" priority="474" id="{001900ED-0025-4D3F-A75A-00DE003D007D}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18642,7 +18642,7 @@
           <xm:sqref>F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="473" id="{002C00D7-004B-4282-8FC2-00C200C00086}">
+          <x14:cfRule type="dataBar" priority="473" id="{00B70083-0059-4560-B76D-00F500B40073}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18652,7 +18652,7 @@
           <xm:sqref>F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="472" id="{00480029-00AC-4CD0-9F02-002F009B0009}">
+          <x14:cfRule type="dataBar" priority="472" id="{00B70083-0062-4918-ACF4-00B000790092}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18662,7 +18662,7 @@
           <xm:sqref>N152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="471" id="{000B00C0-0098-4975-863C-003600080095}">
+          <x14:cfRule type="dataBar" priority="471" id="{0033007F-00D6-40B6-B077-001300A500F4}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18672,7 +18672,7 @@
           <xm:sqref>S152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="470" id="{00790008-00E1-40F3-9D58-004600D20089}">
+          <x14:cfRule type="dataBar" priority="470" id="{00F6006C-0050-4682-B45F-0063005D0013}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18682,7 +18682,7 @@
           <xm:sqref>T152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="469" id="{001E004F-0050-4A15-BE31-007900CA00A1}">
+          <x14:cfRule type="dataBar" priority="469" id="{004D001D-002C-49BA-AE9F-00A800610005}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18694,7 +18694,7 @@
           <xm:sqref>T152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="467" id="{00C10004-0000-482B-9B9B-00D7007F00EB}">
+          <x14:cfRule type="dataBar" priority="467" id="{00240074-009C-4030-BFEC-001800CD00A5}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18704,7 +18704,7 @@
           <xm:sqref>N150:N152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="466" id="{005C0089-0050-4AD3-98F1-0090003A0008}">
+          <x14:cfRule type="dataBar" priority="466" id="{0071002A-0035-415E-B0C3-00B600870041}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18714,7 +18714,7 @@
           <xm:sqref>T150:T152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="465" id="{0052008F-0054-4EB1-B47A-004C00D00023}">
+          <x14:cfRule type="dataBar" priority="465" id="{00E3000B-0030-4ADE-924A-00C4008D0092}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18724,7 +18724,7 @@
           <xm:sqref>U150:U152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="464" id="{00440051-00C5-4559-9493-00760008001E}">
+          <x14:cfRule type="dataBar" priority="464" id="{00840098-0065-43DF-B4E8-004800B30091}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18734,7 +18734,7 @@
           <xm:sqref>U150:U152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="463" id="{00310031-0005-4729-A539-000000280044}">
+          <x14:cfRule type="dataBar" priority="463" id="{008E0087-00B6-474D-980A-004100B10033}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18744,7 +18744,7 @@
           <xm:sqref>F150:F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="462" id="{0035006E-0039-4F12-8196-00AF00C1003F}">
+          <x14:cfRule type="dataBar" priority="462" id="{0005000D-00AF-4773-A436-0085003D003D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18756,7 +18756,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="461" id="{002E000C-00DA-4B0F-9034-004B00BB0009}">
+          <x14:cfRule type="dataBar" priority="461" id="{009200FE-0025-4901-A6E1-001A00D1003D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18768,7 +18768,7 @@
           <xm:sqref>F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="460" id="{008C0080-00B3-4248-9C87-0061008200E3}">
+          <x14:cfRule type="dataBar" priority="460" id="{00DF003D-0076-44AC-A62B-00DD004600D9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18780,7 +18780,7 @@
           <xm:sqref>N149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="459" id="{00C50036-002D-4B86-9CF7-00FC008100DB}">
+          <x14:cfRule type="dataBar" priority="459" id="{00720002-00C9-4E34-BEE4-0042007E0027}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18792,7 +18792,7 @@
           <xm:sqref>F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="458" id="{00270036-0046-481E-9229-00D800E500EF}">
+          <x14:cfRule type="dataBar" priority="458" id="{0073007F-001A-4936-83B4-000D00870006}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18804,7 +18804,7 @@
           <xm:sqref>N149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="457" id="{003E003F-00EE-465B-9D52-00E100810001}">
+          <x14:cfRule type="dataBar" priority="457" id="{0098007E-008C-47BF-9B8A-008E009900EB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18816,7 +18816,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="456" id="{002F0045-00FB-4E53-91E5-007A00A00070}">
+          <x14:cfRule type="dataBar" priority="456" id="{00F9005E-008D-4ED2-80C6-0050005C00D3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18828,7 +18828,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="455" id="{005E00C7-0069-4D6F-92BA-00330041007C}">
+          <x14:cfRule type="dataBar" priority="455" id="{006F00B2-006F-4369-BE89-006D00A0000C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18840,7 +18840,7 @@
           <xm:sqref>F149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="454" id="{00E70095-0095-4CE6-B2AB-005F009F004F}">
+          <x14:cfRule type="dataBar" priority="454" id="{00C600A0-0068-46DA-B7DE-00E900C000F6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18852,7 +18852,7 @@
           <xm:sqref>N149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="453" id="{00D500B0-0037-4164-A40D-00F800760016}">
+          <x14:cfRule type="dataBar" priority="453" id="{008E0058-0031-46BB-90AE-00B2002E0001}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18864,7 +18864,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="452" id="{00A1005A-00D2-4D25-8E65-008D002A00D8}">
+          <x14:cfRule type="dataBar" priority="452" id="{00420058-006B-4836-811B-000D00A9008D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18876,7 +18876,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="451" id="{004600E1-006B-40F7-AAAE-00A3008E0014}">
+          <x14:cfRule type="dataBar" priority="451" id="{002A00E3-0035-4034-A7DA-008300C5000B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18888,7 +18888,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="450" id="{00EB00D8-0049-42D5-93BD-00B40040000A}">
+          <x14:cfRule type="dataBar" priority="450" id="{00360096-00F6-4634-BDE4-005600CC00F5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18900,7 +18900,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="449" id="{00E000F9-000C-4A08-A24F-005C00D000BF}">
+          <x14:cfRule type="dataBar" priority="449" id="{0006006E-004F-4B79-876A-00F600480025}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18912,7 +18912,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="448" id="{006D00FE-0066-4659-A9A5-000B00860037}">
+          <x14:cfRule type="dataBar" priority="448" id="{00F10071-00BD-45E6-A6BB-0065007B00F8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18924,7 +18924,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="447" id="{00170032-00D1-470C-B4CF-00F000A100F4}">
+          <x14:cfRule type="dataBar" priority="447" id="{001F00E0-0048-4329-9638-006500F40082}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18936,7 +18936,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="446" id="{00EE00D1-00DF-402F-B515-000700E60011}">
+          <x14:cfRule type="dataBar" priority="446" id="{0052007F-0085-4B2D-B594-00EF00370015}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18948,7 +18948,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="445" id="{00710098-000B-4E3A-A636-0012002D00B0}">
+          <x14:cfRule type="dataBar" priority="445" id="{00BD004D-00A0-4EC5-AB13-0032007600CD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18960,7 +18960,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="444" id="{00FD0058-00CB-4109-B99D-00CD00A30092}">
+          <x14:cfRule type="dataBar" priority="444" id="{00F300F2-005C-4A70-8E0A-00EB00B3001B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18972,7 +18972,7 @@
           <xm:sqref>S149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="443" id="{002A0090-001B-4A19-978C-00E90048006D}">
+          <x14:cfRule type="dataBar" priority="443" id="{00B50099-008A-40A0-97AD-00A900570050}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18984,7 +18984,7 @@
           <xm:sqref>T149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="442" id="{0027001E-00E1-4277-A61D-001000980001}">
+          <x14:cfRule type="dataBar" priority="442" id="{00DA0041-007E-4B0D-B4EA-00FE008800C1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -18996,7 +18996,7 @@
           <xm:sqref>T149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="440" id="{00CE00B9-0077-423C-82A1-00DF0031000E}">
+          <x14:cfRule type="dataBar" priority="440" id="{002F0076-006F-4A14-A541-0021007300F4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19008,7 +19008,7 @@
           <xm:sqref>U149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="439" id="{00BF0022-0011-4752-A9C1-00B90087001B}">
+          <x14:cfRule type="dataBar" priority="439" id="{000E0085-0023-47BE-BFE7-003100610022}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19020,7 +19020,7 @@
           <xm:sqref>U149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="391" id="{0027009C-00C9-4D26-9BD4-0039000B0059}">
+          <x14:cfRule type="dataBar" priority="391" id="{007A00D0-0021-4EB9-9B30-0088002F007B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19032,7 +19032,7 @@
           <xm:sqref>F163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="384" id="{009C0000-0075-458D-BD8A-005700AC0061}">
+          <x14:cfRule type="dataBar" priority="384" id="{00400091-00A9-464C-9146-006800CE00A9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19044,7 +19044,7 @@
           <xm:sqref>F161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="383" id="{007200B1-009E-4A57-872D-00E400E000A6}">
+          <x14:cfRule type="dataBar" priority="383" id="{00430060-006F-4E21-ABDE-00F900B2001D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19056,7 +19056,7 @@
           <xm:sqref>T157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="382" id="{00D60037-00B9-487C-AB2C-0097006B0025}">
+          <x14:cfRule type="dataBar" priority="382" id="{0030009D-005B-47B5-B025-00D6009100D1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19068,7 +19068,7 @@
           <xm:sqref>T157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="381" id="{009B0011-00E5-4B39-94A8-0048007000C4}">
+          <x14:cfRule type="dataBar" priority="381" id="{00F100BD-001B-4C47-918C-004B0026008A}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19078,7 +19078,7 @@
           <xm:sqref>T157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="377" id="{008400BB-0074-44DD-93A1-007400680091}">
+          <x14:cfRule type="dataBar" priority="377" id="{00EC0076-0038-4ACF-AC39-00A7002600E9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19090,7 +19090,7 @@
           <xm:sqref>T161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="376" id="{0062001E-0018-4B3D-809B-0067009F0054}">
+          <x14:cfRule type="dataBar" priority="376" id="{00B00050-007E-47DF-AE06-001D007000EB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19102,7 +19102,7 @@
           <xm:sqref>T161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="375" id="{003200D6-0011-466E-AE11-00DA00B50083}">
+          <x14:cfRule type="dataBar" priority="375" id="{000C00F4-00DD-4581-8E61-003F0026000F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19112,7 +19112,7 @@
           <xm:sqref>T161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="374" id="{00950055-002D-4003-8F85-001C001E0081}">
+          <x14:cfRule type="dataBar" priority="374" id="{0044003B-000D-425A-A7F9-004F003F0003}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19124,7 +19124,7 @@
           <xm:sqref>T160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="373" id="{009200F7-006F-4D3E-B1BE-00B400C90095}">
+          <x14:cfRule type="dataBar" priority="373" id="{000600EF-00F0-441B-AE7E-007A00E30033}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19136,7 +19136,7 @@
           <xm:sqref>T160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="372" id="{00FA00AE-005D-4876-BB56-003E005E000E}">
+          <x14:cfRule type="dataBar" priority="372" id="{009A00F0-0063-4E8A-9243-0013000C0060}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19146,7 +19146,7 @@
           <xm:sqref>T160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="371" id="{001A00B3-00D0-4A99-B46B-00FA00880012}">
+          <x14:cfRule type="dataBar" priority="371" id="{00100016-0053-4C0D-8F33-005E00300089}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19158,7 +19158,7 @@
           <xm:sqref>U157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="370" id="{00930087-002A-4AFD-A539-00D500D000EE}">
+          <x14:cfRule type="dataBar" priority="370" id="{00A60031-0096-4473-8408-005A00660092}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19170,7 +19170,7 @@
           <xm:sqref>U157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="369" id="{00B800C4-00FD-4AAA-9298-0006003B00F4}">
+          <x14:cfRule type="dataBar" priority="369" id="{00FC009B-0097-479B-8D52-00A800AB0079}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19180,7 +19180,7 @@
           <xm:sqref>U157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="366" id="{007200CB-00B3-4F60-964A-00040003005B}">
+          <x14:cfRule type="dataBar" priority="366" id="{009A00C8-002C-4011-BC60-003C00AE00A4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19192,7 +19192,7 @@
           <xm:sqref>U161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="365" id="{008400EF-00A7-4095-8688-00F300C5003B}">
+          <x14:cfRule type="dataBar" priority="365" id="{000C0079-00BB-437A-A944-00A40027005C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19204,7 +19204,7 @@
           <xm:sqref>U161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="364" id="{00E30007-00FD-48EF-B28C-007600C40077}">
+          <x14:cfRule type="dataBar" priority="364" id="{00E3003A-002A-436A-B938-00F900D40021}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19214,7 +19214,7 @@
           <xm:sqref>U161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="363" id="{0065009A-00D9-440A-9AF7-0015000D0038}">
+          <x14:cfRule type="dataBar" priority="363" id="{001E006D-0012-467A-A1FC-007700E200D5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19226,7 +19226,7 @@
           <xm:sqref>U160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="362" id="{008D00AF-0002-4552-8880-0037009F00DC}">
+          <x14:cfRule type="dataBar" priority="362" id="{0032006B-0015-48D5-A080-004C00A900C0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19238,7 +19238,7 @@
           <xm:sqref>U160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="361" id="{00C000E1-0052-4D49-BD9B-006200A200C8}">
+          <x14:cfRule type="dataBar" priority="361" id="{00EC00C2-0015-4ACB-8BCD-009B0010003C}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19248,7 +19248,7 @@
           <xm:sqref>U160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="360" id="{008C00E8-003C-4454-967B-003500570016}">
+          <x14:cfRule type="dataBar" priority="360" id="{00BC0036-00BA-4CE6-A2C3-008000BC00E9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19260,7 +19260,7 @@
           <xm:sqref>S158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="359" id="{00B300BA-0009-4FD7-9ED4-006E00FD004A}">
+          <x14:cfRule type="dataBar" priority="359" id="{00800034-009A-4DC0-BE53-002D00AD009C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19272,7 +19272,7 @@
           <xm:sqref>F158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="358" id="{00BB0087-009F-4FF3-AFE0-00F000F100A8}">
+          <x14:cfRule type="dataBar" priority="358" id="{00D2004A-00BD-4F96-B8AA-005200810043}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19284,7 +19284,7 @@
           <xm:sqref>N158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="357" id="{0052004B-00FA-463C-84D8-001900EA0041}">
+          <x14:cfRule type="dataBar" priority="357" id="{00E40084-004A-48FB-9580-008800E600CD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19296,7 +19296,7 @@
           <xm:sqref>F166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="356" id="{00070033-0040-46BD-B64D-005800800052}">
+          <x14:cfRule type="dataBar" priority="356" id="{005B00A9-006D-48BE-AA56-003700040006}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19308,7 +19308,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="355" id="{005200C8-0015-4DAA-AB26-005B00A1003E}">
+          <x14:cfRule type="dataBar" priority="355" id="{00B3005B-00A6-4970-A9E5-007100D6001A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19320,7 +19320,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="354" id="{009900B5-00D4-4357-AABB-004C00B80006}">
+          <x14:cfRule type="dataBar" priority="354" id="{0038008F-0016-446A-BBAF-00CB00AD0027}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19330,7 +19330,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="353" id="{001B004C-006F-45C9-8C31-002400CE00BE}">
+          <x14:cfRule type="dataBar" priority="353" id="{006800DB-0055-4061-B65A-00D0001700FC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19342,7 +19342,7 @@
           <xm:sqref>F157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="352" id="{002300B4-00F4-46E5-9232-00C100A400F0}">
+          <x14:cfRule type="dataBar" priority="352" id="{00990073-00FE-4B7F-A73E-005500120059}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19354,7 +19354,7 @@
           <xm:sqref>N157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="351" id="{002B0093-0000-4525-9185-0038000F0096}">
+          <x14:cfRule type="dataBar" priority="351" id="{00B100F7-00CF-4C8A-BB3F-007400E400D4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19366,7 +19366,7 @@
           <xm:sqref>F157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="350" id="{007100A9-00DB-46B3-A63B-002500DF00B9}">
+          <x14:cfRule type="dataBar" priority="350" id="{00D4001E-00FD-44D8-9611-006E00C2007C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19378,7 +19378,7 @@
           <xm:sqref>N157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="349" id="{002D008D-00B8-4C3D-829E-006B00CD00A9}">
+          <x14:cfRule type="dataBar" priority="349" id="{009D00DE-00A6-4744-B58F-00CB00EF0014}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19390,7 +19390,7 @@
           <xm:sqref>F157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="348" id="{00D90064-008E-4F43-8D9F-00DA004F005C}">
+          <x14:cfRule type="dataBar" priority="348" id="{000500D1-0028-4A31-8A6A-00B5003300B8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19402,7 +19402,7 @@
           <xm:sqref>N157</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="347" id="{005600EE-00AD-4E9D-8A17-001A009C009D}">
+          <x14:cfRule type="dataBar" priority="347" id="{00900049-0040-4D14-B59D-00490045000D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19414,7 +19414,7 @@
           <xm:sqref>S159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="346" id="{009800B1-0010-48EE-93C7-00660013008C}">
+          <x14:cfRule type="dataBar" priority="346" id="{00C900AF-0095-49B5-9E2B-007600B70002}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19426,7 +19426,7 @@
           <xm:sqref>F159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="345" id="{00310047-0098-40D5-AF62-000A001D00DD}">
+          <x14:cfRule type="dataBar" priority="345" id="{00DA0065-001D-4421-96C3-003F007B0084}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19438,7 +19438,7 @@
           <xm:sqref>N159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="344" id="{004D0004-00D7-41AF-96BD-0073002100E7}">
+          <x14:cfRule type="dataBar" priority="344" id="{00500086-00E2-4543-A8E2-0011001B0050}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19450,7 +19450,7 @@
           <xm:sqref>F164</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="343" id="{00570067-00FD-43CB-A60E-000F001E0074}">
+          <x14:cfRule type="dataBar" priority="343" id="{001200CB-0031-4C0F-B067-00E800CF0027}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19462,7 +19462,7 @@
           <xm:sqref>T160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="342" id="{00BB0097-0049-4CDD-9AB0-009700CD0011}">
+          <x14:cfRule type="dataBar" priority="342" id="{005B0067-009C-49D7-96A9-00ED004200E8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19474,7 +19474,7 @@
           <xm:sqref>T160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="341" id="{0021006C-001D-403A-A4D4-00D500A20066}">
+          <x14:cfRule type="dataBar" priority="341" id="{00140013-0088-45C4-B6B7-002300A60017}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19484,7 +19484,7 @@
           <xm:sqref>T160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="340" id="{002B003B-004F-45B7-9E3C-004B00DF003E}">
+          <x14:cfRule type="dataBar" priority="340" id="{002E0037-001C-4207-92C1-0096002400A3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19496,7 +19496,7 @@
           <xm:sqref>T159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="339" id="{00590090-00A3-4348-A73A-003C004A006D}">
+          <x14:cfRule type="dataBar" priority="339" id="{0039000D-0035-4450-A95B-006A001F00EC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19508,7 +19508,7 @@
           <xm:sqref>T159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="338" id="{00D60009-00F0-4E70-A59C-005800270070}">
+          <x14:cfRule type="dataBar" priority="338" id="{00AE00A9-003D-4597-896A-00D600FA0077}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19518,7 +19518,7 @@
           <xm:sqref>T159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="337" id="{003A00ED-007E-4DFB-8F0F-001100DE0092}">
+          <x14:cfRule type="dataBar" priority="337" id="{00F800BC-00FA-4A55-98C0-00E700CC00E4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19530,7 +19530,7 @@
           <xm:sqref>T164</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="336" id="{00F5003F-0063-4788-AD2F-00280038005D}">
+          <x14:cfRule type="dataBar" priority="336" id="{005B0054-0017-436F-81E8-00DF0052001F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19542,7 +19542,7 @@
           <xm:sqref>T164</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="335" id="{008F004E-00BE-471E-B264-002E007B00AD}">
+          <x14:cfRule type="dataBar" priority="335" id="{006B00C0-0064-4BF4-9F99-005600BE0036}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19552,7 +19552,7 @@
           <xm:sqref>T164</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="334" id="{0029002C-00E6-4897-BC0A-00DD00A700E5}">
+          <x14:cfRule type="dataBar" priority="334" id="{00B800A4-0063-45D4-9B57-00BA0096005E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19564,7 +19564,7 @@
           <xm:sqref>T163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="333" id="{001900FA-00E2-4ABC-8152-00F5003E00C4}">
+          <x14:cfRule type="dataBar" priority="333" id="{00A5007D-001C-4D86-A937-0060008B0030}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19576,7 +19576,7 @@
           <xm:sqref>T163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="332" id="{00320098-006D-4385-874F-002E0022001A}">
+          <x14:cfRule type="dataBar" priority="332" id="{00AA0039-001F-4074-8BCF-00CB005D006F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19586,7 +19586,7 @@
           <xm:sqref>T163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="331" id="{00690096-0076-4C84-B03A-002800C600E9}">
+          <x14:cfRule type="dataBar" priority="331" id="{0052003D-00F1-4AF3-8A53-0031008F00DE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19598,7 +19598,7 @@
           <xm:sqref>U160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="330" id="{001E00DD-00EC-4B59-800D-00BF0073001D}">
+          <x14:cfRule type="dataBar" priority="330" id="{008B0014-00EB-4B5B-AF08-004700F70088}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19610,7 +19610,7 @@
           <xm:sqref>U160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="329" id="{00CF00FF-00D8-4FB4-8DAA-00DE00D2002A}">
+          <x14:cfRule type="dataBar" priority="329" id="{00FF00A2-008D-4190-B4B1-001000740077}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19620,7 +19620,7 @@
           <xm:sqref>U160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="328" id="{008400B1-0009-4F9B-8874-0071002D00FA}">
+          <x14:cfRule type="dataBar" priority="328" id="{006A0009-0016-498C-AE1D-00DD006D00EA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19632,7 +19632,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="327" id="{006D00BD-0022-4F50-AA4A-008B00D900CF}">
+          <x14:cfRule type="dataBar" priority="327" id="{00B400EB-007A-452C-B64F-003C003A00A6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19644,7 +19644,7 @@
           <xm:sqref>U159</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="326" id="{0092000D-00FF-4B68-97FF-0022007C0095}">
+          <x14:cfRule type="dataBar" priority="326" id="{00950057-0024-461E-AA62-001000330071}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19656,7 +19656,7 @@
           <xm:sqref>U164</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="325" id="{00BD0055-0078-40C3-8386-007800EB00D2}">
+          <x14:cfRule type="dataBar" priority="325" id="{00DF0028-0034-4DF5-8983-009200670098}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19668,7 +19668,7 @@
           <xm:sqref>U164</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="324" id="{00A000C4-00ED-48D0-A23D-003C00C700A5}">
+          <x14:cfRule type="dataBar" priority="324" id="{00C20098-0047-491C-85FA-003E000500A1}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19678,7 +19678,7 @@
           <xm:sqref>U164</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="323" id="{00070084-00B0-4172-A0E2-00F3005000C7}">
+          <x14:cfRule type="dataBar" priority="323" id="{00C00061-0047-484F-88B8-005B00D50081}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19690,7 +19690,7 @@
           <xm:sqref>U163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="322" id="{00780028-0003-47A6-8117-00F600A6002D}">
+          <x14:cfRule type="dataBar" priority="322" id="{002D002E-00E4-4795-9D0E-008D0071007A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19702,7 +19702,7 @@
           <xm:sqref>U163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="321" id="{00BE006E-0054-4218-A214-00FE00A000EE}">
+          <x14:cfRule type="dataBar" priority="321" id="{00960020-007E-46F5-BDDC-005600C0004C}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -19712,7 +19712,7 @@
           <xm:sqref>U163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="320" id="{005F008B-00C3-4898-87FF-00FE00AA001B}">
+          <x14:cfRule type="dataBar" priority="320" id="{00270061-005D-43A5-A319-00C4005E0083}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19724,7 +19724,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="319" id="{005C008C-00FA-482F-BB0B-0076007F0013}">
+          <x14:cfRule type="dataBar" priority="319" id="{007E0041-0036-4B04-AC52-00D400BD0032}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19736,7 +19736,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="318" id="{007500BF-001A-4D86-8DF7-00F2008300A1}">
+          <x14:cfRule type="dataBar" priority="318" id="{00FF006A-0044-45B3-9BD0-001600CE00A7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19748,7 +19748,7 @@
           <xm:sqref>N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="317" id="{002C0091-0095-4811-B747-002600BD00BA}">
+          <x14:cfRule type="dataBar" priority="317" id="{00C20090-0060-4E3E-AB29-004000C00005}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19760,7 +19760,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="316" id="{00650036-00A3-4052-8831-0018008F003F}">
+          <x14:cfRule type="dataBar" priority="316" id="{00E4008B-00C3-4CB2-844E-0061005500BF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19772,7 +19772,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="315" id="{004800AE-0077-4AA7-B4D3-00EA00AC0022}">
+          <x14:cfRule type="dataBar" priority="315" id="{003D0002-00A6-4F96-8063-006500600080}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19784,7 +19784,7 @@
           <xm:sqref>N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="314" id="{007500F5-004E-43BA-80F6-008F00A000FA}">
+          <x14:cfRule type="dataBar" priority="314" id="{00620027-00E5-425D-B7B3-007A00180075}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19796,7 +19796,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="313" id="{00F00049-00D9-4AB1-AB37-0048001C000B}">
+          <x14:cfRule type="dataBar" priority="313" id="{008600A6-00EC-48C7-ABFA-005C006700A5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19808,7 +19808,7 @@
           <xm:sqref>N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="312" id="{00270020-00FE-4705-BFA7-00C800610068}">
+          <x14:cfRule type="dataBar" priority="312" id="{004A00D7-0076-43CA-B9D7-00EB00070041}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19820,7 +19820,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="311" id="{007C009A-0028-4782-84C8-0079000B00AB}">
+          <x14:cfRule type="dataBar" priority="311" id="{005800AA-00D0-41E3-950A-00CE003C00D6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19832,7 +19832,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="310" id="{008200F8-00F2-4477-AC7F-00FC002900C8}">
+          <x14:cfRule type="dataBar" priority="310" id="{00AF00A8-00A7-4109-99EC-0080002400E9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19844,7 +19844,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="309" id="{008100AF-00E9-4419-9495-009F0040000E}">
+          <x14:cfRule type="dataBar" priority="309" id="{0032005C-0039-42F0-A119-00930004000E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19856,7 +19856,7 @@
           <xm:sqref>N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="308" id="{00210077-005D-4576-8579-003C0077004A}">
+          <x14:cfRule type="dataBar" priority="308" id="{00940055-00FD-44BD-917C-002500470040}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19868,7 +19868,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="307" id="{00E10066-000D-4F18-96EB-007300F00068}">
+          <x14:cfRule type="dataBar" priority="307" id="{00DD0074-00AA-4EF4-A250-000000240039}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19880,7 +19880,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="306" id="{0062002F-005C-4454-9DA1-006400620036}">
+          <x14:cfRule type="dataBar" priority="306" id="{00A90087-00CB-4B9B-A7B2-002300F400CF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19892,7 +19892,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="305" id="{00020036-00D1-45B8-8D2B-002100CF009C}">
+          <x14:cfRule type="dataBar" priority="305" id="{009400F2-00DB-4B53-95B3-007F001A00CF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19904,7 +19904,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="304" id="{003800DF-00C9-48D0-963B-005200730048}">
+          <x14:cfRule type="dataBar" priority="304" id="{004E0073-00F4-4214-8904-009F00170022}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19916,7 +19916,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="303" id="{009500B3-0088-495F-8602-0022005200B9}">
+          <x14:cfRule type="dataBar" priority="303" id="{00ED00EA-00DF-421E-9B65-006A00740018}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19928,7 +19928,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="302" id="{000F00A1-0072-4E73-910E-0042001700EA}">
+          <x14:cfRule type="dataBar" priority="302" id="{00A90018-004D-4DD9-87F4-00C6000E00D3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19940,7 +19940,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="301" id="{00DC00FB-00FA-4494-96A5-00C400C30041}">
+          <x14:cfRule type="dataBar" priority="301" id="{0094004F-005B-4872-9EAA-006900970068}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19952,7 +19952,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="300" id="{00D00075-007A-4716-AD6E-009B004D006D}">
+          <x14:cfRule type="dataBar" priority="300" id="{00FB00D5-00E7-42E3-A546-007400EE0072}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19964,7 +19964,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="299" id="{000A00C2-0055-481F-8475-00A2009700CD}">
+          <x14:cfRule type="dataBar" priority="299" id="{00F20067-00F3-481E-99C5-0008003F005B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19976,7 +19976,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="298" id="{00B700EE-00EA-4E76-9B00-00490004006C}">
+          <x14:cfRule type="dataBar" priority="298" id="{00E30083-0079-4F7B-8590-0061002D0001}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -19988,7 +19988,7 @@
           <xm:sqref>T154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="297" id="{001A001E-00AC-4CAC-8465-00B000B200AD}">
+          <x14:cfRule type="dataBar" priority="297" id="{00BA0018-00EE-4947-A91C-009E00EC0011}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20000,7 +20000,7 @@
           <xm:sqref>T154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="295" id="{000000E0-00CD-4433-BC41-005700B900F9}">
+          <x14:cfRule type="dataBar" priority="295" id="{00CF00BB-0016-4E73-ADAA-0041008C00DC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20012,7 +20012,7 @@
           <xm:sqref>U154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="294" id="{0043008E-00EF-4DD7-B2C7-002D00820064}">
+          <x14:cfRule type="dataBar" priority="294" id="{00B70066-00B0-41B6-BF5A-004900C30055}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20024,7 +20024,7 @@
           <xm:sqref>U154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="292" id="{006F0021-0010-44C1-A4A8-002200D700F3}">
+          <x14:cfRule type="dataBar" priority="292" id="{0051003C-0015-4140-A949-009200C700DE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20036,7 +20036,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="291" id="{00770088-00CE-437E-B5BA-00B000D200C2}">
+          <x14:cfRule type="dataBar" priority="291" id="{00A50003-00ED-42C8-8EFA-00D500DA0002}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20048,7 +20048,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="290" id="{001100BB-0067-48AD-BEA5-008700E00087}">
+          <x14:cfRule type="dataBar" priority="290" id="{00B000BB-001F-4C5A-AE82-006400440079}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20060,7 +20060,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="289" id="{00CB0003-0023-4CD7-AAA4-009500E800E9}">
+          <x14:cfRule type="dataBar" priority="289" id="{00930051-008A-49B5-BB5E-0024000400E3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20072,7 +20072,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="288" id="{00F7002B-0056-4735-8646-0035002500FA}">
+          <x14:cfRule type="dataBar" priority="288" id="{00FA00E3-0028-4AF8-A0F4-00EC00E30051}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20084,7 +20084,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="287" id="{0031001E-00EE-4AAA-9408-006600DB0028}">
+          <x14:cfRule type="dataBar" priority="287" id="{001E0070-0047-4FA5-A844-004400B80002}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20096,7 +20096,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="286" id="{00F6008D-00A8-460D-A32E-00EC00A500CE}">
+          <x14:cfRule type="dataBar" priority="286" id="{00D70096-00C6-48F4-8DFC-000A00D4008C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20108,7 +20108,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="285" id="{00400033-00BA-4F46-8D9A-00B700220090}">
+          <x14:cfRule type="dataBar" priority="285" id="{00950012-00C1-4444-BC6D-007000BA00CA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20120,7 +20120,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="284" id="{00E7000D-0027-42BE-B942-00FC006800E0}">
+          <x14:cfRule type="dataBar" priority="284" id="{00290097-000A-4626-A0B0-002700FE00A4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20132,7 +20132,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="283" id="{003000DE-00AB-4461-8977-008D00730003}">
+          <x14:cfRule type="dataBar" priority="283" id="{00AF0085-0064-4823-9091-00F400DB00C2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20144,7 +20144,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="282" id="{00030054-0038-4373-A423-00AB00CB0051}">
+          <x14:cfRule type="dataBar" priority="282" id="{00200003-002C-4F55-B901-0095008F0038}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20156,7 +20156,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="281" id="{00A600E1-009E-45C6-8791-006B000B005B}">
+          <x14:cfRule type="dataBar" priority="281" id="{00DA00C0-00B2-4835-9D22-009F007400E6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20168,7 +20168,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="280" id="{000800AC-00C8-4C05-B038-00BB00DE0006}">
+          <x14:cfRule type="dataBar" priority="280" id="{00B30000-000E-4DF1-ABF3-007700E700B0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20180,7 +20180,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="279" id="{003600CD-0094-48E5-9E52-00B50039003B}">
+          <x14:cfRule type="dataBar" priority="279" id="{009000BC-009F-4358-8CD5-001A00F400EA}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20190,7 +20190,7 @@
           <xm:sqref>N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="278" id="{000C00D5-00E8-41B1-B57B-00940078005F}">
+          <x14:cfRule type="dataBar" priority="278" id="{006400A4-00C0-417D-B968-00BD0051002F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -20202,7 +20202,7 @@
           <xm:sqref>N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="277" id="{00E60060-008E-4BDF-9426-00AD004100F4}">
+          <x14:cfRule type="dataBar" priority="277" id="{00A60044-004F-46F6-AC11-008F00440034}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20212,7 +20212,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="276" id="{001F007A-0057-45E4-8113-00AB001B006C}">
+          <x14:cfRule type="dataBar" priority="276" id="{00B300DC-007D-4EC9-82E1-007D00BB0037}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -20224,7 +20224,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="275" id="{002300AB-0089-49C4-A7CE-00BC00300090}">
+          <x14:cfRule type="dataBar" priority="275" id="{00C5005A-007C-4796-B7DB-00C000F60071}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -20236,7 +20236,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="274" id="{001C00BF-00CA-4028-9E67-00F5003F0002}">
+          <x14:cfRule type="dataBar" priority="274" id="{000C00AF-00EE-44D7-A6AD-0049001700CE}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -20248,7 +20248,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="273" id="{006700D1-0036-43FA-B76D-00D6006C000B}">
+          <x14:cfRule type="dataBar" priority="273" id="{00C500CE-00BA-418E-86F4-0076003E0032}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20258,7 +20258,7 @@
           <xm:sqref>F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="272" id="{00630055-0053-49D3-A356-00D9007C0051}">
+          <x14:cfRule type="dataBar" priority="272" id="{003B00F2-00C9-4AC9-9D39-00ED004C0075}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20268,7 +20268,7 @@
           <xm:sqref>N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="271" id="{009D006A-0084-4C9B-BE85-00D900110083}">
+          <x14:cfRule type="dataBar" priority="271" id="{00FD001B-005E-4A2F-B7A8-000400B200C0}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20278,7 +20278,7 @@
           <xm:sqref>S154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="270" id="{00350008-000F-462A-A337-0050005F00C4}">
+          <x14:cfRule type="dataBar" priority="270" id="{00840059-00F8-4752-B437-004800640075}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20288,7 +20288,7 @@
           <xm:sqref>T154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="269" id="{006500DC-00F1-4114-B2A2-002000DE007B}">
+          <x14:cfRule type="dataBar" priority="269" id="{00FE0089-007B-4289-A6BD-00AC00CF0036}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -20300,7 +20300,7 @@
           <xm:sqref>T154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="267" id="{008C00A4-00F0-4309-BB53-009B00B5006D}">
+          <x14:cfRule type="dataBar" priority="267" id="{000000CB-002E-4D40-8CF4-003C007700C7}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20310,7 +20310,7 @@
           <xm:sqref>N154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="265" id="{00C50039-003E-4601-8D78-00D4007D0001}">
+          <x14:cfRule type="dataBar" priority="265" id="{00A4000D-0071-492E-81B9-005600D000E1}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20320,7 +20320,7 @@
           <xm:sqref>U154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="264" id="{001300FD-00B9-4B98-90DA-00B10089009E}">
+          <x14:cfRule type="dataBar" priority="264" id="{008400AD-004A-4C4D-A6A9-00F1005500D6}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20330,7 +20330,7 @@
           <xm:sqref>U154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="262" id="{007D0011-0065-4C0F-A027-0089001E0097}">
+          <x14:cfRule type="dataBar" priority="262" id="{009B00A0-00D2-45D4-9D78-004800590019}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20342,7 +20342,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="261" id="{009D00B0-0061-4F9C-8A21-00BD00AC001B}">
+          <x14:cfRule type="dataBar" priority="261" id="{00EC008A-00F7-4F0B-87DD-002C00DC0049}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20354,7 +20354,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="260" id="{006100A5-0073-43C3-9972-003A008400DE}">
+          <x14:cfRule type="dataBar" priority="260" id="{0028009A-0009-4052-85A1-00FC00E000C7}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20364,7 +20364,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="259" id="{00A800A9-0026-4110-8D7F-0029005700FD}">
+          <x14:cfRule type="dataBar" priority="259" id="{00EE0030-00FD-4CD5-8019-0050008B005E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20376,7 +20376,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="258" id="{00B200D1-0064-4B97-811F-005300320044}">
+          <x14:cfRule type="dataBar" priority="258" id="{009300C7-0030-4E4A-A5FB-009000780057}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20388,7 +20388,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="257" id="{00CE004A-0087-49F0-B1C7-00D6008E0010}">
+          <x14:cfRule type="dataBar" priority="257" id="{00B20003-00A7-4BEA-9EB7-001D00F3000C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20400,7 +20400,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="256" id="{00F4002F-0054-48F7-A712-00AE0084000B}">
+          <x14:cfRule type="dataBar" priority="256" id="{00670001-0042-4108-9EAB-00A800FF0087}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20412,7 +20412,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="255" id="{00C30063-0033-487F-81EE-008A005800AB}">
+          <x14:cfRule type="dataBar" priority="255" id="{00A60090-0043-404F-A700-0013005200CD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20424,7 +20424,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="254" id="{002C00AF-00E8-441B-9B4B-001700B70065}">
+          <x14:cfRule type="dataBar" priority="254" id="{005C0099-0099-4950-A2FC-00D2002000BB}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20434,7 +20434,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="253" id="{00180035-0022-420C-A6CE-00D800850077}">
+          <x14:cfRule type="dataBar" priority="253" id="{00E50028-0077-4D5D-BD87-007400B6008C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20446,7 +20446,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="252" id="{00E30092-0016-4538-B905-00E600E400A6}">
+          <x14:cfRule type="dataBar" priority="252" id="{00DF00E6-00C0-4E12-BE89-00BE00D00077}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20458,7 +20458,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="251" id="{00B400B1-0002-4E4F-A0AB-009E001C006E}">
+          <x14:cfRule type="dataBar" priority="251" id="{00F80008-0011-433C-92AC-008100F90012}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20470,7 +20470,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="250" id="{00280000-0060-4FB1-8D38-00B100C800B9}">
+          <x14:cfRule type="dataBar" priority="250" id="{00FF00DE-0097-4373-B44C-00FE00DA0031}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20482,7 +20482,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="249" id="{00A2000A-00C4-41FB-A32E-008F00D900E5}">
+          <x14:cfRule type="dataBar" priority="249" id="{00400090-009E-49C9-821F-00750052004E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20494,7 +20494,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="248" id="{007500C3-00D2-4D06-86E1-004000F000A8}">
+          <x14:cfRule type="dataBar" priority="248" id="{00210060-00A6-480F-BAFD-00C0004F006E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20506,7 +20506,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="247" id="{001D00F3-0013-4364-98B3-0062006200EF}">
+          <x14:cfRule type="dataBar" priority="247" id="{002500D4-008A-46F3-BB00-008200E200A0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20518,7 +20518,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="246" id="{00E900B5-00F2-4F04-8C91-00F100A400DC}">
+          <x14:cfRule type="dataBar" priority="246" id="{00B800D6-0084-436A-84AE-00A600D20064}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20530,7 +20530,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="245" id="{00B10068-00E5-4208-88AD-00DB004400CB}">
+          <x14:cfRule type="dataBar" priority="245" id="{005800E0-00F4-4CEA-BF95-0063004C00D6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20542,7 +20542,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="244" id="{006A0051-0055-477B-B551-009100A800D6}">
+          <x14:cfRule type="dataBar" priority="244" id="{00E70073-003A-4B47-BF0A-00D900A00043}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20554,7 +20554,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="243" id="{00A30038-009B-4CC7-97B6-00A800B400B7}">
+          <x14:cfRule type="dataBar" priority="243" id="{00E40034-0098-4C80-9B71-00C300F5001C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20566,7 +20566,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="242" id="{00E6002D-00E5-411B-8C00-00300029003F}">
+          <x14:cfRule type="dataBar" priority="242" id="{0036008C-0092-485F-9DAA-00BC00DB006A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20578,7 +20578,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="241" id="{00C400E3-0015-49EE-8EA0-00AD00080029}">
+          <x14:cfRule type="dataBar" priority="241" id="{00270021-00B6-4CE4-AD91-00D600F000DE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20590,7 +20590,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="240" id="{008000A3-00F2-4BC9-837E-00A0007400BE}">
+          <x14:cfRule type="dataBar" priority="240" id="{00500085-00EC-4E34-935A-007900FA0057}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20602,7 +20602,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="239" id="{00260011-00D3-42E7-8D60-009B004B00A6}">
+          <x14:cfRule type="dataBar" priority="239" id="{004B0046-0094-4BE0-86EE-0060004800E1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20614,7 +20614,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="238" id="{005000FF-0097-4627-88B8-006A004100FD}">
+          <x14:cfRule type="dataBar" priority="238" id="{00730005-00AC-4194-90D0-001F0002006F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20626,7 +20626,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="237" id="{007F0051-0065-4DC1-93D1-008200AC009F}">
+          <x14:cfRule type="dataBar" priority="237" id="{00E800A7-005C-4991-8F86-003B00DB009C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20638,7 +20638,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="236" id="{008A0024-005B-41E4-AD2F-00B800F200DA}">
+          <x14:cfRule type="dataBar" priority="236" id="{00ED00DC-000B-4C0C-8783-008600200057}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20650,7 +20650,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="235" id="{009000B4-0008-4393-9A11-00F700BF00A7}">
+          <x14:cfRule type="dataBar" priority="235" id="{0040007F-0095-4AD0-A28E-004F003C0054}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20662,7 +20662,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="234" id="{005500C1-00A7-49B5-88B0-00A8001E004A}">
+          <x14:cfRule type="dataBar" priority="234" id="{00E7009E-0014-4E4B-952C-000F009F0097}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20674,7 +20674,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="233" id="{00830094-0034-4CA9-AEE4-00E200440053}">
+          <x14:cfRule type="dataBar" priority="233" id="{008D0069-000E-4C36-9D3E-006700DA00EF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20686,7 +20686,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="232" id="{004F0094-004B-4CA8-BADC-0027004D0026}">
+          <x14:cfRule type="dataBar" priority="232" id="{004F0027-00F5-42FB-98EC-001900EF002E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20698,7 +20698,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="231" id="{00DE002D-0092-4F94-B6D2-00DD008B000A}">
+          <x14:cfRule type="dataBar" priority="231" id="{00A20041-0003-440B-99C1-008300760031}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20710,7 +20710,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="230" id="{00D100BB-0010-467D-827E-004F00D600B0}">
+          <x14:cfRule type="dataBar" priority="230" id="{005300D4-006C-4064-AF69-00CE005000A2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20722,7 +20722,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="229" id="{00F70081-007A-43D1-891C-00E6009D0054}">
+          <x14:cfRule type="dataBar" priority="229" id="{0077000A-003D-4C49-BEA0-00D4003B0046}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20734,7 +20734,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="228" id="{00FE00BF-0095-42F3-8451-000100A800C7}">
+          <x14:cfRule type="dataBar" priority="228" id="{00490076-00D8-4318-9E7D-00B10023002C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20746,7 +20746,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="227" id="{00DF0093-00C9-4B2F-B388-009B009D0021}">
+          <x14:cfRule type="dataBar" priority="227" id="{009F00FD-008C-45FD-855B-004B00FA004F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20758,7 +20758,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="226" id="{004700ED-0000-41F2-9BF6-004500E2009F}">
+          <x14:cfRule type="dataBar" priority="226" id="{007E0095-0060-4237-A751-008C00CB00DD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20770,7 +20770,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="225" id="{00150067-00C6-4E4E-B09E-004500D3009E}">
+          <x14:cfRule type="dataBar" priority="225" id="{00D2005B-0005-43A6-9399-00FB0069009B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20782,7 +20782,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="224" id="{001F0060-0045-41FE-810C-00850068006F}">
+          <x14:cfRule type="dataBar" priority="224" id="{0033008B-0070-4CE4-ADDA-00FA000C0029}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20794,7 +20794,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="223" id="{006400F0-0067-40C5-A0B0-00D400FC00E2}">
+          <x14:cfRule type="dataBar" priority="223" id="{003F0006-008B-4362-A562-008E00D6006A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20806,7 +20806,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="222" id="{00D40082-006E-4A36-AB58-008000360049}">
+          <x14:cfRule type="dataBar" priority="222" id="{008D000B-0016-40F2-9860-008100920056}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20818,7 +20818,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="221" id="{00FD00A5-00AB-4A8E-86EF-004400C70041}">
+          <x14:cfRule type="dataBar" priority="221" id="{003500F7-00CC-440C-9018-00710006007F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20830,7 +20830,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="220" id="{00510030-00C0-416F-B4DE-005F002A0013}">
+          <x14:cfRule type="dataBar" priority="220" id="{00CC00F0-0001-4662-BF77-007600F100D8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20842,7 +20842,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="219" id="{00B400E5-0053-4F6B-8318-0062000400BC}">
+          <x14:cfRule type="dataBar" priority="219" id="{005F0079-003A-4109-8E19-0034007E00D7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20854,7 +20854,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="218" id="{00150094-0072-4BD3-9E63-00F000650089}">
+          <x14:cfRule type="dataBar" priority="218" id="{008F004D-00F8-4F10-96F4-00ED00FA00CD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20866,7 +20866,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="217" id="{009600C5-0049-4483-8AB0-00A400D8003A}">
+          <x14:cfRule type="dataBar" priority="217" id="{00630040-00AC-428B-A59A-00B400BE00FF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20878,7 +20878,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="216" id="{00A00035-00D8-43E4-9159-00A800240074}">
+          <x14:cfRule type="dataBar" priority="216" id="{008F00CC-0011-48B8-8274-002000B6009D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20890,7 +20890,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="215" id="{007300FD-0006-46EA-96F3-0021009700DD}">
+          <x14:cfRule type="dataBar" priority="215" id="{000700F8-0043-493A-AD42-00C90000008F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20902,7 +20902,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="214" id="{00990054-00C7-4E5F-AD4C-003300ED006C}">
+          <x14:cfRule type="dataBar" priority="214" id="{00DD00DD-0014-47DE-B030-00C700E5003D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20914,7 +20914,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="213" id="{00B600B8-0026-4942-BB48-006100F9009F}">
+          <x14:cfRule type="dataBar" priority="213" id="{00DB00C1-0028-483E-9E95-00E8009200D2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -20926,7 +20926,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="212" id="{001600D0-00CF-4E39-A0D2-009A0060004B}">
+          <x14:cfRule type="dataBar" priority="212" id="{00820026-00A7-46F2-9C96-00DB00E100DE}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20936,7 +20936,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="211" id="{006400C4-005B-4DF8-9F82-005E00F10066}">
+          <x14:cfRule type="dataBar" priority="211" id="{007000E9-0013-4832-B8CE-001B00EF00A7}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -20948,7 +20948,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="210" id="{005D0041-00F8-42BE-9B18-00A300F70048}">
+          <x14:cfRule type="dataBar" priority="210" id="{009600B4-009B-47C4-869F-00BE00B000F9}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20958,7 +20958,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="209" id="{001400EA-0038-4CC9-A5ED-007F00A300F1}">
+          <x14:cfRule type="dataBar" priority="209" id="{00A20047-00B5-4CC4-B094-00F4009C002D}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -20970,7 +20970,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="208" id="{00B900E7-0014-4A53-AC7C-004400840098}">
+          <x14:cfRule type="dataBar" priority="208" id="{0070000B-005F-46C9-A5E8-003900220096}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -20982,7 +20982,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="207" id="{00EA0061-00CF-41A1-8326-000A00460005}">
+          <x14:cfRule type="dataBar" priority="207" id="{003200F1-003A-4C39-827A-00510026004E}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -20994,7 +20994,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="206" id="{00EE00E2-00D3-43FD-9D5F-0092000500C6}">
+          <x14:cfRule type="dataBar" priority="206" id="{00780045-00BD-404A-96FE-000900AF00EA}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21004,7 +21004,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="205" id="{00320054-000B-489A-8BA9-002100620076}">
+          <x14:cfRule type="dataBar" priority="205" id="{008400C0-002A-44EE-B187-00E300390059}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21014,7 +21014,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="204" id="{00B2009C-00EB-44AC-BA72-00040098008F}">
+          <x14:cfRule type="dataBar" priority="204" id="{00A60085-0018-4F58-A30D-000D00F9004C}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21024,7 +21024,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="203" id="{003C00BD-0011-4E75-831D-00AF00A60031}">
+          <x14:cfRule type="dataBar" priority="203" id="{00FC00AA-0018-4C11-B27F-002700D7003E}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21034,7 +21034,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="202" id="{00990001-00A3-4122-9D3C-00C1004F0016}">
+          <x14:cfRule type="dataBar" priority="202" id="{00CB008A-00EF-4371-A910-00AA00B400C7}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -21046,7 +21046,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="201" id="{00BD00D2-002D-412E-B013-00D900220005}">
+          <x14:cfRule type="dataBar" priority="201" id="{00E4009B-00A8-4198-8063-00E8006D0028}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21056,7 +21056,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="200" id="{00F30024-003C-4CC1-AD26-00A000D600C6}">
+          <x14:cfRule type="dataBar" priority="200" id="{00FF00A0-007F-4BC1-8CE9-00FA00A800A1}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21066,7 +21066,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="199" id="{00FB0094-0083-4DE5-BCA9-00C600D400E2}">
+          <x14:cfRule type="dataBar" priority="199" id="{00A70064-0022-43E0-ADF7-007700C70056}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21076,7 +21076,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="198" id="{00FE008D-000F-45F8-9521-000E005500D2}">
+          <x14:cfRule type="dataBar" priority="198" id="{00260012-0043-44FE-9E2D-00B9000E00D6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21088,7 +21088,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="197" id="{005A001D-006F-4494-B222-009D00660031}">
+          <x14:cfRule type="dataBar" priority="197" id="{0045002D-00D8-4EA3-8F6A-003D00FB00B1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21100,7 +21100,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="196" id="{00DB00FA-00F1-46F9-AF30-00CC00BD0045}">
+          <x14:cfRule type="dataBar" priority="196" id="{00FD0041-00DE-43A7-833C-003E00270080}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21112,7 +21112,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="195" id="{001500A5-00C7-4043-BD3B-003300C000C5}">
+          <x14:cfRule type="dataBar" priority="195" id="{00B0002D-00C9-48DA-AD89-006500B800A6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21124,7 +21124,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="194" id="{00F30013-0097-43C2-8C6F-000900B3001C}">
+          <x14:cfRule type="dataBar" priority="194" id="{00DB00FC-000A-4B2A-B748-00F800E700D8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21136,7 +21136,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="193" id="{006500EB-0070-4220-A1A2-005300B000FD}">
+          <x14:cfRule type="dataBar" priority="193" id="{009200EE-0052-4411-B5FA-002400390005}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21148,7 +21148,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="192" id="{006E0001-0066-43A9-AB85-006C00B8002D}">
+          <x14:cfRule type="dataBar" priority="192" id="{00B1001E-0014-480B-9BD9-00D3002C0079}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21160,7 +21160,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="191" id="{0019007E-00BD-46FC-B8F4-001800350026}">
+          <x14:cfRule type="dataBar" priority="191" id="{00250058-0064-474D-AA16-0037008300CD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21172,7 +21172,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="190" id="{001C0025-0041-451F-A54B-002E00880070}">
+          <x14:cfRule type="dataBar" priority="190" id="{00600051-00F7-455A-9530-00FB0050004B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21184,7 +21184,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="189" id="{00150077-0099-47E8-94B1-00AE007800F1}">
+          <x14:cfRule type="dataBar" priority="189" id="{004100D4-00F7-45C8-B036-000900760031}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21196,7 +21196,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="188" id="{00700068-003D-404A-A04A-003B00E30051}">
+          <x14:cfRule type="dataBar" priority="188" id="{008900DF-0080-44BC-8D4A-006200A80023}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21208,7 +21208,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="187" id="{00AD0087-0058-4F3D-9CF1-00DA00800072}">
+          <x14:cfRule type="dataBar" priority="187" id="{00C60075-0089-447B-ABE7-003100160003}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21220,7 +21220,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="186" id="{00E8001C-0005-43F6-B96C-00DF00B500E0}">
+          <x14:cfRule type="dataBar" priority="186" id="{00990093-008E-4568-9F5A-003C007000D9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21232,7 +21232,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="185" id="{00B5007B-0070-4463-8FAE-00F900CA007D}">
+          <x14:cfRule type="dataBar" priority="185" id="{00B7000D-00B0-4B93-B20B-00DB009C0004}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21244,7 +21244,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="184" id="{0066000E-0018-4BF4-8FBA-00AF00B70054}">
+          <x14:cfRule type="dataBar" priority="184" id="{00F3009E-00C5-4AEF-8220-00E5006F0058}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21256,7 +21256,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="183" id="{00210083-005C-4441-8E5F-00D400E80098}">
+          <x14:cfRule type="dataBar" priority="183" id="{0031001D-00B9-4F58-918D-004300CF00DB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21268,7 +21268,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="182" id="{00E500F0-003D-4A68-9E4F-002100630011}">
+          <x14:cfRule type="dataBar" priority="182" id="{00EB002A-00F8-46E7-B264-006400590029}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21280,7 +21280,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="181" id="{00AE001F-00C7-405A-B508-004B00E90007}">
+          <x14:cfRule type="dataBar" priority="181" id="{000E00DF-00C5-4AB6-8FDC-00B700060094}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21292,7 +21292,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="180" id="{007F00D8-005A-46E7-B528-004C00CF007E}">
+          <x14:cfRule type="dataBar" priority="180" id="{00650017-00C0-4989-B4AE-002200C40034}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21302,7 +21302,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="179" id="{001A00A5-00D9-4508-BAA5-005500AC0043}">
+          <x14:cfRule type="dataBar" priority="179" id="{003D0018-00D8-4F13-A320-00BB005A008F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21314,7 +21314,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="178" id="{000A0089-0012-4403-B137-002200C6003C}">
+          <x14:cfRule type="dataBar" priority="178" id="{00090005-00F9-4175-AE16-00CE007D0032}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21326,7 +21326,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="177" id="{001A0003-0094-489C-9002-007500D500FB}">
+          <x14:cfRule type="dataBar" priority="177" id="{00B600C3-0010-4081-89AA-003100BC00FF}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21336,7 +21336,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="176" id="{00ED00CA-0064-45AA-97CE-008C004F0063}">
+          <x14:cfRule type="dataBar" priority="176" id="{003500C3-00F1-4AA6-A130-00DA00E500D5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21348,7 +21348,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="175" id="{00340033-0016-45F8-B316-0071001F0010}">
+          <x14:cfRule type="dataBar" priority="175" id="{0089009C-0035-4457-B083-001D007F004B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21360,7 +21360,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="174" id="{006200EB-0062-4B67-BE4D-00D8005500DD}">
+          <x14:cfRule type="dataBar" priority="174" id="{00620031-00A8-4563-8A2B-00A3006A00B2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21372,7 +21372,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="173" id="{005800ED-00BB-48F4-B6BD-00B800600037}">
+          <x14:cfRule type="dataBar" priority="173" id="{0048009C-00DA-4A73-8039-001700620064}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21384,7 +21384,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="172" id="{00ED00A2-006C-42DD-BA1D-00A20079000B}">
+          <x14:cfRule type="dataBar" priority="172" id="{00B2009B-006A-4467-8BC5-00A6007600C0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21396,7 +21396,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="171" id="{000600B9-0039-4B29-8538-00060013008C}">
+          <x14:cfRule type="dataBar" priority="171" id="{00A000CA-00AD-46EE-A31A-001100B800E9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21408,7 +21408,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="170" id="{002A0058-00D2-4DF3-98F7-00E70091008E}">
+          <x14:cfRule type="dataBar" priority="170" id="{007900DE-00F9-4E15-AF56-00C8006D0018}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21420,7 +21420,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="169" id="{00D6007E-00EA-48CB-A92F-00FD00100032}">
+          <x14:cfRule type="dataBar" priority="169" id="{00900016-00FB-44D0-8050-005F00F5005B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21432,7 +21432,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="168" id="{0019002E-002D-438D-8C27-008B00210063}">
+          <x14:cfRule type="dataBar" priority="168" id="{0010008B-0091-4A27-BCA2-00F600BD0071}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21444,7 +21444,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="167" id="{00FC0070-0057-4C6E-8E4D-009E00340040}">
+          <x14:cfRule type="dataBar" priority="167" id="{006200D8-001A-414A-825D-0050009C004A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21456,7 +21456,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="166" id="{005B0006-004A-4529-B057-00F2005700E8}">
+          <x14:cfRule type="dataBar" priority="166" id="{00F50016-00BB-4299-A8E9-00DD00A00087}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21468,7 +21468,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="165" id="{005200FC-0000-45EE-99CF-00820004005A}">
+          <x14:cfRule type="dataBar" priority="165" id="{00E20011-00DA-4371-B32E-00C3007500B1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21480,7 +21480,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="164" id="{00F500C8-00C0-43B5-9743-009200870021}">
+          <x14:cfRule type="dataBar" priority="164" id="{00E200CE-0046-4D98-BD22-00BB00070097}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21492,7 +21492,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="163" id="{00A6005F-00D0-4DBD-A6A8-005F006600F5}">
+          <x14:cfRule type="dataBar" priority="163" id="{00C0008E-00F3-4F39-94C8-001A001E00E2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21504,7 +21504,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="162" id="{00F500AC-0088-499B-B206-008200510027}">
+          <x14:cfRule type="dataBar" priority="162" id="{00D80022-0073-4027-B35C-005D006C0093}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21516,7 +21516,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="161" id="{005000CD-0017-422F-8F09-001B002E008C}">
+          <x14:cfRule type="dataBar" priority="161" id="{0056003C-006A-4CBF-A1BD-005900E500E8}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21526,7 +21526,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="160" id="{00150049-00C8-4720-BC1B-00FF005F009E}">
+          <x14:cfRule type="dataBar" priority="160" id="{001F00EC-00E2-443D-AA45-001400F70071}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21538,7 +21538,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="159" id="{00A00092-00D7-4378-ABBD-007800A8002E}">
+          <x14:cfRule type="dataBar" priority="159" id="{008D00FA-00DA-48FA-89E2-004C00070001}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21550,7 +21550,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="158" id="{002900BA-009D-439C-A91A-00F100140029}">
+          <x14:cfRule type="dataBar" priority="158" id="{00B30046-00DC-42CA-99B1-00BA00570046}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -21560,7 +21560,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="157" id="{008A004B-0071-4BEC-9E5B-00A400D500CC}">
+          <x14:cfRule type="dataBar" priority="157" id="{007C00D8-0048-410A-8913-000C00A000C2}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21572,7 +21572,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="156" id="{00410005-0027-4613-9487-00DE004B00D0}">
+          <x14:cfRule type="dataBar" priority="156" id="{00D0009C-0072-42CF-B37F-008600EC003F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21584,7 +21584,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="155" id="{007E00E8-00BF-4955-8052-002D007D00CF}">
+          <x14:cfRule type="dataBar" priority="155" id="{00090001-0004-44C2-8B49-000A00E80079}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21596,7 +21596,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="154" id="{00420099-00FC-4976-8C14-004200D900D3}">
+          <x14:cfRule type="dataBar" priority="154" id="{005A00D9-00BD-4698-B712-007700BB005C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21608,7 +21608,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="153" id="{007E0048-0089-48AE-B6BB-003D003D00D1}">
+          <x14:cfRule type="dataBar" priority="153" id="{006E00E4-00B3-452E-BEE1-00DB00E6005D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21620,7 +21620,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="152" id="{001C0028-0074-424D-8B6A-006F002600D4}">
+          <x14:cfRule type="dataBar" priority="152" id="{0056003F-0086-4ADC-BE07-00EA006A00A0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21632,7 +21632,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="151" id="{00E900C5-004C-4715-845D-0064005600F2}">
+          <x14:cfRule type="dataBar" priority="151" id="{00A9003A-00CA-464D-8E3F-00C90049006E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21644,7 +21644,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="150" id="{00D500DE-00F2-4104-AA7F-005900070025}">
+          <x14:cfRule type="dataBar" priority="150" id="{00CC0078-00A9-486E-801B-00D000B10086}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21656,7 +21656,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="149" id="{0079005B-00DB-43A5-B14E-0093001C002F}">
+          <x14:cfRule type="dataBar" priority="149" id="{00A7002C-0018-4107-8642-00340053008F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21668,7 +21668,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="148" id="{0031006A-0088-443F-A384-006000CA0001}">
+          <x14:cfRule type="dataBar" priority="148" id="{000B00B4-0055-489D-979B-001600160082}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21680,7 +21680,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="147" id="{004100DD-003D-4D1B-921A-007800CF00DE}">
+          <x14:cfRule type="dataBar" priority="147" id="{00CE0095-0076-4A48-AB41-003C007E009E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21692,7 +21692,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="146" id="{0057001E-00BB-4428-9ECF-00DD00360044}">
+          <x14:cfRule type="dataBar" priority="146" id="{009E0062-0064-420E-8078-00EC00650027}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21704,7 +21704,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="145" id="{008D00F5-008F-428C-87EC-003400B100D7}">
+          <x14:cfRule type="dataBar" priority="145" id="{00300066-0088-49AE-879E-005C009600B8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21716,7 +21716,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="144" id="{00BC00CA-0045-49DE-ACE5-00DB0055005A}">
+          <x14:cfRule type="dataBar" priority="144" id="{006F0047-0043-46D1-A549-008E007C009E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21728,7 +21728,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="143" id="{00C30071-008D-427F-9017-00B000420014}">
+          <x14:cfRule type="dataBar" priority="143" id="{002100D8-00EF-41FA-9A3D-005A008300C1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21740,7 +21740,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="142" id="{00E10042-002A-4709-8730-000C004E00C3}">
+          <x14:cfRule type="dataBar" priority="142" id="{00E10001-0019-4B29-B997-00B700C40054}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21752,7 +21752,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="141" id="{006000F4-0053-4506-9115-005D007600DB}">
+          <x14:cfRule type="dataBar" priority="141" id="{0083008D-0006-4EE5-804F-00A0005D00AF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21764,7 +21764,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="140" id="{00290043-00C3-4914-9ECE-00F900CF00A8}">
+          <x14:cfRule type="dataBar" priority="140" id="{002000C2-0006-4B5F-AB97-00BF001C0082}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21776,7 +21776,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="139" id="{00440047-00CA-4B81-8590-005900F30005}">
+          <x14:cfRule type="dataBar" priority="139" id="{006000A5-0001-420C-8DE7-0029001C0089}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21788,7 +21788,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="138" id="{00580002-0072-4A7D-BA8A-003000530018}">
+          <x14:cfRule type="dataBar" priority="138" id="{002500D0-00C4-4076-AAE6-00C3005C00C6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21800,7 +21800,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="137" id="{005B004F-00B3-4DB3-B2A4-00BF006000E9}">
+          <x14:cfRule type="dataBar" priority="137" id="{00F8008A-0010-4276-BCFD-008300700021}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21812,7 +21812,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="136" id="{001000C0-0025-490B-9564-00E200480082}">
+          <x14:cfRule type="dataBar" priority="136" id="{00D800AB-000D-454F-9DAC-004B0049002C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21824,7 +21824,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="135" id="{00FB00DE-00DB-46E3-A7A0-009400190018}">
+          <x14:cfRule type="dataBar" priority="135" id="{009C0096-0001-46D6-B89D-005C00D50029}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21836,7 +21836,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="134" id="{00690005-001F-4580-B12F-001C000E002F}">
+          <x14:cfRule type="dataBar" priority="134" id="{003F00F9-005B-461E-BC67-008B0059005D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21848,7 +21848,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="133" id="{00FA008D-00A7-4178-8583-005800C4007F}">
+          <x14:cfRule type="dataBar" priority="133" id="{00B90039-00D0-4A8C-A201-0046007C00CB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21860,7 +21860,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="132" id="{00AD000A-0051-4294-836C-0091006F00EF}">
+          <x14:cfRule type="dataBar" priority="132" id="{00BB0040-00F0-4E91-9097-004400840019}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21872,7 +21872,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="131" id="{00A90048-0024-4B7A-9E79-0046009E006A}">
+          <x14:cfRule type="dataBar" priority="131" id="{00FB0038-0086-459D-8E76-00F0009C00C5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21884,7 +21884,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="130" id="{0003001C-005A-4784-8BE3-005500650032}">
+          <x14:cfRule type="dataBar" priority="130" id="{00EA003D-00C7-4D1F-8DFB-00CE00C300E0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21896,7 +21896,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="129" id="{000C0091-00C2-461C-98FB-00350075001F}">
+          <x14:cfRule type="dataBar" priority="129" id="{006C0089-0065-4A53-B01D-002C00830043}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21908,7 +21908,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="128" id="{00DF0073-0011-4F74-844D-000600230032}">
+          <x14:cfRule type="dataBar" priority="128" id="{00820036-0015-4ABD-8EB8-00D400CD00EA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21920,7 +21920,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="127" id="{001100D2-0075-43DE-AE05-002C00BA00AF}">
+          <x14:cfRule type="dataBar" priority="127" id="{008D004A-0056-4AAD-8E22-001E002700B1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21932,7 +21932,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="126" id="{00A10061-00E0-4882-A05D-00C4002800DA}">
+          <x14:cfRule type="dataBar" priority="126" id="{00230023-00C9-40E0-AA57-008B00180019}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21944,7 +21944,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="125" id="{008A007E-00CA-4F58-9471-003800960055}">
+          <x14:cfRule type="dataBar" priority="125" id="{009E000C-007C-4DB4-B7DB-00F3004F004C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21956,7 +21956,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="124" id="{00450040-00C4-4D95-B4C1-0051008400ED}">
+          <x14:cfRule type="dataBar" priority="124" id="{00A7008A-0050-4AF6-B964-001A00E1004A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21968,7 +21968,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="123" id="{00BC006E-0041-40E2-A633-006E006D007E}">
+          <x14:cfRule type="dataBar" priority="123" id="{001700B2-0040-44FE-AC41-00F600A80077}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21980,7 +21980,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="122" id="{0068008D-007B-4D12-9CFF-001A00320069}">
+          <x14:cfRule type="dataBar" priority="122" id="{0053005C-0073-4307-9A2C-0050003E0059}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21992,7 +21992,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="121" id="{007C00F4-0058-468F-B4A2-00DA00C50011}">
+          <x14:cfRule type="dataBar" priority="121" id="{00160015-0000-46CC-8313-00F3005000C2}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22002,7 +22002,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="120" id="{008800B7-001E-4409-B610-00DE004500DC}">
+          <x14:cfRule type="dataBar" priority="120" id="{00F7007E-00A8-4C7F-9E9B-001E002F00E1}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22014,7 +22014,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="119" id="{00CF0029-0053-4A66-BD60-00E50025008B}">
+          <x14:cfRule type="dataBar" priority="119" id="{000E0065-00CE-4EB5-A16F-001C00750050}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22026,7 +22026,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="118" id="{00CF00FF-0048-4CBE-B63D-00BB00430085}">
+          <x14:cfRule type="dataBar" priority="118" id="{00EA0067-00A4-4A28-8D38-004700B5000C}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22036,7 +22036,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="117" id="{000E0019-002D-4F31-B3DB-003900D9000D}">
+          <x14:cfRule type="dataBar" priority="117" id="{003B00D7-0076-4E5A-B90B-0061005A00F4}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -22048,7 +22048,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="116" id="{00A10003-0037-4A16-BAF2-008000F70072}">
+          <x14:cfRule type="dataBar" priority="116" id="{00ED001B-0091-439D-8F18-001200F500A5}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22058,7 +22058,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="115" id="{00C00092-0038-443B-A20C-000F00E8005C}">
+          <x14:cfRule type="dataBar" priority="115" id="{001200CA-00A0-4E06-BFE2-003B00370006}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -22070,7 +22070,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="114" id="{00A3000A-0057-4D95-A354-0058004D007C}">
+          <x14:cfRule type="dataBar" priority="114" id="{00A90069-008D-48B5-A42F-002600110056}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22080,7 +22080,7 @@
           <xm:sqref>F155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="113" id="{00E20070-0059-4770-A0F7-004000430031}">
+          <x14:cfRule type="dataBar" priority="113" id="{00E5007D-0041-4A40-8B9A-006A00CA00E7}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22090,7 +22090,7 @@
           <xm:sqref>N155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="112" id="{00840008-0061-4927-8300-005D00F00051}">
+          <x14:cfRule type="dataBar" priority="112" id="{002700C0-0025-4721-AEBC-000900900036}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22100,7 +22100,7 @@
           <xm:sqref>S155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="111" id="{00CC0045-00D9-4350-9C55-004700170049}">
+          <x14:cfRule type="dataBar" priority="111" id="{00F10075-00AC-429B-A1D7-00E200FB005C}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22110,7 +22110,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="110" id="{0026005F-0010-47F5-A141-0006009D0027}">
+          <x14:cfRule type="dataBar" priority="110" id="{000F001D-00D9-4728-84EE-0070009B00BE}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -22122,7 +22122,7 @@
           <xm:sqref>T155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="109" id="{004A00A5-00F9-46F9-97D8-0088009F0053}">
+          <x14:cfRule type="dataBar" priority="109" id="{00FE00C8-00CF-4EC8-847C-0051008700A3}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22132,7 +22132,7 @@
           <xm:sqref>U155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="104" id="{00AD0095-00B9-4964-AE08-00B1000300E9}">
+          <x14:cfRule type="dataBar" priority="104" id="{005300A7-0091-49F6-992C-00D100D1005F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22144,7 +22144,7 @@
           <xm:sqref>F166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="103" id="{00DC00ED-0078-45B5-91D8-003200DC00D1}">
+          <x14:cfRule type="dataBar" priority="103" id="{00F40019-002A-4836-AB2A-00B50089008C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22156,7 +22156,7 @@
           <xm:sqref>F166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="102" id="{00570030-00F8-4404-A86E-009900F30015}">
+          <x14:cfRule type="dataBar" priority="102" id="{000500FD-0084-4262-8EFA-0067008900C5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22168,7 +22168,7 @@
           <xm:sqref>F167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="101" id="{009B00DB-00C0-40B2-AE1B-001B00B90098}">
+          <x14:cfRule type="dataBar" priority="101" id="{007C00D1-00B0-4C1D-83C6-00E8004E000B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22180,7 +22180,7 @@
           <xm:sqref>S166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="100" id="{001600D5-0041-4845-AD24-00AC008C00C3}">
+          <x14:cfRule type="dataBar" priority="100" id="{00BF00CB-00A3-4D33-872A-00FC00A20081}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22192,7 +22192,7 @@
           <xm:sqref>F166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="99" id="{009500AF-0024-417F-A255-00370007001D}">
+          <x14:cfRule type="dataBar" priority="99" id="{00700057-0000-4FAB-A43D-00E70080002D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22204,7 +22204,7 @@
           <xm:sqref>N166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="98" id="{00D90073-00D0-4441-BF8B-009F00480018}">
+          <x14:cfRule type="dataBar" priority="98" id="{004E00F0-005B-4643-84CC-005E00BE0089}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22216,7 +22216,7 @@
           <xm:sqref>F6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="97" id="{001200D6-0045-484F-BDDD-006A008E0089}">
+          <x14:cfRule type="dataBar" priority="97" id="{00090043-00F3-4C88-94E5-002200D800A9}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22226,7 +22226,7 @@
           <xm:sqref>F6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="96" id="{00E2002D-000F-40C4-A8AA-003A008300D1}">
+          <x14:cfRule type="dataBar" priority="96" id="{00100089-004C-4CE3-A3A0-008100400096}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22236,7 +22236,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="95" id="{00A1002B-0064-4589-8097-00B500640016}">
+          <x14:cfRule type="dataBar" priority="95" id="{00F900E8-00CA-4870-B23D-0073007000CD}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22246,7 +22246,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="94" id="{002300C7-0030-499A-9356-00BD00CA00AD}">
+          <x14:cfRule type="dataBar" priority="94" id="{004B001A-00D4-4DA1-BFE5-00E400460089}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22256,7 +22256,7 @@
           <xm:sqref>T153:U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="93" id="{00470020-0035-4A76-A1EF-005E003100BF}">
+          <x14:cfRule type="dataBar" priority="93" id="{00C6003D-0055-4830-9C40-0012003C00AC}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22266,7 +22266,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="92" id="{0080005E-008A-4369-995A-005D005A00B8}">
+          <x14:cfRule type="dataBar" priority="92" id="{00D80089-0018-490B-8002-008F00BF0095}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22276,7 +22276,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="91" id="{00250019-0041-4078-ABE2-0016001300EF}">
+          <x14:cfRule type="dataBar" priority="91" id="{005000F1-0039-46C7-A40B-005000FD0088}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22286,7 +22286,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="90" id="{00C500C9-00DA-4606-9AC4-001300D6000B}">
+          <x14:cfRule type="dataBar" priority="90" id="{0055006C-0037-4EA9-976D-001C00D5007F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -22298,7 +22298,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="89" id="{001500C8-00F4-405D-880C-00D30028000B}">
+          <x14:cfRule type="dataBar" priority="89" id="{00690069-00C7-44D3-BF42-0089007E0073}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22308,7 +22308,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="88" id="{009F0038-00F0-47B0-AFBB-00910025004E}">
+          <x14:cfRule type="dataBar" priority="88" id="{009A006A-006B-4811-B67E-00E200F90086}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22318,7 +22318,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="87" id="{009A00A0-0030-408F-A991-0017004E0003}">
+          <x14:cfRule type="dataBar" priority="87" id="{00730080-0084-48F3-975D-009200BA0068}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -22330,7 +22330,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="86" id="{009800D2-000A-458D-9325-004000B30006}">
+          <x14:cfRule type="dataBar" priority="86" id="{00470058-0000-4ED4-AC86-0094009D0059}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22340,7 +22340,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="85" id="{00E800A4-00E1-4299-9726-001900A50032}">
+          <x14:cfRule type="dataBar" priority="85" id="{002F00BA-0054-41A9-99C8-00EB00E2007E}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -22352,7 +22352,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="84" id="{00290056-00D8-4D25-A7BA-00A000350007}">
+          <x14:cfRule type="dataBar" priority="84" id="{007000F9-002A-4B08-ABF5-00C0009C004D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22364,7 +22364,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="83" id="{00A3004F-0045-469D-A1AD-00A4006D0026}">
+          <x14:cfRule type="dataBar" priority="83" id="{0069004B-0021-410F-B232-00A0008B00E5}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22374,7 +22374,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="82" id="{00CC001E-0081-4E9A-959B-00AF009000F8}">
+          <x14:cfRule type="dataBar" priority="82" id="{005D00D9-00C4-41DF-9277-006C00DF00BE}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22386,7 +22386,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="81" id="{002000A8-00FF-4319-B999-005B00380027}">
+          <x14:cfRule type="dataBar" priority="81" id="{0066007E-0069-4619-BB96-00AF00C400A6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22398,7 +22398,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="80" id="{00460083-002D-4F20-979B-00D700480034}">
+          <x14:cfRule type="dataBar" priority="80" id="{004E007E-00BE-4D69-BB36-00C5003F0006}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22408,7 +22408,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="79" id="{006500DA-004B-456C-A223-00FB0027009A}">
+          <x14:cfRule type="dataBar" priority="79" id="{00FE00C2-0072-4240-A280-0027001F004A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22420,7 +22420,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="78" id="{00320041-0009-420B-A0E0-00EB008A00DB}">
+          <x14:cfRule type="dataBar" priority="78" id="{0099008F-0069-46F3-AB88-0090002E0052}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22432,7 +22432,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="77" id="{00CF007B-009B-449B-9D0D-00F3009C0041}">
+          <x14:cfRule type="dataBar" priority="77" id="{00AD00AD-0067-47A7-8A76-00E9003E002E}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22442,7 +22442,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="76" id="{001B004B-00AC-4680-935B-0029005300E4}">
+          <x14:cfRule type="dataBar" priority="76" id="{007B005E-003A-4731-AF9E-00BB007300A6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22454,7 +22454,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="75" id="{006C00A5-002D-4B91-BD47-0052004600D4}">
+          <x14:cfRule type="dataBar" priority="75" id="{004A0097-0097-41F8-8D0C-00D500850059}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22466,7 +22466,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="74" id="{00DB00F5-0022-409A-895A-00E1009000B7}">
+          <x14:cfRule type="dataBar" priority="74" id="{00BE0052-000A-4290-9C59-007B002700C6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22478,7 +22478,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="73" id="{00670029-00B2-4D83-A3F7-003600E800BE}">
+          <x14:cfRule type="dataBar" priority="73" id="{0049009D-00B3-47A3-A381-0005003B0048}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22490,7 +22490,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="72" id="{00D300A0-00B7-43FF-AC6F-006C00520005}">
+          <x14:cfRule type="dataBar" priority="72" id="{00EC00D3-00B8-4193-8EA9-005900590026}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22500,7 +22500,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="71" id="{00D700FB-00B9-4920-8F6D-001300F300FD}">
+          <x14:cfRule type="dataBar" priority="71" id="{0005007F-001C-4D3F-896B-008500A8003D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22512,7 +22512,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="70" id="{00BE00BF-008E-4FFF-B6BF-009900DD0049}">
+          <x14:cfRule type="dataBar" priority="70" id="{004E0092-0011-4C05-8308-00BE00FB0043}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22524,7 +22524,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="69" id="{00AC0061-0040-4BA7-93A2-001700F50076}">
+          <x14:cfRule type="dataBar" priority="69" id="{00700039-00DB-434A-A53C-003E0097004C}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22534,7 +22534,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="68" id="{00820065-00D2-4984-B02E-003200CD0093}">
+          <x14:cfRule type="dataBar" priority="68" id="{008800B3-009B-4F4A-8FBD-00C800920034}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22546,7 +22546,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="67" id="{007B00BC-000C-4A31-B564-0011007800C5}">
+          <x14:cfRule type="dataBar" priority="67" id="{00970088-003D-4954-9ED3-00BD00380043}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22558,7 +22558,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="66" id="{005B00A7-001D-42E4-A53E-005E005600E9}">
+          <x14:cfRule type="dataBar" priority="66" id="{00A4008B-00FD-4057-B2CB-006B00460038}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22570,7 +22570,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="65" id="{00920067-00B6-46FF-A379-005500BE0013}">
+          <x14:cfRule type="dataBar" priority="65" id="{00D9004F-00CC-49A5-9CC9-009300C90094}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22582,7 +22582,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="64" id="{0031008A-0089-426B-A339-002400990084}">
+          <x14:cfRule type="dataBar" priority="64" id="{00F50031-0054-4FB2-9219-00A10017005F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22594,7 +22594,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="63" id="{009100AE-00D3-47A8-BB69-0016009B0001}">
+          <x14:cfRule type="dataBar" priority="63" id="{00640079-0000-462C-909F-007800EF008D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22606,7 +22606,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="62" id="{003D0068-0021-422A-89B9-007A000C0029}">
+          <x14:cfRule type="dataBar" priority="62" id="{00750042-002D-4CE1-B461-00A100E40046}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22618,7 +22618,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="61" id="{00F80071-005E-4674-B11E-00F700BD00E0}">
+          <x14:cfRule type="dataBar" priority="61" id="{00010075-00A4-46A2-BCB6-005400D500F6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22630,7 +22630,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="60" id="{001F0094-008B-471E-9A9B-0000009500F7}">
+          <x14:cfRule type="dataBar" priority="60" id="{00F70063-00DC-486A-92B9-00AA001600BB}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22642,7 +22642,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="59" id="{00A60060-0000-427D-9877-005200AA0026}">
+          <x14:cfRule type="dataBar" priority="59" id="{0022005B-0052-4CDB-A7D1-00D900DB00CB}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22652,7 +22652,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="58" id="{00DC0074-001C-48FC-A2F7-00B400DA000D}">
+          <x14:cfRule type="dataBar" priority="58" id="{0020008C-0002-4429-9E8A-00C000FC0036}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22662,7 +22662,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="57" id="{00C10046-002C-4BCA-B0FF-00BB006B00DA}">
+          <x14:cfRule type="dataBar" priority="57" id="{0040007A-0030-4385-9672-00BB00E100D7}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22674,7 +22674,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="56" id="{00F800FE-00B8-4BD1-B08E-0024004600C1}">
+          <x14:cfRule type="dataBar" priority="56" id="{00CC00A8-0012-4C01-BF7C-00AE00250046}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22686,7 +22686,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="55" id="{005E0087-0026-4F51-AA1B-00C600510063}">
+          <x14:cfRule type="dataBar" priority="55" id="{000900EB-001E-4AD3-B21B-00C3008100ED}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22698,7 +22698,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="54" id="{003100D9-0009-4E57-81FF-0095003B0001}">
+          <x14:cfRule type="dataBar" priority="54" id="{00840064-00AD-43AD-86DD-002000AB001A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22710,7 +22710,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="53" id="{00810000-00C5-47C0-B262-007F00940075}">
+          <x14:cfRule type="dataBar" priority="53" id="{00960053-0078-4650-AB8D-00FE001F008E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22722,7 +22722,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="52" id="{004000D5-005E-4ADD-AE97-00600025000C}">
+          <x14:cfRule type="dataBar" priority="52" id="{0001006A-00F0-4914-B7EF-00470002009D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22734,7 +22734,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="51" id="{00C3005F-00A8-49C2-9E83-0021009C00AF}">
+          <x14:cfRule type="dataBar" priority="51" id="{0066004E-00B5-404B-916E-00CA002D0071}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22746,7 +22746,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="50" id="{0073006C-0099-44FE-BB22-00C000F500E3}">
+          <x14:cfRule type="dataBar" priority="50" id="{00AA0092-000E-461C-978E-00AA006F0060}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22758,7 +22758,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="49" id="{00BD006E-00B3-41B1-8C61-00B200EB002D}">
+          <x14:cfRule type="dataBar" priority="49" id="{00A60014-0010-4908-9300-00BD0090002D}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22770,7 +22770,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="48" id="{00DC00F6-0070-4C2D-BFA5-009A00CE00D8}">
+          <x14:cfRule type="dataBar" priority="48" id="{00BD0028-00AF-4B4B-9DD6-0044005B0012}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22782,7 +22782,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="47" id="{00A20092-003D-4CBF-A5F4-00DD0017000C}">
+          <x14:cfRule type="dataBar" priority="47" id="{0008008E-0050-47A8-ADE8-000200F200DC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22794,7 +22794,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="46" id="{001900A4-0048-4AEC-BC6D-00DC00520032}">
+          <x14:cfRule type="dataBar" priority="46" id="{00730085-00A8-4946-B68C-0016003800BF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22806,7 +22806,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="45" id="{00E100A2-0075-4A09-B733-000700560034}">
+          <x14:cfRule type="dataBar" priority="45" id="{006500E6-0005-4453-9A2A-00F100420038}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22818,7 +22818,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="44" id="{00B8004D-008D-4BAC-A85A-0097003C0044}">
+          <x14:cfRule type="dataBar" priority="44" id="{00B60069-00B4-4DDA-A08C-008C002B0060}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22830,7 +22830,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="43" id="{009A0005-0019-4A68-943A-0087002B00A4}">
+          <x14:cfRule type="dataBar" priority="43" id="{007B0057-006C-40BB-9905-00DE006B00A6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22842,7 +22842,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="42" id="{005E0071-006E-482A-9E08-00CA00E1006B}">
+          <x14:cfRule type="dataBar" priority="42" id="{004D005E-00DC-4E15-A791-0056006D00A4}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22854,7 +22854,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="41" id="{003100B0-00E5-47ED-94F3-0043007800C5}">
+          <x14:cfRule type="dataBar" priority="41" id="{00B400D7-0074-4D54-BE4D-008D004F001E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22866,7 +22866,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="40" id="{00780086-00F0-43D4-BE40-00A200470021}">
+          <x14:cfRule type="dataBar" priority="40" id="{00BD002F-00C9-4717-933A-00600063009F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22878,7 +22878,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="39" id="{0092001D-00E0-4526-8FAC-00DB000D001B}">
+          <x14:cfRule type="dataBar" priority="39" id="{001F006B-0063-467A-A8AC-000C000E0034}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22890,7 +22890,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="38" id="{001B0049-005A-4156-BA83-00E900E700C1}">
+          <x14:cfRule type="dataBar" priority="38" id="{00BC0032-0067-479D-8BAD-000900C100D0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22902,7 +22902,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="37" id="{009300F1-0099-4571-B14F-00E9008C00D2}">
+          <x14:cfRule type="dataBar" priority="37" id="{00D200BF-0004-4C33-B5F4-002D00BF00B6}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22914,7 +22914,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="36" id="{009F002C-00E7-4684-BBBC-0061009400E0}">
+          <x14:cfRule type="dataBar" priority="36" id="{001D003C-007B-43E9-88A3-004B001F0067}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22926,7 +22926,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="35" id="{00A900AD-003F-47E7-9A0D-0022000700F5}">
+          <x14:cfRule type="dataBar" priority="35" id="{007B0022-0078-4FAB-8F41-000D00480089}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22938,7 +22938,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="34" id="{00C40097-00DE-44F1-BF42-009400970026}">
+          <x14:cfRule type="dataBar" priority="34" id="{004A0093-0092-4D93-B897-0060002C003A}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22950,7 +22950,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="33" id="{00FB006F-0075-491A-BA85-00840081006A}">
+          <x14:cfRule type="dataBar" priority="33" id="{002D0057-0013-46C5-98A4-005400C10051}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22960,7 +22960,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="32" id="{00AC002C-00DC-42B7-B23D-00AF00D00009}">
+          <x14:cfRule type="dataBar" priority="32" id="{00A70039-00E7-441E-A948-00AB00A30033}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22972,7 +22972,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="31" id="{00B40074-0075-4A8D-8A32-00C8004E00E3}">
+          <x14:cfRule type="dataBar" priority="31" id="{00F90055-00CD-42BF-AB6E-00AA0047002F}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22984,7 +22984,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="30" id="{005100C2-00C8-43E6-8EC2-00300008000C}">
+          <x14:cfRule type="dataBar" priority="30" id="{009900D6-0064-4E47-B700-00D100B500F9}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -22994,7 +22994,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="29" id="{00C5005E-009C-4EBB-907E-002D00460049}">
+          <x14:cfRule type="dataBar" priority="29" id="{00710018-0075-483E-A947-001E002B0025}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23006,7 +23006,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="28" id="{00CD00D0-007F-4FEA-8F8D-0052000E006C}">
+          <x14:cfRule type="dataBar" priority="28" id="{00DA00DD-00C7-45AB-8099-008D00C30018}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23018,7 +23018,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="27" id="{001A000F-000C-450D-B390-0098009800CD}">
+          <x14:cfRule type="dataBar" priority="27" id="{004E00C7-000A-4855-8AD2-00B50088000E}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23030,7 +23030,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="26" id="{0050004C-00DA-4A07-84AD-0018003F0015}">
+          <x14:cfRule type="dataBar" priority="26" id="{002200A0-00B1-4AFC-8D96-00DA009800C0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23042,7 +23042,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="25" id="{008100A0-0012-4115-9B13-00B400790020}">
+          <x14:cfRule type="dataBar" priority="25" id="{004C008C-0025-4734-8BE6-000D00BE00DC}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23054,7 +23054,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="24" id="{003F00D8-0075-4972-815D-00A500F30020}">
+          <x14:cfRule type="dataBar" priority="24" id="{00EE006E-0060-40E0-A851-0083001900E8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23066,7 +23066,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="23" id="{00920034-00A9-467D-86F3-009A0070000D}">
+          <x14:cfRule type="dataBar" priority="23" id="{00ED008B-0083-4A2D-AC4E-00BC002300E8}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23078,7 +23078,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="22" id="{00460041-00DA-4126-875F-008D004C00E9}">
+          <x14:cfRule type="dataBar" priority="22" id="{00F30039-0095-4E17-8728-00F50066001B}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23090,7 +23090,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="21" id="{002800EA-00C2-4307-82B4-002200F50053}">
+          <x14:cfRule type="dataBar" priority="21" id="{005400D4-0099-496B-8162-000D00460054}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23102,7 +23102,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="20" id="{00110067-000A-4104-9B1B-0032008F00B5}">
+          <x14:cfRule type="dataBar" priority="20" id="{00A00082-0055-4DB8-8C68-00E7005700B3}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23114,7 +23114,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="19" id="{0094008A-0060-48AB-B2AC-002C0001007B}">
+          <x14:cfRule type="dataBar" priority="19" id="{00DC0093-0069-44C1-A701-00DE003E0078}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23126,7 +23126,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="18" id="{0045001A-00C5-46F1-A29C-0084001700AD}">
+          <x14:cfRule type="dataBar" priority="18" id="{007200D9-002D-451E-A9B2-00F3008800CF}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23138,7 +23138,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="17" id="{00B400EA-0098-45FE-B2E7-00AE003C00BA}">
+          <x14:cfRule type="dataBar" priority="17" id="{00330033-00CE-4680-9C97-00FA00E70073}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23150,7 +23150,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="16" id="{00A2003E-0042-4C27-BDC8-00DB001C0028}">
+          <x14:cfRule type="dataBar" priority="16" id="{00E8007E-0049-4570-B4F4-00C7001A0026}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23160,7 +23160,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="15" id="{00770083-0024-49CA-969E-009A006A0044}">
+          <x14:cfRule type="dataBar" priority="15" id="{00950024-0022-40C6-BF89-008E005C0087}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -23172,7 +23172,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="14" id="{00870072-0065-49CD-B28B-004B0007003B}">
+          <x14:cfRule type="dataBar" priority="14" id="{00B8003A-0055-4744-9002-007C001700AA}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23182,7 +23182,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="13" id="{00E00053-0033-4FB8-8AE3-0049002000A1}">
+          <x14:cfRule type="dataBar" priority="13" id="{002900F0-00CA-4203-8306-00970034003C}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -23194,7 +23194,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="12" id="{00B50019-004B-4971-A367-000D002F0050}">
+          <x14:cfRule type="dataBar" priority="12" id="{0087003D-0085-4600-B808-000700B700E4}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -23206,7 +23206,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="11" id="{001200F7-0027-4AD7-A087-00A400B300B5}">
+          <x14:cfRule type="dataBar" priority="11" id="{0098003D-00F3-4FED-8287-00CF00CB00E2}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -23218,7 +23218,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="10" id="{00480083-00B1-45A7-9B5E-003F0042002F}">
+          <x14:cfRule type="dataBar" priority="10" id="{004B0007-009B-4B0F-A39C-006000B9000B}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23228,7 +23228,7 @@
           <xm:sqref>F153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="9" id="{0050006A-003B-4900-B2ED-00E700CD00D1}">
+          <x14:cfRule type="dataBar" priority="9" id="{004D00FB-00F9-4668-A921-0008009E00CF}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23238,7 +23238,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="8" id="{00770091-00E0-45C2-AEF2-00C70077006A}">
+          <x14:cfRule type="dataBar" priority="8" id="{006A0038-00DE-4A88-A20A-00A1000200B0}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23248,7 +23248,7 @@
           <xm:sqref>S153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="7" id="{008C007D-00EE-4E5D-99EE-00F700350093}">
+          <x14:cfRule type="dataBar" priority="7" id="{0006002F-004F-48FB-B93B-0012000800AA}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23258,7 +23258,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="6" id="{003F001F-000B-436E-B4DC-008800BC0030}">
+          <x14:cfRule type="dataBar" priority="6" id="{00FA0063-005D-492B-9A93-005600900009}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -23270,7 +23270,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="5" id="{00AB0029-0034-4E41-ACB3-00C9000600D8}">
+          <x14:cfRule type="dataBar" priority="5" id="{001500B1-00C8-4B65-B3BE-00CD006C00FC}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23280,7 +23280,7 @@
           <xm:sqref>N153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="4" id="{006500E5-0018-4AD1-8159-008700F100AB}">
+          <x14:cfRule type="dataBar" priority="4" id="{00DB00BD-00FF-4C31-BEC0-00C6005300CB}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23290,7 +23290,7 @@
           <xm:sqref>T153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3" id="{00FA0036-004C-47CA-8942-00CF00DC004D}">
+          <x14:cfRule type="dataBar" priority="3" id="{00270009-00A2-4A1E-B268-007300CF0007}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23300,7 +23300,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2" id="{00A200B6-00F0-4ECA-9AAF-00D100BE0009}">
+          <x14:cfRule type="dataBar" priority="2" id="{00B80058-00A3-4CBC-A9CD-003F005F0032}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -23310,7 +23310,7 @@
           <xm:sqref>U153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1" id="{005F00E4-00A5-40B4-9259-007B008000F7}">
+          <x14:cfRule type="dataBar" priority="1" id="{00B80089-00CE-4BED-9519-001D0025000F}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -28087,7 +28087,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="13" id="{00D000CC-00B3-4783-9255-00CD006B0096}">
+          <x14:cfRule type="dataBar" priority="13" id="{0056002E-00C8-4F4F-B805-000B00500021}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28099,7 +28099,7 @@
           <xm:sqref>F17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="11" id="{00F10054-00B1-4AE8-836D-007B009C008F}">
+          <x14:cfRule type="dataBar" priority="11" id="{007600DD-0061-4A44-92EF-005800A10097}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28111,7 +28111,7 @@
           <xm:sqref>N4:N11 N13:N18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="10" id="{000D00DC-001F-4A16-B623-006800260070}">
+          <x14:cfRule type="dataBar" priority="10" id="{00CF0035-002C-4FC0-8693-00D4001D00C0}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28123,7 +28123,7 @@
           <xm:sqref>R4:R11 R13:R18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="15" id="{009300B2-002A-4AFD-8B30-00460058009F}">
+          <x14:cfRule type="dataBar" priority="15" id="{004200F7-00CC-4021-8588-004300520051}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28135,7 +28135,7 @@
           <xm:sqref>R1:R11 R13:R18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="17" id="{00C200E8-00C7-4033-8291-00FA00800095}">
+          <x14:cfRule type="dataBar" priority="17" id="{006200C1-00C4-46CB-8CC4-00950002001C}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28147,7 +28147,7 @@
           <xm:sqref>N1:N11 N13:N18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="74" id="{0085003D-0071-4015-B399-001C00630063}">
+          <x14:cfRule type="dataBar" priority="74" id="{003C0020-00F6-407B-8320-0018001A0065}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28159,7 +28159,7 @@
           <xm:sqref>F1:F11 F13:F14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="6" id="{006300BB-009B-48C4-9BAA-00BF00A50097}">
+          <x14:cfRule type="dataBar" priority="6" id="{007100A2-00EE-4D20-AAAE-00B900F40013}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28171,7 +28171,7 @@
           <xm:sqref>F12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="5" id="{00C00083-0069-472B-8DDF-00B6000100F3}">
+          <x14:cfRule type="dataBar" priority="5" id="{00CE00A4-00A6-40B1-A115-00AF00E50041}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28183,7 +28183,7 @@
           <xm:sqref>N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="4" id="{00A800DE-00C0-4F45-AE66-00D8007E00E9}">
+          <x14:cfRule type="dataBar" priority="4" id="{006300D6-00FB-4AFE-8D1D-0039003A00A9}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28195,7 +28195,7 @@
           <xm:sqref>R12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="7" id="{000300BE-0030-426C-B772-00F300FB0024}">
+          <x14:cfRule type="dataBar" priority="7" id="{00F800CC-002D-4EE5-A4D0-000D00EF0015}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28207,7 +28207,7 @@
           <xm:sqref>R12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="8" id="{000C00FE-006B-4218-8AB4-00B0007D00D6}">
+          <x14:cfRule type="dataBar" priority="8" id="{00B500B2-006D-4F74-810D-00CB00850021}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28219,7 +28219,7 @@
           <xm:sqref>N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="9" id="{00060057-0080-461D-BD29-00FC00B4006C}">
+          <x14:cfRule type="dataBar" priority="9" id="{00B100D1-00BB-4708-9F14-001700610052}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28231,7 +28231,7 @@
           <xm:sqref>F12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="3" id="{001400EB-0001-47F0-9174-0022002F00FE}">
+          <x14:cfRule type="dataBar" priority="3" id="{001B0057-00FB-4106-906F-0025000B00F5}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28243,7 +28243,7 @@
           <xm:sqref>R4:R17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2" id="{00E5006B-000B-440F-94E5-004D00DE00FC}">
+          <x14:cfRule type="dataBar" priority="2" id="{00B200C7-0078-4791-833B-00AB006400EA}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28255,7 +28255,7 @@
           <xm:sqref>N4:N17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="1" id="{00F300AC-007D-4787-9C21-007F001B0088}">
+          <x14:cfRule type="dataBar" priority="1" id="{00510026-00A5-47FF-834E-00F3009200FD}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28267,7 +28267,7 @@
           <xm:sqref>F4:F17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="75" id="{00270056-00E2-4129-8428-008B00A90032}">
+          <x14:cfRule type="dataBar" priority="75" id="{00EE00BF-0026-43F9-83CB-0055003D0006}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -28279,7 +28279,7 @@
           <xm:sqref>F4:F11 F13:F18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="77" id="{00750016-0055-4A79-ACC9-006A00780012}">
+          <x14:cfRule type="dataBar" priority="77" id="{00CA0052-0039-4FE0-AD05-00E200E40031}">
             <x14:dataBar maxLength="100" minLength="0" axisPosition="automatic" direction="context" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
